--- a/Noticias_Calcario_20260723.xlsx
+++ b/Noticias_Calcario_20260723.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D521"/>
+  <dimension ref="A1:D520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e2471054300949a6a1e2db1d4be&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a6263720c134cf998936ed89d546006&amp;url=https%3a%2f%2fwww.standardmedia.co.ke%2fsmart-harvest%2farticle%2f2001553298%2fmuranga-county-distributes-lime-to-coffee-farmers-to-boost-production&amp;c=8181289782834766550&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -1541,66 +1541,66 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Transporte de calcário ficará temporariamente suspenso a partir de agosto - Prefeitura de Sidrolândia</t>
+          <t>Cotações Agrícolas para esta Sexta-feira 17 de Julho de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>17/07/2026 10:55</t>
+          <t>17/07/2026 11:55</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQckh6Yk1FVUpxQ2w3LTd3RENtblNmNFZ0ekd0TFNYUlI4blJwampSZ0FINEdOSlVMd1hYT1N2aW8tS1BGSGFFV25qWHpCZEt4VzV2bWJYMC04eVRXWDlXZDlYS3N4b3VndDhYZVhHQW9fMGQtdUxBUVBVQmQ2RklETUlRaFVHbFMza0lsaU80SFUyV1IwOElvdGNWbXk3TXFVVEszUjVnQ0hacmhoTk9aOTVPV3ZYUkl2M1IzazEzQ05WQ2FaWFBLNWhDdW5FbEJqM1RLSC1MZ185ZlFacFJsRmNjVllUc2l0N3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQNWJzVkRJVkl2OVJ4c3VqeHVlX09mSmJRMXJLUDdLTkNZT2pLRFFlT2M4cklRLWt3d3hLQll2VFhnY09OODBkV0UxMmxzaGdkeDNJYnNpN3BBRC1fdDZOc3BhSzZnRHFhM0l1SnkyT0FwdDI0MjhiWmpoUGhPdWoyamJ2d0hrZGg2aVRDVGZoTFJZYzA0Ukx2MVVHMkpTSGZaYWJYS0J3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Após polêmica da maconha, Piovani detona Virginia e chama de "loira de laboratório": "Cheiro de enxofre" - Folha Vitória</t>
+          <t>Transporte de calcário ficará temporariamente suspenso a partir de agosto - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>17/07/2026 07:47</t>
+          <t>17/07/2026 10:55</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTmh6UXNDdlRkVklBdWpzaWVtc1ZGZk5aVzNTMGRGeXN0MFlrMWktN2Jnd3hEdFJYMnJuV2VvQ3ViWG9YNVYwNzh2TWZwT2pFcDZpVHBFcHpvaHMyN2o0X2t2bzF0b1VNN3pmdlNENjAwNmd0enk4bjNqSHNVSFMwMFdnYTNDREMyZzdfRUQ2WFAyNGNiVURxaExPQU01enlFbU1XTHNyVnFWdUtiSlhLLUczYWNiUExDZWNOS1kwRTdfcmtjZ0RCQlEzbnVXYlNSSk5CdjhGakFfZ001SGIzbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQckh6Yk1FVUpxQ2w3LTd3RENtblNmNFZ0ekd0TFNYUlI4blJwampSZ0FINEdOSlVMd1hYT1N2aW8tS1BGSGFFV25qWHpCZEt4VzV2bWJYMC04eVRXWDlXZDlYS3N4b3VndDhYZVhHQW9fMGQtdUxBUVBVQmQ2RklETUlRaFVHbFMza0lsaU80SFUyV1IwOElvdGNWbXk3TXFVVEszUjVnQ0hacmhoTk9aOTVPV3ZYUkl2M1IzazEzQ05WQ2FaWFBLNWhDdW5FbEJqM1RLSC1MZ185ZlFacFJsRmNjVllUc2l0N3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Galeria de Porcelanato - serie New Limestone - 3 - ArchDaily</t>
+          <t>Após polêmica da maconha, Piovani detona Virginia e chama de "loira de laboratório": "Cheiro de enxofre" - Folha Vitória</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>17/07/2026 05:20</t>
+          <t>17/07/2026 07:47</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUm10el9ibGdzeXJnbUozcmNURExkYmRjNVpSUEdNblBrZE1oQ0Y2TEs4NlNsTGJIVmllNFB2a2FDRDBZM1dxc2I1ZTl0alJIU3dHZXczLUhMYUUwMXhQUWdvbk5LdTFwby1KYzV2aDJMWVhBa3h5bWVxdm8tN19FV3BYOXRhVERCS0I4a3d1SDdtdV9LVlloVHVCYTBvS3o2dXhr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPTmh6UXNDdlRkVklBdWpzaWVtc1ZGZk5aVzNTMGRGeXN0MFlrMWktN2Jnd3hEdFJYMnJuV2VvQ3ViWG9YNVYwNzh2TWZwT2pFcDZpVHBFcHpvaHMyN2o0X2t2bzF0b1VNN3pmdlNENjAwNmd0enk4bjNqSHNVSFMwMFdnYTNDREMyZzdfRUQ2WFAyNGNiVURxaExPQU01enlFbU1XTHNyVnFWdUtiSlhLLUczYWNiUExDZWNOS1kwRTdfcmtjZ0RCQlEzbnVXYlNSSk5CdjhGakFfZ001SGIzbg?oc=5</t>
         </is>
       </c>
     </row>
@@ -1612,161 +1612,161 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Galeria de Limestone, Granite and Travertine - 8 - ArchDaily</t>
+          <t>Galeria de Porcelanato - serie New Limestone - 3 - ArchDaily</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>17/07/2026 03:58</t>
+          <t>17/07/2026 05:20</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOY0pYQ3FwR0g1cHlZMnk3bnlsc1dqRFlqZ3ktVWcycHB5TU9GcDRSOFUweHpsXzA4VzVYdkh0QS1RV2JoYkNLZXB2bzhrQmNPZHVwUnowVERPYTNqLU8zelNPUVZZQU5lLVk2UnJRYlI5Q2wxTVBSLVpKYXQ1NWl2VUh1VDJTQUQ1Nk9EekZUWmk0NGhsLW9hM3FLVmQ4b0lsempwNGl0NzRpWXFpcVpyT2VfVm9nLW1UT2YteklKdlZTQV9zM1RJMTBZcXdhMFppR0NkbGhPSlE1SS13R2VNUFJwcXFnZ3dic192am9xSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQUm10el9ibGdzeXJnbUozcmNURExkYmRjNVpSUEdNblBrZE1oQ0Y2TEs4NlNsTGJIVmllNFB2a2FDRDBZM1dxc2I1ZTl0alJIU3dHZXczLUhMYUUwMXhQUWdvbk5LdTFwby1KYzV2aDJMWVhBa3h5bWVxdm8tN19FV3BYOXRhVERCS0I4a3d1SDdtdV9LVlloVHVCYTBvS3o2dXhr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Galeria de Casa de Calcário / Archer + Braun - 31 - ArchDaily</t>
+          <t>Galeria de Limestone, Granite and Travertine - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>17/07/2026 01:57</t>
+          <t>17/07/2026 03:58</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQT2NkakNmbkgzalhHVXJQbk1jUFhaYldjUDY5bzd5dk5rUGpNZDVwcUs4UGZnb2dSSmx1OHowbUppbmhEWjZkSnBmTnJFQlFEWjhKSVdFS0JuSVRSdkJWOHVnUzRFS2NXRER2eEpIUllodnRJZ2Z3d19CZ0k4TmNJV3lmd3pzaG1na1BXeDE2TWMtUEVrYWNNOUNYSmYwYnRvLU45UUxTQ0tKa1F5VFY5cDBxVWtlbnlFeWhHWVVYSEdUQTd5R0Zld0J0NndycjU5aXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxOY0pYQ3FwR0g1cHlZMnk3bnlsc1dqRFlqZ3ktVWcycHB5TU9GcDRSOFUweHpsXzA4VzVYdkh0QS1RV2JoYkNLZXB2bzhrQmNPZHVwUnowVERPYTNqLU8zelNPUVZZQU5lLVk2UnJRYlI5Q2wxTVBSLVpKYXQ1NWl2VUh1VDJTQUQ1Nk9EekZUWmk0NGhsLW9hM3FLVmQ4b0lsempwNGl0NzRpWXFpcVpyT2VfVm9nLW1UT2YteklKdlZTQV9zM1RJMTBZcXdhMFppR0NkbGhPSlE1SS13R2VNUFJwcXFnZ3dic192am9xSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 25 - ArchDaily</t>
+          <t>Galeria de Casa de Calcário / Archer + Braun - 31 - ArchDaily</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>17/07/2026 01:18</t>
+          <t>17/07/2026 01:57</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQbFY3SFNuUWE1NVB1UW44bFBMd3NZZWtKVlY2SmU2LXRIaEU4cXBEUjF5SlVMN1pyQ3pmbUdlU0VmNUl6STVzUE5JcTJfOVFyNlp2WXJ1ajVsTTl5M3RQclFBTEVDbFZhNXVxN3pRRWh5UVZ2UVBMQjYydnI5aWc1SU1LOVUyWUpBLUgtWHc4VVRxSTV2V256LXVnR2xzb2V0M0ljQ2JoT1dMU2NhamI1anJlREV6aGRQZkFuUFlGY0pXY2VYQjdnVWRQMDJaalVWOVd6X2xpRkk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQT2NkakNmbkgzalhHVXJQbk1jUFhaYldjUDY5bzd5dk5rUGpNZDVwcUs4UGZnb2dSSmx1OHowbUppbmhEWjZkSnBmTnJFQlFEWjhKSVdFS0JuSVRSdkJWOHVnUzRFS2NXRER2eEpIUllodnRJZ2Z3d19CZ0k4TmNJV3lmd3pzaG1na1BXeDE2TWMtUEVrYWNNOUNYSmYwYnRvLU45UUxTQ0tKa1F5VFY5cDBxVWtlbnlFeWhHWVVYSEdUQTd5R0Zld0J0NndycjU5aXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 25 - ArchDaily</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>16/07/2026 20:53</t>
+          <t>17/07/2026 01:18</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQbFY3SFNuUWE1NVB1UW44bFBMd3NZZWtKVlY2SmU2LXRIaEU4cXBEUjF5SlVMN1pyQ3pmbUdlU0VmNUl6STVzUE5JcTJfOVFyNlp2WXJ1ajVsTTl5M3RQclFBTEVDbFZhNXVxN3pRRWh5UVZ2UVBMQjYydnI5aWc1SU1LOVUyWUpBLUgtWHc4VVRxSTV2V256LXVnR2xzb2V0M0ljQ2JoT1dMU2NhamI1anJlREV6aGRQZkFuUFlGY0pXY2VYQjdnVWRQMDJaalVWOVd6X2xpRkk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Esqueça o asfalto comum: asfalto com caroços de azeitona captura carbono em Barcelona, substitui calcário por biochar e promete reduzir 76% da pegada climática sem perder resistência ao calor, à umidade, às fissuras e ao tráfego urbano, abrindo caminh - CPG Click Petróleo e Gás</t>
+          <t>Índia aprova nova política de investimentos em ureia - GlobalFert</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>16/07/2026 17:18</t>
+          <t>16/07/2026 20:53</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOVkZzaEljMWxZcmVQc1hIWGVDY095R1ZNbk9aQUswNENKME5IQnc4d21nNm1KUWxGYk80Y1dLSUJLd1lONERoc21RNFRHTGRUN0huRXYzQXFfMjJvTzlYcmIxRWxLY3BZemxZaVZHRl9sVDJUZlVYdGxmS0dnQXpfRFhPR1R4RTRVcERfbWhZdVE3T0ZtREJpUU9uR2pjbjRVQzM2TGZjX3B0ZDVHZWd4YzZ1Vm5nZV9vT2ZsbmZPZ3ZiNm5VVmMwQUtwb3REcVktalFMc011LXhTT1p3dng3Q0NfNmRhcG5MVFFEcmNjeVB6VG0yWTJhQ3haTlFjVEI3NGdnWVBDaG93OTBKamR3SXU0akx1UFJxQnJOMFRncE5vSHVNOGRDc2tEbERBNkEtd09HbVVnNXBXdS1qWEJaaWQwZ1NLZjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOeUZvQlZWVTlrTnNwbkkwZnVGT3hZYlNEWjhCeEVxR21OOU5aV2YwdmoxUHV4X0Yycm1LSGlHYkp3S1F5NkRaZFUyTEpBdmNaemJhSFB0WXFYNmU1c194SFZtaXBlQlF5d2Z3a0ltOThHbXVNSGxvLXdXT2JfT2hkZUs3ZHF0MUFodzJPdW5WSzVlQk1rZzlyNGZuNmY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 5 - ArchDaily</t>
+          <t>Esqueça o asfalto comum: asfalto com caroços de azeitona captura carbono em Barcelona, substitui calcário por biochar e promete reduzir 76% da pegada climática sem perder resistência ao calor, à umidade, às fissuras e ao tráfego urbano, abrindo caminh - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>16/07/2026 15:35</t>
+          <t>16/07/2026 17:18</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQMWs0R1JTWnUwTFNadktVN2lNemtJeG40WWdOa1RzdXZyQnBJQUFWVGU0RlVYRWNwc1hGT2ZVbjI1ck0yVGJYYlNQQ1doVmdTUDlyamRsQ011U0pPeEVNN0dqY0tPSVJXbkdLWnRPSWRhbHFnMUNxbXBoNEVwWUJsT043N3J2aXlGLTM0YU0wYkUtdE1yUGY2dEdiR056RG5UTzg0aUF0SlBYWUlVbzdpaExLN19ObzBXdlhUclYwd2QtS0RPVFZtS2ZtRGE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxOVkZzaEljMWxZcmVQc1hIWGVDY095R1ZNbk9aQUswNENKME5IQnc4d21nNm1KUWxGYk80Y1dLSUJLd1lONERoc21RNFRHTGRUN0huRXYzQXFfMjJvTzlYcmIxRWxLY3BZemxZaVZHRl9sVDJUZlVYdGxmS0dnQXpfRFhPR1R4RTRVcERfbWhZdVE3T0ZtREJpUU9uR2pjbjRVQzM2TGZjX3B0ZDVHZWd4YzZ1Vm5nZV9vT2ZsbmZPZ3ZiNm5VVmMwQUtwb3REcVktalFMc011LXhTT1p3dng3Q0NfNmRhcG5MVFFEcmNjeVB6VG0yWTJhQ3haTlFjVEI3NGdnWVBDaG93OTBKamR3SXU0akx1UFJxQnJOMFRncE5vSHVNOGRDc2tEbERBNkEtd09HbVVnNXBXdS1qWEJaaWQwZ1NLZjg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 5 - ArchDaily</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>16/07/2026 15:34</t>
+          <t>16/07/2026 15:35</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQMWs0R1JTWnUwTFNadktVN2lNemtJeG40WWdOa1RzdXZyQnBJQUFWVGU0RlVYRWNwc1hGT2ZVbjI1ck0yVGJYYlNQQ1doVmdTUDlyamRsQ011U0pPeEVNN0dqY0tPSVJXbkdLWnRPSWRhbHFnMUNxbXBoNEVwWUJsT043N3J2aXlGLTM0YU0wYkUtdE1yUGY2dEdiR056RG5UTzg0aUF0SlBYWUlVbzdpaExLN19ObzBXdlhUclYwd2QtS0RPVFZtS2ZtRGE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 4 - ArchDaily</t>
+          <t>Ibram alerta Fazenda sobre ‘escassez crítica’ de enxofre frente à guerra no Irã - Agência iNFRA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPSWZqdzlVMnphVVNtYlMtZTh3X1RwUHFmY01tQlJxeDZVYTFhWUd3TTNJVWxWUUpWZV9BdmJJcFJlaXdmTmprRnJKMmp6SjZwaUNuZ2N3RGFIY29xYnk3Y1RNeU45SHdDbENpaEU2SUJwcDVqZFMwS09CcG05UkVPenRhUENNdXFmMEYyVFBjT09aOXBzUjZQVzBTTHNBZ0hfc3N5Y05SMTRrcWN1NGZGcUtTenowbmxDSVFyTndIa3FXb0l1XzlWYXRHMEk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQWVlDSXJhUjhBLXJpZ0pnVFJEYm1FbjNpeVkxX3RnR20tZXNLOUZFWHVWVWdBekVYOXh2cGpJVEtodmtjSnRKR2VKWWpkeHpEbDQ4S0dXS19WNHdPWkdJMDNodkVTUllxLVhEV1lMVkxMUmZFWWlETm5uQlZaRVZFRXRva0sxOUFGVzB4Mnl4a1RuM3djY01YX0hYSDYzaWpIaVhzRjdyZ09ERE8z?oc=5</t>
         </is>
       </c>
     </row>
@@ -1788,193 +1788,193 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 2 - ArchDaily</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 4 - ArchDaily</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>16/07/2026 15:32</t>
+          <t>16/07/2026 15:34</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQRVJGNHE3Wl9WZ1h0YjVDM3NSN2RkdllYVlZJTG9IaFJPSmdJcGpaemI5VjlhSHVuaklKd3hUMHJjQkZMTUl5a0dMSmtpa2gtdk9zckF2SWFyMGZHc0JhXzNTNnMzS2p0N2VuNk5oWTJkLUxxcmdmMmVQZ0pxVGh5eWVMaDhpWnZSMmF2MHc0Sk5RS2RBckFaNmdVYzN1SktScDZDVUZqem5FVlo3TmNDV3NmVjNUenJPY3otX1JkRWhvOHQ5aEd6NktKSXQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPSWZqdzlVMnphVVNtYlMtZTh3X1RwUHFmY01tQlJxeDZVYTFhWUd3TTNJVWxWUUpWZV9BdmJJcFJlaXdmTmprRnJKMmp6SjZwaUNuZ2N3RGFIY29xYnk3Y1RNeU45SHdDbENpaEU2SUJwcDVqZFMwS09CcG05UkVPenRhUENNdXFmMEYyVFBjT09aOXBzUjZQVzBTTHNBZ0hfc3N5Y05SMTRrcWN1NGZGcUtTenowbmxDSVFyTndIa3FXb0l1XzlWYXRHMEk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Relação de troca entre commodities e fertilizantes melhora em junho - CNN Brasil</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 2 - ArchDaily</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>16/07/2026 15:09</t>
+          <t>16/07/2026 15:32</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ083ZEVXbTlzZEJWOGFwLWZJNy12LWdDcV8yUWRRUzFsa3c5Q0tqRlhQZVRESVZwU1JOR3ZvcktUYlJVTm16b1RyQmZRcG15TjYwVlg5YjRCQkRaZU5SdVhBajZobWhhN3k4Nlk1a1FCaEgyanlWYlZsSHBSb1pYT0pKVXhkalhuSGZnd1o5T3MzZFVLRHNHMlhjQ0xTdVo3dF9IYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQRVJGNHE3Wl9WZ1h0YjVDM3NSN2RkdllYVlZJTG9IaFJPSmdJcGpaemI5VjlhSHVuaklKd3hUMHJjQkZMTUl5a0dMSmtpa2gtdk9zckF2SWFyMGZHc0JhXzNTNnMzS2p0N2VuNk5oWTJkLUxxcmdmMmVQZ0pxVGh5eWVMaDhpWnZSMmF2MHc0Sk5RS2RBckFaNmdVYzN1SktScDZDVUZqem5FVlo3TmNDV3NmVjNUenJPY3otX1JkRWhvOHQ5aEd6NktKSXQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
+          <t>Relação de troca entre commodities e fertilizantes melhora em junho - CNN Brasil</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>16/07/2026 14:06</t>
+          <t>16/07/2026 15:09</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQQ083ZEVXbTlzZEJWOGFwLWZJNy12LWdDcV8yUWRRUzFsa3c5Q0tqRlhQZVRESVZwU1JOR3ZvcktUYlJVTm16b1RyQmZRcG15TjYwVlg5YjRCQkRaZU5SdVhBajZobWhhN3k4Nlk1a1FCaEgyanlWYlZsSHBSb1pYT0pKVXhkalhuSGZnd1o5T3MzZFVLRHNHMlhjQ0xTdVo3dF9IYw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>O pequeno detalhe na história da Esfinge de Gizé que ajuda a explicar quem realmente construiu o monumento e a origem de seu nariz quebrado</t>
+          <t>Ibram alerta Ministério da Fazenda sobre crise de enxofre no Brasil - tmc.com.br</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>16/07/2026 14:01</t>
+          <t>16/07/2026 14:06</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e22840445a6bb3073b47f1d0a87&amp;url=https%3a%2f%2fwww.brasil247.com%2ftendencias%2f2026%2f07%2f17%2fo-pequeno-detalhe-na-historia-da-esfinge-de-gize-que-ajuda-a-explicar-quem-realmente-construiu-o-monumento-e-a-origem-de-seu-nariz-quebrado%2f&amp;c=11243632077870985315&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQd09GVWFtZzZYdVpMWC1jWXA2TElWMlFleFI1eXFtdkVYQ1JGaEp5SU4wVmpJUXpfMUFYdUl0U2dUeUJ3aUt4Zm43Q09ia1NqLUN2cjFOMUQ3YllzUmVJV3VyLTBrVWY1VW9HcTV6bDl2cnZJWmhTNmdVQ3ZkdFVsay1aX1ZxNFpUU3BZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 8 - ArchDaily</t>
+          <t>O pequeno detalhe na história da Esfinge de Gizé que ajuda a explicar quem realmente construiu o monumento e a origem de seu nariz quebrado</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>16/07/2026 13:21</t>
+          <t>16/07/2026 14:01</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNQlJkVjBpYk1xQ090TG90alp1VElrclpxYW9QVGg5MEVCYXBGb01nMzNzQWY1XzZmRWZDVnplTVVFZkpKVURwUEtfNFlLc2VnX3lNVEZoekZCNVB2WnUxTUZmMUNJLTVSQU1CMlBWX2dWZkNMS0RDMnhXVVJCT1BSYkhUeHJyRFFyb01sY0daYl9LckVFc1d6T24zQnkteHBpb1VvYTh3ajBXQUIxWk1TQUlIel9ldUpkLUFudQ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a62637127514cce807a8122af676e49&amp;url=https%3a%2f%2fwww.brasil247.com%2ftendencias%2f2026%2f07%2f17%2fo-pequeno-detalhe-na-historia-da-esfinge-de-gize-que-ajuda-a-explicar-quem-realmente-construiu-o-monumento-e-a-origem-de-seu-nariz-quebrado%2f&amp;c=11243632077870985315&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>São José dos Campos: Prefeitura abre inscrições para programa de transporte gratuito de calcário a produtores rurais - 012 News</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 8 - ArchDaily</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>16/07/2026 11:16</t>
+          <t>16/07/2026 13:21</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPdE1HS2p0SklJSEdWOFd3THVDMjU0LTZFenBORjJ2RHFCdTQwLVJUNEJoZkt3M2F5Y2c1U1BDb2NEYkRhemxCRnMyVVZrYllOeXFvYzlpazJpSE0yRGNGcGFEeXVYU3lmRHl5R3ZPNzZZeTZjTHZoeU5zWVpURmdpSVdPZ3IzMFlLV0tfNEhZMmt6eWpFM1hpY1F3TVFfYzNqaHIzYUdWOWNQSHFXRFVLY0lWNmduX2F4MkxlZk1qTWc4VXpLeW5jUVdTRVp0cXlVbHRHcy1sSi1ORms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNQlJkVjBpYk1xQ090TG90alp1VElrclpxYW9QVGg5MEVCYXBGb01nMzNzQWY1XzZmRWZDVnplTVVFZkpKVURwUEtfNFlLc2VnX3lNVEZoekZCNVB2WnUxTUZmMUNJLTVSQU1CMlBWX2dWZkNMS0RDMnhXVVJCT1BSYkhUeHJyRFFyb01sY0daYl9LckVFc1d6T24zQnkteHBpb1VvYTh3ajBXQUIxWk1TQUlIel9ldUpkLUFudQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
+          <t>São José dos Campos: Prefeitura abre inscrições para programa de transporte gratuito de calcário a produtores rurais - 012 News</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>16/07/2026 09:14</t>
+          <t>16/07/2026 11:16</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxPdE1HS2p0SklJSEdWOFd3THVDMjU0LTZFenBORjJ2RHFCdTQwLVJUNEJoZkt3M2F5Y2c1U1BDb2NEYkRhemxCRnMyVVZrYllOeXFvYzlpazJpSE0yRGNGcGFEeXVYU3lmRHl5R3ZPNzZZeTZjTHZoeU5zWVpURmdpSVdPZ3IzMFlLV0tfNEhZMmt6eWpFM1hpY1F3TVFfYzNqaHIzYUdWOWNQSHFXRFVLY0lWNmduX2F4MkxlZk1qTWc4VXpLeW5jUVdTRVp0cXlVbHRHcy1sSi1ORms?oc=5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 1 - ArchDaily</t>
+          <t>Preço do enxofre importado pelo Brasil entre 2020 e junho de 2026 - Farmnews</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>16/07/2026 02:55</t>
+          <t>16/07/2026 09:14</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQOWo3UnlLclN0X1FmSmlMSHFyR01tdERWeFhhcUZyTUZYTFhqaUFUZUszQkNLbVdlUC1nMF9IYy1PMkk5cmRlaFFoVDFPVTdrWUItekFIbkc1dnNMejdJZjdxckRtVGlPajJ0bGRuY09xZWNUZzZISXk0cG5GS2NPaUU4c201VlZGWGIzRm16ZHRzLU1vOXNfNFMyczVNMF93aWh4UGs4c2VtMElWYV9qU0JXcUpsdVhNdkctWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQNXZMb055LVlJVzBzMmRkX2xrNUNpZHREU0NjUGUxR2wtNmU1a3RNaEZNdzVMd2lzaDUwMDNjanpZbjVLck9wX2RmdFk0UnNvWGJtdjFLcEtrUVdjNm14MXR1N1U0RWdyUTNjNWsySm5DUjBnWHFXUWJxNGloMmlmbkpRQWlCbW9RLTRzSkdxcGxUZjJCVTBfVldOV0xOQllmTGVrMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 7 - ArchDaily</t>
+          <t>Galeria de Revestimiento porcelánico estilo piedra - Limestone - 1 - ArchDaily</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>16/07/2026 00:44</t>
+          <t>16/07/2026 02:55</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQM3Zqano5SnRnSU8yODRfZS14UlFkZWpRVGpXUnNjeUVsRGhIWjIwWkdGa3BNNlo1UkZfOW00QUJjQVFWWUl5ZFQybzhMM0gwM2pzZ0t1M3pidXZaOVlsdWpjd3huRW9NUnN2bDRuLVBCdWJxSHpURzJINk12VUpKOWk0ME1hVjdHSnNVS1NwbUJrcTBwZlo5VjlBUWVlN053NjUwckdsNXBRdkZTZGNSVnRRNEVCM1FKV052V25fOExUa1dsZ3ZKLVR3bXk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQOWo3UnlLclN0X1FmSmlMSHFyR01tdERWeFhhcUZyTUZYTFhqaUFUZUszQkNLbVdlUC1nMF9IYy1PMkk5cmRlaFFoVDFPVTdrWUItekFIbkc1dnNMejdJZjdxckRtVGlPajJ0bGRuY09xZWNUZzZISXk0cG5GS2NPaUU4c201VlZGWGIzRm16ZHRzLU1vOXNfNFMyczVNMF93aWh4UGs4c2VtMElWYV9qU0JXcUpsdVhNdkctWQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -1986,17 +1986,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 19 - ArchDaily</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 7 - ArchDaily</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>15/07/2026 22:06</t>
+          <t>16/07/2026 00:44</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPbnk4bW9hMFVROEt4bTA4SFhmSDdTa3EtZDhVeXZxTUJJYXI4d2NhODAzYnZycTA0Y0Fxa1VKVzhScXUzRkJjdFBFMF9nYjYwTFFGOUZ5VzZrMHh6S0p3UTJMZXNiSVRBYy1xTTBLSUZKYXZiXzc1NE9Wc3RtMW1VQzdNY0hFU1RCNXhpUE43VGtDekVxQUI4UlJ0bHEyOWJfN1U2Y2VWeU5GWnZ5MFpyYmdzRmtmTXhNYTlYb2tubHFkNUQwanBMbXhzZlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQM3Zqano5SnRnSU8yODRfZS14UlFkZWpRVGpXUnNjeUVsRGhIWjIwWkdGa3BNNlo1UkZfOW00QUJjQVFWWUl5ZFQybzhMM0gwM2pzZ0t1M3pidXZaOVlsdWpjd3huRW9NUnN2bDRuLVBCdWJxSHpURzJINk12VUpKOWk0ME1hVjdHSnNVS1NwbUJrcTBwZlo5VjlBUWVlN053NjUwckdsNXBRdkZTZGNSVnRRNEVCM1FKV052V25fOExUa1dsZ3ZKLVR3bXk?oc=5</t>
         </is>
       </c>
     </row>
@@ -2008,61 +2008,61 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 20 - ArchDaily</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 19 - ArchDaily</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>15/07/2026 20:54</t>
+          <t>15/07/2026 22:06</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQTWJPNkZHRHlkVEZOdF81VTRuWlkwMnZ0M0ZVaUhiLVRoYUlCbTlHX3dIYk9YYlpwZ0RUMEJZVE8zYnVGSk1qRUx1bzJvWU5fMDJIc0VMQlh5RC1nWjA0QTlzMVJxMi10MVJHZWpfakd6bHpfbEFOb0ptQmRxN2tDc0ZRdUZiLUZCa1dGSmNpUEtXNUxENmEwaGtWUlc2Y1AtbThTbWFsR09SMlFCcG5zaWRxQkl4aFZFa210Nl9CR3dKdW50RlN1TVdlak4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPbnk4bW9hMFVROEt4bTA4SFhmSDdTa3EtZDhVeXZxTUJJYXI4d2NhODAzYnZycTA0Y0Fxa1VKVzhScXUzRkJjdFBFMF9nYjYwTFFGOUZ5VzZrMHh6S0p3UTJMZXNiSVRBYy1xTTBLSUZKYXZiXzc1NE9Wc3RtMW1VQzdNY0hFU1RCNXhpUE43VGtDekVxQUI4UlJ0bHEyOWJfN1U2Y2VWeU5GWnZ5MFpyYmdzRmtmTXhNYTlYb2tubHFkNUQwanBMbXhzZlE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - URB News</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 20 - ArchDaily</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>15/07/2026 20:03</t>
+          <t>15/07/2026 20:54</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdDlVYVNNb1BPck5nYjJxM3pZaEttdlotN25QZkhOelo3S1k0MV9tWXpSXzJxYnNvOUhuTFl4SVZaSHFwTUZBLVM2a3haZ2N0djA4ajJMLUxkUTloM0hMaGJac0l5RGNfaTVxVkM4ejcwT3J3TmdFeTZkYnJyZDc3OGp6Vl90Zi00VEJPQlJYZWQybVc5YVU0MlFUMDdBWVUtZFVieE9ucUppSnVpUktKM1p0VnpNYno5UnFaY2hhVGZqZmZoU3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQTWJPNkZHRHlkVEZOdF81VTRuWlkwMnZ0M0ZVaUhiLVRoYUlCbTlHX3dIYk9YYlpwZ0RUMEJZVE8zYnVGSk1qRUx1bzJvWU5fMDJIc0VMQlh5RC1nWjA0QTlzMVJxMi10MVJHZWpfakd6bHpfbEFOb0ptQmRxN2tDc0ZRdUZiLUZCa1dGSmNpUEtXNUxENmEwaGtWUlc2Y1AtbThTbWFsR09SMlFCcG5zaWRxQkl4aFZFa210Nl9CR3dKdW50RlN1TVdlak4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 14 - ArchDaily</t>
+          <t>“Sinto cheiro de enxofre vindo do futuro dela”, dispara Luana Piovani em novo ataque a Virginia - URB News</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>15/07/2026 18:48</t>
+          <t>15/07/2026 20:03</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbDdfWU9IMS1UdzZUVGdMNU16U0kySE1CYnpEVlh5S3l6dE1IMWFCcWktcXBjTThXSkpUYlRuT21XYmlkb19falAwSGtrcHBmN01yWGFWX3NmMjNRd1VvWkFnSVRGWUEzZFRfRlJCTHlyM0N4OFJBbmRoY3c2RTQ1WENsNHlLUFpyN3lRdDdkYXo1d3V2b2hoWGstUW5oWFVTX2dDOGRUUktib2Y3WmNNTTBhRENMVmtzc1I0XzlvY2VFdERMUkI1cXNfQ1Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPdDlVYVNNb1BPck5nYjJxM3pZaEttdlotN25QZkhOelo3S1k0MV9tWXpSXzJxYnNvOUhuTFl4SVZaSHFwTUZBLVM2a3haZ2N0djA4ajJMLUxkUTloM0hMaGJac0l5RGNfaTVxVkM4ejcwT3J3TmdFeTZkYnJyZDc3OGp6Vl90Zi00VEJPQlJYZWQybVc5YVU0MlFUMDdBWVUtZFVieE9ucUppSnVpUktKM1p0VnpNYno5UnFaY2hhVGZqZmZoU3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -2074,17 +2074,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 11 - ArchDaily</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 14 - ArchDaily</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>15/07/2026 18:18</t>
+          <t>15/07/2026 18:48</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPY1B1d0FYTmlyX2RWaGxDS0FhTnoyR3hhd1Y3ZWtUOWxpYngxNDF5azExVnREVlRTUnlvQ0VCdWJfODRrX2pBbVZGZzZQTHF1elVLc08tamRzSWFIS1JxVUZuQzkxSU1xa1FFM1oxY3VJYm11Tmg5UFVaZmZacS1vQUJXdEFaelZhdllOQzY0Z08zZ0RPY3RTcjJBM1FfV2ZRRzBVamUyS3BLZHVld09NeHMzZ3VsWVBVcmlmX2o4UU82VUtDRXdnN3VGV2k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbDdfWU9IMS1UdzZUVGdMNU16U0kySE1CYnpEVlh5S3l6dE1IMWFCcWktcXBjTThXSkpUYlRuT21XYmlkb19falAwSGtrcHBmN01yWGFWX3NmMjNRd1VvWkFnSVRGWUEzZFRfRlJCTHlyM0N4OFJBbmRoY3c2RTQ1WENsNHlLUFpyN3lRdDdkYXo1d3V2b2hoWGstUW5oWFVTX2dDOGRUUktib2Y3WmNNTTBhRENMVmtzc1I0XzlvY2VFdERMUkI1cXNfQ1Q?oc=5</t>
         </is>
       </c>
     </row>
@@ -2096,17 +2096,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 27 - ArchDaily</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 11 - ArchDaily</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>15/07/2026 16:24</t>
+          <t>15/07/2026 18:18</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQLUxPaFB5N3dKa0FIdzJqRkFPNnBBd25fZTh6UDhOb1N5MTVfTm1nOHU2Rlp4RlByTHhHcUVRTlB6dXItNktNSGlFVmNxX0JFRGhscDNxNFdPZUM2ak5FREJteU83M2hPRFBxekE4bmIwdGRXX2pXeThUU1ZCTUk5NXROZHR0TXBhUTNLaHRuc2t2ZkhTaHFWbGUyZnZnbU1aeUdPaFBBcWFwMzcyMVZrakFnY2pyZ0ctR0tBWWJHbDZrWUxTbVFmTG1uOExPbU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPY1B1d0FYTmlyX2RWaGxDS0FhTnoyR3hhd1Y3ZWtUOWxpYngxNDF5azExVnREVlRTUnlvQ0VCdWJfODRrX2pBbVZGZzZQTHF1elVLc08tamRzSWFIS1JxVUZuQzkxSU1xa1FFM1oxY3VJYm11Tmg5UFVaZmZacS1vQUJXdEFaelZhdllOQzY0Z08zZ0RPY3RTcjJBM1FfV2ZRRzBVamUyS3BLZHVld09NeHMzZ3VsWVBVcmlmX2o4UU82VUtDRXdnN3VGV2k?oc=5</t>
         </is>
       </c>
     </row>
@@ -2118,39 +2118,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 16 - ArchDaily</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 27 - ArchDaily</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>15/07/2026 16:17</t>
+          <t>15/07/2026 16:24</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZjZ6dUlTSmRrZmk1TWlfWmNPV0x1bUdsakZuRmZyYzJ1VFBCU2JKczNSeGNEOTgwcXRtdnV6WVNGZExGdUozbVlUYnhkX0Y2WWFpNE4wcDVHLWhydkZ4allYZW0zRG5Yeko1TnFYa3ZodkkzaXo2Vl9vZzVzeVFKeDNKanBWREl0NTZLSGFNd1FoMFdwc0VNNEF6V01uQ2F3dDJuOGswZlY1SWFQNzVmb0dmSEVfcmUwMGwxM20zOWZDWnpxeUZ1NF9xS3U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQLUxPaFB5N3dKa0FIdzJqRkFPNnBBd25fZTh6UDhOb1N5MTVfTm1nOHU2Rlp4RlByTHhHcUVRTlB6dXItNktNSGlFVmNxX0JFRGhscDNxNFdPZUM2ak5FREJteU83M2hPRFBxekE4bmIwdGRXX2pXeThUU1ZCTUk5NXROZHR0TXBhUTNLaHRuc2t2ZkhTaHFWbGUyZnZnbU1aeUdPaFBBcWFwMzcyMVZrakFnY2pyZ0ctR0tBWWJHbDZrWUxTbVFmTG1uOExPbU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
+          <t>Galeria de Casa Panorama / Mosaic Design Inc. - 16 - ArchDaily</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>15/07/2026 16:02</t>
+          <t>15/07/2026 16:17</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZjZ6dUlTSmRrZmk1TWlfWmNPV0x1bUdsakZuRmZyYzJ1VFBCU2JKczNSeGNEOTgwcXRtdnV6WVNGZExGdUozbVlUYnhkX0Y2WWFpNE4wcDVHLWhydkZ4allYZW0zRG5Yeko1TnFYa3ZodkkzaXo2Vl9vZzVzeVFKeDNKanBWREl0NTZLSGFNd1FoMFdwc0VNNEF6V01uQ2F3dDJuOGswZlY1SWFQNzVmb0dmSEVfcmUwMGwxM20zOWZDWnpxeUZ1NF9xS3U?oc=5</t>
         </is>
       </c>
     </row>
@@ -2162,39 +2162,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Planalto inicia entrega de 286 toneladas de calcário para produtores rurais - O Alto Uruguai</t>
+          <t>Inscrições abertas para programa de transporte de calcário - Prefeitura de São José dos Campos</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>15/07/2026 15:16</t>
+          <t>15/07/2026 16:02</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYWpqVlRKZGxfN2NhRUZHN0pjRzlkc3FqcEVEczlGeGhoT25iVVphQ3p0bE9vdEhiNy1pbzVqWFMyYWdGbUJhNDJzUkJ6MEdfMlU5elJGQlU0XzJXQUVpUVJSdFVmZ3Q4ZTdEZWhuWUNMUnZPdU1zSkpHT1EwdkEzYTBnX2IzMnQxTjAtSDMtS3pQd1JJbEJKbUo2LUgxXzBKOURmTWJGUWtTcnkwamdFbDJWZ2xSVTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQTUp6cUdvLVg1dzUwM09XdVNwdjBXZjZsQ19EWk9iWlFPWHNyclc2SDJXbW4teFRqcGFQN2tRVXBuOFZjMDYwUE9wRldmdzlVclozN1cydWdnTjJQQnRTaEJielBIa3ZJNFZrWERtRHpoR25JWnliSXRmeUZ1YnN1WlpHemhhWENnZVVlYlc5RkhaV0JLSVhGZ29UR0FjRVdWRUx4bUQ4ZE43NFRr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Quarta-feira 15 de Julho de 2026 - RRMAIS</t>
+          <t>Planalto inicia entrega de 286 toneladas de calcário para produtores rurais - O Alto Uruguai</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>15/07/2026 10:39</t>
+          <t>15/07/2026 15:16</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQUnpUTzJYa20zSHBoS2N1bzQ0blV0N01kcmVhRldRSzdTNFo1S0FtNndGZUFPQklINDdsenFpVmtscm53X0dqRjNtdlI0VldyM21iQUtDb1VYRE9DdVhlSFhTVVZ4MF94bW9yNHVnay02RmZ6ZTlidE9ta0hZOEtfdldCb3p5MTJQcWJaWFNVMGozX0J1RVY1ODJXdzBoaERiRDZSZUFZUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOYWpqVlRKZGxfN2NhRUZHN0pjRzlkc3FqcEVEczlGeGhoT25iVVphQ3p0bE9vdEhiNy1pbzVqWFMyYWdGbUJhNDJzUkJ6MEdfMlU5elJGQlU0XzJXQUVpUVJSdFVmZ3Q4ZTdEZWhuWUNMUnZPdU1zSkpHT1EwdkEzYTBnX2IzMnQxTjAtSDMtS3pQd1JJbEJKbUo2LUgxXzBKOURmTWJGUWtTcnkwamdFbDJWZ2xSVTg?oc=5</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e233b734cabaee823cb4f045c9e&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a62637111bb4415a383110696fcab4c&amp;url=https%3a%2f%2fcorreiodoestado.com.br%2fcidades%2frejeito-da-industria-de-celulose-e-testado-como-fertilizante-agricola%2f469582%2f&amp;c=4497034278206266286&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
+          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2678,19 +2678,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fabricante de fertilizantes Mosaic reduz produção no Brasil por impactos da guerra no Irã - Folha de S.Paulo</t>
+          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2700,19 +2700,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNdG53eFV5WG9kaWlMRjlEZ0d2OUM5Mm5EMDZ3UVFNX0IwNFktOVdfN1NiYmpvZHU2WEF3UjJ6RmdNcExjSkJQQm1iYmRuNHllMTVzSnNKeG5SeUhhY01uVG5EMk9yREs1WjQyNS1tSDkwQVZOUF9acWlsc3dkVG5SMGtxV1JfWGp0SWRjdG5yMklKN2lCVWhJQ3ZRWjBYRlZjaVd6MVZfYzFPbG5nR2NQaFhZWXFuZmN2QnRfRkY1MWNBR1FyZGJyS0lkY1VNU1RFUzJEbXBCcWY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Por que a transição energética ameaça o enxofre para fertilizantes - CNN Brasil</t>
+          <t>Mosaic Fertilizantes inicia hibernação em Uberaba devido a falta de enxofre - Canal Rural</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNYXc2bkZWdVRXcm9FUmpYWEx4eVRLdHRLdWZsMV9qRDdPWmlVMHBGekhCaC1fd0xDOXV0RXB5TFl2Rlk5QkJ5UUNrM3FEQ1ZWdFhFVkdaZ3FGVXVPSFpMalQ1a3ZFa2V4MUt4Zms4MkNoTGttcktMVFVVSGVSejNUQkZqWUVwSC1UdXlsYWNqY092b1l0bkVSdmlmT2RDMTdFOHNHYUtiT3lRZjIwR1pBSDJqaHVxWU9kbGZ6ekJFeGNCZzNyN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOV3NNYmk3Z2wtOE5EbW1waDVvbU1Wem1BWU1RcVc1SDNFN1FsZkZXcFFmMkxVYzh0Uml6dlJBcVBmdk9wbDI0cTVEU0lEbWNRc0hnYkZvRFdaYS1rXzFVWDBYRkZmLTA0bldYdERnQ3BRazJFNzdOYUVFZ3M3RFlHbE00YkNydXFaN1ljSEVlelNxMlFzQ0c5N3dqVGxBb095a1pLSGkwa1NZX2trQUJuZFJjMA?oc=5</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Desenvolvido ao longo de quase duas décadas num laboratório, o concreto "vivo" com bactérias que fabricam calcário e fecham sozinhas as próprias rachaduras já chegou a áreas do aeroporto de Schiphol e a um estacionamento de 12.000 m² na Holanda - CPG Click Petróleo e Gás</t>
+          <t>Um helicóptero despeja 200 toneladas de calcário por dia sobre lagos da Suécia, faz 162 carregamentos em uma única jornada e tenta neutralizar a chuva ácida que alterou a química da água durante décadas - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxONFI3b2x4REx2NFFYMm5rQTdWTl9YU1JsS1VGa0w0azdsczVXQzdaSHBWbHNXeXpNS1ZtUVlRU1VUUWtSR3ZLc2hhMWdjbklURTk4Q0JycEJpU1l6ZGtNVldqWUV0Q0lzd1pNdGZVNmlhUE84dmhtOTEyRHFLVFRoUnRmaHNYRHZMVzQySG1tQl9UaU1kOUFvS2N5NmZSU0lvNUdPNjBjanF1a2RQVE4wSUdRSVFUY0ZfbnZQT291R0xrX2ZtOWhHaVlNcnI1NVdWZ0JmM0huN0lMV0s2ZkZXLUJ3dnFHZTh1bXZTcVhzMDRFVldaQ3VSZmkyLWRXMGFiZ3p1dUh2by1uLWUyTGM4bXA2dmswVUVkazM5MGluSV9nYVhEUTYwRWF6T1JpSjhKbHFIYXpQVS1Sc0lDSWc5VVNKNjhIS0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxPMHBUZUlrOVNEWUdWdW85U1h6YVExN3F4UGhUMDFfaXk1RmRDZ1I2Z3BkaXVwVkNrSzVTdGFvMFNhVk12b3VJajRhRlAwYTJ0QVZPRnI0MTFQeFdybDdBVkFnLUhkS19Oei0yRTJ6bWpxVS0zRUU0Slp3QnZzZG5tZjNJSm9DN25FMTJoTEN2U01oQllxc3MyX1RneGJRVElVeGgxQm9nMHRhVFYzOUlIRDhKcUF5YzJ2dGdQZ0tzR0ZYcUxmUXdsVTFKS3A4RXBvYkczSHV0Zk5ZNW5pbmtLeFpFYTVJeDhzN0JHeHRSQ2hsSk1TZ2JubFVUT0NfN3pTSG40SU85WF9VMEJTYmt5bHdNWW9jTlpHeWhQdzRITUtXV3ltSFoycmttVXRsMGtnSTNTMTEza3E2WXlhUkhtY2dnbzhDUkE?oc=5</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Um helicóptero despeja 200 toneladas de calcário por dia sobre lagos da Suécia, faz 162 carregamentos em uma única jornada e tenta neutralizar a chuva ácida que alterou a química da água durante décadas - CPG Click Petróleo e Gás</t>
+          <t>Desenvolvido ao longo de quase duas décadas num laboratório, o concreto "vivo" com bactérias que fabricam calcário e fecham sozinhas as próprias rachaduras já chegou a áreas do aeroporto de Schiphol e a um estacionamento de 12.000 m² na Holanda - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxPMHBUZUlrOVNEWUdWdW85U1h6YVExN3F4UGhUMDFfaXk1RmRDZ1I2Z3BkaXVwVkNrSzVTdGFvMFNhVk12b3VJajRhRlAwYTJ0QVZPRnI0MTFQeFdybDdBVkFnLUhkS19Oei0yRTJ6bWpxVS0zRUU0Slp3QnZzZG5tZjNJSm9DN25FMTJoTEN2U01oQllxc3MyX1RneGJRVElVeGgxQm9nMHRhVFYzOUlIRDhKcUF5YzJ2dGdQZ0tzR0ZYcUxmUXdsVTFKS3A4RXBvYkczSHV0Zk5ZNW5pbmtLeFpFYTVJeDhzN0JHeHRSQ2hsSk1TZ2JubFVUT0NfN3pTSG40SU85WF9VMEJTYmt5bHdNWW9jTlpHeWhQdzRITUtXV3ltSFoycmttVXRsMGtnSTNTMTEza3E2WXlhUkhtY2dnbzhDUkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxONFI3b2x4REx2NFFYMm5rQTdWTl9YU1JsS1VGa0w0azdsczVXQzdaSHBWbHNXeXpNS1ZtUVlRU1VUUWtSR3ZLc2hhMWdjbklURTk4Q0JycEJpU1l6ZGtNVldqWUV0Q0lzd1pNdGZVNmlhUE84dmhtOTEyRHFLVFRoUnRmaHNYRHZMVzQySG1tQl9UaU1kOUFvS2N5NmZSU0lvNUdPNjBjanF1a2RQVE4wSUdRSVFUY0ZfbnZQT291R0xrX2ZtOWhHaVlNcnI1NVdWZ0JmM0huN0lMV0s2ZkZXLUJ3dnFHZTh1bXZTcVhzMDRFVldaQ3VSZmkyLWRXMGFiZ3p1dUh2by1uLWUyTGM4bXA2dmswVUVkazM5MGluSV9nYVhEUTYwRWF6T1JpSjhKbHFIYXpQVS1Sc0lDSWc5VVNKNjhIS0U?oc=5</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
+          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
+          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Alta do enxofre impacta produção de fertilizantes e Mosaic anuncia hibernação da unidade em Uberaba - G1</t>
+          <t>Para evitar demissões na Mosaic, Prefeitura de Uberaba sinaliza redução de impostos - G1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNdjlTZE83dWZYdURPNTFzRWhqdVpEUmdWQ1ZuZHlQakpNWno4RllBdm5nZWVWSkdONE0tRjF1WVVTdmV3aTFheFlTUWZlQVpjZnFNZnFycjRLRGxjdEFaS2I1YzBHYnJVQlQ2bUVlOFB1a1Q0aERCbUlTZ1kwU0hOdFZlb0R0NVJ6R2ZfczlCUl8tWW0wcVZEdldjYTBQZ3h6ZVdSeWZJMzBkZnZ6cUNEOU9EX0pJV1ZDcFd6SUw5eTNmTnNoWG56dnFTeUJUSHNCZXlyVnVULWs2RF9LeWJUblk0QlkxcDA5dERwMGlfQUZLNW1mNTUtTWN30gGIAkFVX3lxTE1KSHdXV3lzVzM3YXlzaGJYM3p3c2lCMW5zVDd4YTVjU0x0d3pJakNiUVQzQ1FpUmx4MXM2YkFaSXowZ0Z4UlBHV0dMTklQb2s0MHFuMEVQRGZLN0JLa0lZS3hVTnRwUXloQ2RSQjlQZl9GM21xd2ZfTDRUQXh2VS1nLUNaMWJ0QnFfVHl4UUxzdWVZVjBBNThNeVR1Z29ycjhKTF9Vakx0aWxKWEVGaE5uWUZvNnlzNDkwdXBkNmxSbXU0eGd3Q0ktY1ZjdTBUTXlMUkdUYlRob19aREJvd2dfQ25VMVRWNXF1c2ZscjEwQ1RzQ196dEZGZUxOUWlMbi1LdTJkUU8ybw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOWTREUFFrb3B2UGF1dWRjQmhXM3lTdFJEX0JyRUhPSWp5R3ZicTk2YWh1YnBwbXpTbnpRSnZ6cUQ3aUx1LVU4b0dub1E2WkFfUnlHZzNmTG1VSkNVYVYzci0tbzRuX2hxSmpRRXlvYzlUcVAwSFdKbXVTOVlqSjlvcGllMVA0YWF0QlhnV2xKYmkyU1FxSlFoam5vcFVFQWZSekhqOFUtc0RNZXJ3eUlmS1VMY0J0cmxXbHlZczZWTjFfNmswMGh3VXRpMXJ6a0RYekhnZFZmUmlKTFl0RHBQUUdzRdIB8gFBVV95cUxNT1QwMkdFYWF6R1V3NHpfSVBHZFFDbHNhTzVOQkFSMmkweGxLaldvZXhOY0I5SkFObWJCcWlmN1FZdk9zOHVwMVZIck5oZHJEb2pRakltU01QS2prLWZublBLekVpNGtHY1JHNlhObHRlelRBM0ZGaTNwTkFZaUNFMTZBNkV1SEZSOWMzRndwd3h5ZGZhdWprczhBOXNlbF9NMlBsV0tEdVFQUXhnT1BMdjdCbnVKY3BWdzVUeDdWLV9HTDZGeVFMd3h1OS1jTWlIMnROQlc5VnRFUmE2VnpXVXJ3Vl9QSGZZTVNhdkFVZE9NZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Crise da Mosaic mobiliza autoridades e acende alerta sobre empregos e economia de Uberaba - JM Online</t>
+          <t>Fertilizantes: Mosaic avalia alternativas contra restrições na oferta de enxofre - Money Times</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxObTBDYTQzZm1LS01jMnNkVzAwUnN1UFowRXlROEQ5SlNxcm5hQjRRemNhWXhOTTVoT0N4NG8zN1BiYjF2QXdDUkcwdGVwby1CcEJxTTI5R2VfWlZCX2ZEMmlQUkdHZVNOZk9Lb3pHb193M1pMZ3ZsdW5OTExiQ3k3bC1mN1U0X3lQOXFnMDJwWU5zTEJFTFpyTE1Nb0xvWnNMNklNa1hvRkNvUlZpYzhURGlYTWpBMTJCRnNYc3QzYWFPNV9GWFZuUEwwa2RtbGwwVWg4MjZwb1BQUdIB4gFBVV95cUxPM3Bnd3VXQnlxUzJVNXY1U0VKdVFrT3N1Z0ZUQVdPWEQtODM1TjJ3UnY0UzBMUHJhc050SWFQQlNvU2pRX0kxUEpOWndKWE4zN0d4TWxyTHhsbV9YdkFyWGV1anJrTzRoM1BwSS00eDgwWTVqNE8wNjA2UWh1NmFidUt5V3hFOVNFZkZ2LTV4Z0pKWE5ZMEJLcHZWVEU2YTJ3eDJMSDNwMzhEelhTWURKSUNxdUhaNTdfNDR3cEg2d1hWNjA5VVV6bUcwOEtpbU9uTmZEVGFHRnZUcl9RcWZzZlhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPQ1FzejVNV0p1cUcyYmFqaDdjYUVULVh5Unhta29iWVhpRXFXUU9XX2VHU29NYkloeXpwR2pMb1FaalBfWWhmVGhHNUxfSHRQZ3NFaU1TRlh5Sl9zcHI0TUxjUlZOc0VwOVZhWXRpdFFhLWFoa3Jhek81M2U0VEZYMk5Hc0xLMTVkNy1wc1NMRjRfeXBWUWtVaW43bWwtZUROUTBwTE9OMGhQUXlza0FJN1BmOHluUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3103,22 +3103,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pare de jogar as cinzas no lixo: saiba como usar esse pó como um reforço natural para suas plantas e canteiros</t>
+          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>09/07/2026 06:15</t>
+          <t>09/07/2026 04:00</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e233b734cabaee823cb4f045c9e&amp;url=https%3a%2f%2fwww.em.com.br%2femfoco%2f2026%2f07%2f09%2fpare-de-jogar-as-cinzas-no-lixo-saiba-como-usar-esse-po-como-um-reforco-natural-para-suas-plantas-e-canteiros%2f&amp;c=3336525689791670118&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3196,105 +3196,105 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sem enxofre por Ormuz, Mosaic fecha fábrica de fertilizantes na Bahia e demite 30 - Movimento Econômico</t>
+          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>09/07/2026 04:00</t>
+          <t>08/07/2026 20:25</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRnJPcG92M29uVXBLdEU4dHBWUHU5TE5wMlI5Q2xGNkd0Y01HR0ptejQ0MjJteEFXUERMWlEwTTRUbnZJaE1OYU1USVVMeVVobXFkNk13WGVlRzNoZVQ1WG13LXFJVjBQODdrTDJuNWdROEJIOTF3Ykp5SXBjTFBiUEJqdTFrX2htRzBTa1JaMnY5LUU2WkstS0RMblk3OFVaSmJqVmVDOGVJaUJWSDJyQ3VySXdNSFNKUVkxZGwzTXM5b2hHV0hUM0wxV3hWOEE4eTJiVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mosaic reduz temporariamente operações com fosfato no Brasil devido a restrições de enxofre - Notícias Agrícolas</t>
+          <t>CESB registra maior produtividade de sua história: 156,13 sacas por hectare - Minuto Rural</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>08/07/2026 20:25</t>
+          <t>08/07/2026 19:57</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxQeC1fdHVhNWRCd2I4T05LeVlMV1ZRU193US0zTDRXMVl0QVpfa2VFQXktajRWUGprTUlYM0hwZWxyaFJlZTBtV2ZDdlJTVmh6QnJnMzZWUXBTWWN6azZfaTVianNDRUpzMDFoSXRnd0p5UUhTcW0xclVKcnppdFJydGlaZnViNWhqYXAyYkhTSUh3b0FNZ0QwWjZSV0I3OEJLdUhzdW1aVEZUd2lmdnFHRXJfb21oZ0g4RUR2N0xVNjM1N0NxbC1MMzlMRVoxRHluZ19HZ2NFcDR4b1p0eFM5U3pqR1dYZno1QVRkT1RaZGtiOWvSAfgBQVVfeXFMTjBtbzUxT0tUb1A4NGxyamM1THlMZGw4V2NaSjZ0TnQxZUtvbk51ZHdsYWk0WWNoald1M0lrM19HdG8wS2dBNFJLaXlLNnRybUhsVGsxOW1nWmNycWgxQldaeWZ0YWpBcEd2Qk1BRTVYNFR0SEpJWjdkRnFXRlNMdFNlT01nVDBGdnNTeVNRNFdlNjBhVkZIQVJ0dWhhaTIxVjlkOWo4RXVVMjdqQlc2bVh4S3p0dWNkQTE2a0NDMTE1Z0puOFoxZDhqOHE2eW9yOWxoLWV0eVV5MGFyVlJHWjZzcXh3MXd3Y0Y5SEFxX25GRW80cWN6VTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOSFF1Y0JFc3NmdFF4Ym8xYTdLYmxMampjbkxzalpGNHdSRE5QUTFXMnZPMkpia1pTVnBKOGtNRkNyM2VnZGlPUEphQTBvUDJZb0ZVRk51NG54OEpHUkhPMmh6MUR1UXd0VERSNmlZeVpUdGRRWFpzZloxcXI4dFZLeFNvS2FoNTBGUDRCSFhLQ1l6UE5iclZTRU9xTDFVWlRoS3lsb2gyQ0RkZDdPY1UwYkktS0dvVmN5Z193?oc=5</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CESB registra maior produtividade de sua história: 156,13 sacas por hectare - Minuto Rural</t>
+          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Prefeitura de Palmas.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>08/07/2026 19:57</t>
+          <t>08/07/2026 11:17</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOSFF1Y0JFc3NmdFF4Ym8xYTdLYmxMampjbkxzalpGNHdSRE5QUTFXMnZPMkpia1pTVnBKOGtNRkNyM2VnZGlPUEphQTBvUDJZb0ZVRk51NG54OEpHUkhPMmh6MUR1UXd0VERSNmlZeVpUdGRRWFpzZloxcXI4dFZLeFNvS2FoNTBGUDRCSFhLQ1l6UE5iclZTRU9xTDFVWlRoS3lsb2gyQ0RkZDdPY1UwYkktS0dvVmN5Z193?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNS3BUcG5OdUxkY0tHNFpTWTdHYkhwaWxVSjJKSVJiTVQzUkw4ZXQ0dTJ3UlhETGVFeDNlOVBlM20xdlVaMnMyZU1zS2VxUndPanFwYVJPc0psRENuVTlhOUh3RmxTZXFtTFVMUjMxWWRpUUF5b20yTUVYRVdpYlh4UkRGQUdIbVk1ZjVBc0VtWk51TE11d3VYQkpfVWxXWWtxS2g2c3JWNThsaHcwSFJ4aVpPMG9QcTRXVlpSLXJxWjJYNzh1NXFpTHFUcE5oOXFsQmU3bFE2RlVBc0NBLS1CMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Prefeitura inicia distribuição de calcário para fortalecer a produção da agricultura familiar em Palmas - Prefeitura de Palmas.</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>08/07/2026 11:17</t>
+          <t>08/07/2026 11:07</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxNS3BUcG5OdUxkY0tHNFpTWTdHYkhwaWxVSjJKSVJiTVQzUkw4ZXQ0dTJ3UlhETGVFeDNlOVBlM20xdlVaMnMyZU1zS2VxUndPanFwYVJPc0psRENuVTlhOUh3RmxTZXFtTFVMUjMxWWRpUUF5b20yTUVYRVdpYlh4UkRGQUdIbVk1ZjVBc0VtWk51TE11d3VYQkpfVWxXWWtxS2g2c3JWNThsaHcwSFJ4aVpPMG9QcTRXVlpSLXJxWjJYNzh1NXFpTHFUcE5oOXFsQmU3bFE2RlVBc0NBLS1CMg?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a626377261a4eedb2d81e9c56dd2079&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre</t>
+          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>08/07/2026 11:07</t>
+          <t>08/07/2026 10:03</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e297d5944eb8db46705242e9aee&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f07%2fmosaic-reduz-operacoes-no-brasil-por-escassez-de-enxofre.ghtml&amp;c=17049096324127703512&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
         </is>
       </c>
     </row>
@@ -3306,39 +3306,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Livro A Rota do Calcário será lançado em Arcos no dia 16 de julho - Jornal Correio Centro Oeste Arcos</t>
+          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - PREFEITURA MUNICIPAL DE Sorriso MT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>08/07/2026 10:03</t>
+          <t>08/07/2026 09:54</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPY09wcjM3NmFCenNKU0d2NnJpa1NMWHp0ekx6MGtwQ3FZWFFiREVyc0xNR3I4VXdtalV2VW1FVjZEOUZ5X3JyZnR0TUFtYUFYTHdxQlZTVE9hZVZOMHJ4M3RZUThpNVNHSEVuNllkV1RFcUhnMkZqbnBYck5MX0lXckFJNGtyWk45bUdVRU9oY2ZoTVNUVGxxdWtR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sorriso começa a receber mais de 1,2 mil toneladas de calcári... - PREFEITURA MUNICIPAL DE Sorriso MT</t>
+          <t>Mosaic reduz operações no Brasil por escassez de enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>08/07/2026 09:54</t>
+          <t>08/07/2026 04:00</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOX3JwQnFZQXByS2VBOVNuWG5vRjhyZ19OUE1DNml6MXlhZjdLUEZOX0d5VHpVOHRxRURNYVNYVU1ITFZXMDhfMzZuWmFKX3MyckNNYUxReVdHU0t6OVAzdFgxZjBNQnJ2T0tNSkJ6bFU4NmlDSjZHRmtyQmZScXhPaUlMZGZSZVh6V3d0OTJ4QmlXVmotN01xSFFzWGZqWklWcVA3UEs0ZHZEV2x0bE1CSG00YVZTUVg4cG1xV0NkYmJidjlvMkdTemU1TTNxdnBkcWlpOUdqY1FXVGNG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mosaic reduz operações no Brasil por escassez de enxofre - Globo Rural</t>
+          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3360,29 +3360,29 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNeURESU1tOVZJdTFPMTAtOVJ0RzVaV2dwZGI4VklqWm5qTUVLRnR5NkZUVC1GQ3lJaEg0YjJNS0JLSDVhT1JGXzZ5UDUzWGY0YXB4bmZDYmdpMlI2WkpLUG1zeVJ6VUN6VHRGbGNaMWd2aU9kQkJlbFhTd2kxZGlRMFZMWDZhWjNkeVNoam9Ya053dzhjeGFETWJySEhadVpkUFN3TjAya2dXNTVIeFJvZ0ZVc1dIZ9IBxAFBVV95cUxQcnRNVFl3amU0YlA0UU82NnRxOVo3c2Q0MkxIdGtLN0JvZ0pGLUtMTmxSME5VTjBZWkJ0UmZvU3ZCWVJwM29iWnN5RWtwb3ZFWGFraVRpLWlWWnJCWndRemlKdnBaQ2J6eG96RjZ0dEdWbzBFUXlzT1gweTQwWGtrRGhRSjVwejFXY0NxY1dsSUZ0S2k4aHc1TG1fN2hLZFdNb3R5MjlGeUxibEctMU9yenF2UFplUHlDdlNOdko0cWhCb1BP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Gaúcha LW mira R$ 600 milhões em contratos erguendo estruturas para empresas como Yara e Mosaic - AgFeed</t>
+          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>08/07/2026 04:00</t>
+          <t>07/07/2026 04:00</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOcFlMVVRvZTZBbXpHWUJZeDFMYmRLeVU2TV8xT3VySk5DWTlwNk01R0hpRVVTdmI4SU1fQlY2RC16WVFnb1VmZUI1dTBlenFLVGc2VnlYQ3JuZ0xLTnhrQlZuNXdSWXpNS2dERnI2SjBZNW0zTnhoRkxuWXpZM2hMTE5CaVlwcU5FNDlTVloybWVPWTAyTUN1Q0ZyLVgxSkl0ZWZNeFMxVm1aWWhNRlQ5QWFWdWt6eWFWUUdTdXg3NThLUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3411,44 +3411,44 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Produtores jogam na defesa e importações de fertilizantes caem, com mercado dividido entre ureia mais barata e fosfatados pressionados - AgFeed</t>
+          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>07/07/2026 04:00</t>
+          <t>06/07/2026 10:47</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxNc0FzbEtWeHBoSTVGSTJOczhoSDdpbFZLSlQ1TG5ucklJTXVFT2ZkS3MwTVh3ajBFUkx0aF9FT2Nmek43REZMTXIwUEVJbTEwLWhyRFRsaVhJNGlqRlNmWTU1QVV1bGZFeVRKVlFyVWRQd3RTdTl1S0ZMYjA1WHpnVUtpREdQaVd4RTlmdFFmdjZjaGhoQTFDYmVRWFlEbjdwTlVLUnVyeS16SzY0bDJ1c3BpWlg4N2RpSGM5OENucS1rZEhNaVk0ajQtcVJLWTlXRDJsUVZ3ZmJ0MXZQRFNRSWNMVDRJNTdoRkZMalgwbzllRFdhM1l0Vw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Enxofre ganha espaço no manejo das lavouras - Agrolink</t>
+          <t>Importações de ureia recuam 32% no semestre - Agrolink</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>06/07/2026 10:47</t>
+          <t>06/07/2026 04:00</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNRVJxOGlMRVRqcWk4R0VXOUtaSHJ2VHN5T1VpVHp6UDBQdlV2Y2ZMWnFCX0Roa2NlSjUtWThaVEJ3WkVsUERlNlNZS0FmeHYwSXRKRVhqMEh5MGxnYWVBVnNIZTdjNFE3SlBzWVdzcTMyTnNnS3pfc1ZMb1BWbmk2QTFFdHFnUkYyTXZjUDZsMjNPOFZjaFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNT0NWVXVuUHBIWmI4SlpmRGZ1Ujk5ek9GRjNHSkcxb2EwY1Y2ZGhPOFJnd1FLSi1yc21tZTFvTUwyWnZ1b0JhNlEyTDh3UFdOdnR2UjU4WDU3STR5eGx2OGMxTUZRUlkxVU9FdW03czY3X01WaWZLLUQ2QkNLVDU0cVFvTVBIeUMtZkVGaS1sN01wQ2pKRHBv?oc=5</t>
         </is>
       </c>
     </row>
@@ -3460,39 +3460,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Importações de ureia recuam 32% no semestre - Agrolink</t>
+          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - Agrolink</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>06/07/2026 04:00</t>
+          <t>04/07/2026 01:00</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNT0NWVXVuUHBIWmI4SlpmRGZ1Ujk5ek9GRjNHSkcxb2EwY1Y2ZGhPOFJnd1FLSi1yc21tZTFvTUwyWnZ1b0JhNlEyTDh3UFdOdnR2UjU4WDU3STR5eGx2OGMxTUZRUlkxVU9FdW03czY3X01WaWZLLUQ2QkNLVDU0cVFvTVBIeUMtZkVGaS1sN01wQ2pKRHBv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Fertilizantes subiram mais que a inflação desde 2016; ureia ainda custa 149% a mais em termos reais - Agrolink</t>
+          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>04/07/2026 01:00</t>
+          <t>03/07/2026 04:00</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOTEZVZTZETDBfN3VETnZRZ1lwamFoV1dlYzJCS3NSQlZaaHdMbXZyM0xUT2JKRWZId3Z3ZDc4VlJjc0s0VDJ5M1hTMnJYclpYZDlEZmxrQVhPXzR3UDBUSkxLc0xGU1lPcWQ2UDROZllLMzdlNHhGTG5RNGtDVGJTbVRPR3BWcGw1YlpvdXVTYnVrSXMzaGE1d1Z1a0dGcWJUSWZqTFUxRERITWVSQUU1eWhTTFBCaFlLa0NFWHFvUDROVnJQbjRyVU1wS25KNmdyX0psZ3lGeW92TTBYYlYzUlVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3521,88 +3521,88 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Metabase fortalece diálogo com trabalhadores da CMOC durante assembleia em Catalão - Badiinho</t>
+          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>03/07/2026 04:00</t>
+          <t>02/07/2026 04:00</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE05NmE4R0M4U3hSUG1Kb2J4dDh3SXlBTjgxeEZ1WUVDU3ZwQ0dORnRBM0FGUUVMZGtYU2cwOUFSYVdub05DTGFuSTg5TUNma2hVMTgtSjRmSWFTQWdoc3VtMVk4TnY1b09aTEhlR1BKT0Q2VGJySVVqaHFVRdIBgAFBVV95cUxOQ2o0VWttOHg1N0NJUDI0TnRERWExay00T2RSRlZhTXl5M0pvTnNzNVdsNzllaDJPenJwQkZRR1I1SURodjFrbnRjbHZaM0NQQ3FXc21ObjlOa1pUZER1ZjdrcGhpQl9YTFBoTjFsUnhIQnczeWJwbVBCNy1FUVZGLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Grupo argentino avalia fábrica de ureia com foco no Brasil - Valor Econômico</t>
+          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>02/07/2026 04:00</t>
+          <t>01/07/2026 10:48</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQYVhPc3NrMDdqN0l0SktKdE03UkVXMXV6cGpTM3ZRSm04a2lMLTRFUGpoRUd4ZF9uekIzRnBlcVlvS1JBM0ZpbW9OVEZEWHA0MFliT3hFVUU2UTg0amZvWVNXX1dVOFFNOGZCTlIxT002RlhuS2MzWXZjaENwV0g4bjQ4Mll3RGdnMEdGTjhITjNyQnJDeGpfTWY2aGJxSmJ2SmJfZXprdzFSRGpZSl9mdXZHUlhVSUHSAcYBQVVfeXFMTmU1U0hwa0N3YmVjNzRrNWU2MTNfalNtQkNTeVQtTmVWX3k5R2hQU2VnRDA3NmZ2X2RKbVBTd0F2QnJSS0FGRG1tRGx5N0Q0RzVvdlpOb3FrYkI3WmUzdGxWNjdVY0Y1bmFfdmJidF9DeV84ZlFpX1hnSWcxZk9mREwyb1I0cjloeE9vZ2ZQZ3hvMlFsSUllbk5wLUR2cDF1TU12bW01bVFfQlY1UWhzQjJpc194S1dZeENMRXpCMTZxcm1YN0pR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Administração Municipal recebe novo distribuidor de calcário para fortalecer a Patrulha Agrícola - Rádio Geração</t>
+          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>01/07/2026 10:48</t>
+          <t>30/06/2026 18:22</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPUy1BS09ua2I5b2szTU1SNVFPWVZSNmFUY1UtRTlseVpQTmxJUk1XX2lvTEtoQUNVcExIdzc0SENBbThvTDQ4X0pydHlPMHJ5bHJaVG94Um4tdHRhNzl4dU1CQlZFS3I1OGtKYU5NWUVraWpmT1hyVTd2ZTZKQUxNamNVZXZSUEtTYU01VnM5MXlrNWd2UzZ5d2N3dnBQaUQ2R1RYSkJRWTR2RkVwTTcxSUxkd1E4bjkwZXd1STJwSzJHeVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Prefeitura garante calcário de graça para fortalecer a agricultura nos bairros de Navegantes - Jornal nos Bairros</t>
+          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>30/06/2026 18:22</t>
+          <t>30/06/2026 04:00</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNWVhCT0tJZHhMbEFaclNMWDVlMjdZQUozR3daYUszUUdoclltNzhBU1hXby16ZnlKVWV2Z01aaUxqVEhkbFNfTmowUEZZdVJSVUluSVM4VGIteTBuV0lpM1V2c2UxR3REZ1NmOXZiMk9QZEhxTXhwd1NRWjFCRFVzNUVicktKWWFBS3F6RGY3cFF4OVpJQnpXVnA1TFJsa0dPSUJ0ZEU4UFdqbi0xWlZPZTR0Q0w1ZGdFQ0hrUnVEUVFiemd6NEthUnUwV2pUbExla2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3614,17 +3614,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes amplia movimento de baixa com recuo da ureia, MAP e cloreto de potássio - Notícias Agrícolas</t>
+          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>30/06/2026 04:00</t>
+          <t>29/06/2026 04:00</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQcWo1blNvbFFwUzl4S0hfaW9sSklENjRLa1M4UzNSNXg5aFd0aWNQUjFhLTNmRDYxZWk1Mlp5WXdRNjZNd1RveGNDbkNsa0o5R1dRM1RTMGFpVUhHYzk3Qms5a09jOVdEX1A0cjZVWmU3SHQ1d29zbHZYeTI4MWpRS19mUFVadUpwY2NQMjJwTzZGMk9HTW82OHVzZHhtbHVQcFpseG83Z2xQUGlKb29NbkxVNHZWQ29SeTVQN01meGFlVV9ZSW9UaVU1azdIOFh6V0JhcktVVzJDblRKNGNYQTNKWnBzVGhRR25xdy1MRTZWMzdlV0J2eNIB_gFBVV95cUxOMWY5TFpKa0RFNVpidGRSdFBOeUczUDduTWxqLUpMWmg4cUxra2N6RF91bTd4MHBlMmluQXNBTE9PTi03WlFRQWNCdUU5NTZaNXV3UTVhclgtaUtva1gxYjZncmtES3V3LVFQcHpCLXoydmtXSXZwOFlfSDhYOUVmbEpETEQ2SkM4cHgyTHBBUTZxUExpTkEtYm5FTjJGLTFJSXBnQzBNNWZmd3M1N2hiRUw0OTNNVU9ra2hJRnIweXR1ZnZfN0RjM2d0c21TRTlteC1rMzA0a2Q2TnlORTFOUEJaRG03Nk1sNkVYNnhtSTJCMm5YWnZ6ZmZjRlo1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3675,22 +3675,22 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Retomada da obras da UFN-III deve suprir 15% da ureia nacional - Notícias Agrícolas</t>
+          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>29/06/2026 04:00</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQaG9vWDljNUdZd3NycVNvUGpFQVdvLUc5UUE3RV9BSTlOTF9SX29XRkR5VEprWF9XejVyUjVlQVNpT0ZuWHFCa3lRYmp4Z1Rxb3d6ZjRjU0stWThQU2FadEtzSjhlSFoxMVpiSEhEYzROOEo4WTBqSmtCeG1paGItSzEyalB3QjJXRXNnVlFiOTZRN3hnaGNzbjZYUmFCaUpLb1BBTWxpRzNnUkU3M1ZrWDBWaG1wUDlxUkFReVhmSEY1a25TMTFZR2hJa05Ncnd1ZnBR0gHYAUFVX3lxTFA3SXZoYkJzV1h5SjRvMmE3bGlVQW51cW1Kd3AzS3Y0ay1QRzhWZ095Ylg5dnBGM1pHMGE5OWdOQzhUaGN3RDNYNUhXZzAzeE5VSFhfTkotUEpaWXk1UEplNkNlVmdzenZMZWVBTVFnUFJSNWtsQmczUGhnc2lqOVNPbUYzYkxqaWxKOGp3TUhZMTRBeXdQS2hIN1RQaXhUeTNhSkNnN1NDLXQ2YTFTNGhza3A5TGMyZ3VuNHFPenR5ZVE3S1drbVZua09VNWVLbVZuamM5Z2hNaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
         </is>
       </c>
     </row>
@@ -3702,29 +3702,29 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Falta de enxofre acende alerta na indústria de fertilizantes no Brasil - Primeira Página</t>
+          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>28/06/2026 04:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNeEpidlVpTkg1WmVXMWlzMTQ3cGNIblRXMV9wX2xsOU1yZG9weml0QkdfVC0xdmNuektjM1N5eEc5Ulh0dUdmWlFfRW9kVGRSVUwwVzJOb3NiclRjeEdJY0pyd1hiVUl2aEZIZkJwbGRuSV9WeUE1NHVTQWhvNlBKcVZwa0NnRnN2V2JlYmpudHhkei1BQUVfMXRUZi1LUDJ2TFhwZC1RNXFydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
+          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
         </is>
       </c>
     </row>
@@ -3763,12 +3763,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ureia despenca após trégua no Oriente Médio - Agrolink</t>
+          <t>Justiça condena herdeira a devolver R$ 4,9 milhões a "gigante do calcário" em MT - FOLHAMAX</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPbnhnc1BFMXFtQ2VwTkVHaUtLWHlXSVAweGtSVE8xMXRBTGJyT0p5QzZzaWVrQU5PODJuMlp2elZib3Ftem1UaEotZ0FmZFZGclhtdzN5MTdyX0FIZ3dfNHk0dng3d1dLM0xlWlNkR1V5ZGoxcDlNNkNNMEZHcHJINmVnQ1R2X1luYkRxamdqTWFYSVBaVFdV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOQ0E2ZGFseTRjVFBDMmV6ZGxHTDdZektMM09pNTZuSGppV3R0eFhSM1lZcWRrSElmeS1MMEhHQWlFTnNWT3dJcDJLeVJrMlFaN2FkLUhadFd2NFhob3hpUE5YLTNZblItdS1pbDExUlZFMS0wSDV3VV9DUmxyZUllYmVXU2ZWQXprNHU0TF9IcnhsR3BySWMzWmx4MWJoclFGa2p6dmZKWGhtVkwwNTVtdW9YOTZSZDBFQmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -3790,39 +3790,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Crise dos fertilizantes: estoque baixo de enxofre ameaça a próxima safra - band.com.br</t>
+          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>25/06/2026 19:02</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQdGoxOXo2NXl5WnpUd3E1ZWQ5RldtTUR2M0F6YnljMXNxb2NVM0RrVDY3WTE5SExJYzdmbzZPYlFlOXhrUTRoZnJ2amFPR2wzNGlVd2JTNDhzYkplbHVET0pJeTh0U292YmtkT1NPb01lY1JyRDk5MG9TaTNEZHQ3ZjlJU0lXNXJJTkRWZUNFbUtUbmdPN3oxX3Z4cVJvWWdtRks4TV9VcXM3SjduOElxckFTSGpncTNJb01YUllNa0RNTmYtVm53T2lHYlJPTEV5ajVCQk1wQThIMnU5aWtHSQ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a62637925814e53946f8067a55cf1b1&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f06%2fcom-pouco-enxofre-industria-de-fertilizante-ja-teme-paralisacoes.ghtml&amp;c=5295783801695414575&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Com pouco enxofre, indústria de fertilizante já teme paralisações</t>
+          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>25/06/2026 19:02</t>
+          <t>25/06/2026 04:00</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e2b17aa4bb1aaaa6134cb188b9f&amp;url=https%3a%2f%2fgloborural.globo.com%2finsumos%2fnoticia%2f2026%2f06%2fcom-pouco-enxofre-industria-de-fertilizante-ja-teme-paralisacoes.ghtml&amp;c=5295783801695414575&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -3851,34 +3851,34 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Terremotos na Venezuela, menor importação de ureia pelo Brasil e prêmios da soja no BR em destaque - Notícias Agrícolas</t>
+          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>25/06/2026 04:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxNS0R0cnpLaTNtU3c2TXZ5bDVkMWlEazJIeHktbEE4RmFjNktPeU1wb1FtUWxmZHExMmFZaXQ3aXJJWW1qMkliSjAtYUxEc3NwclNOMnI1YTNQRnlJTko1aXN4T2M5bXpNZ1R6QTNsSTgyUmZWcU1YUEZWRlc5NS1YcXVKMjBoUzdJSUpuT01wTXFOUy12Nm80c01zcFdqSkNhMFB1Wmt2ZDA4SjFwemJiTTZrV0lxTGJsd25pUXBjcGNlM1VTTnpOemo2dXpHVV90d1Y0STFNdGdoR3ZlZzVDdWxtUTRtZHAwbnkwT1ctWF9NWEppcjRJOGZTeUktbE1wNHlN0gGIAkFVX3lxTE5zUE5IamQ0ZjNxWDNXQVpLcmZuekp1VzRTNEVVZW9yMm5NVFV4M2tTekFOc1dHLVVaQkh3ZngxZ19hdDhpbk1YcGliRkFqOVhrYlVpWWdISzFiNHBkNE5qZnZOUjhBY3FrVDhzbmtpNXBnZThtMjE0di1TS19ZZVdmZHpEVG05eFZVU2xLVHdBbFFkSUdwSzlMNzBpSzlOa1VBX1JheWRxcXJiYUN5a2Qyd1JqQno0SjhxazdsYjhXeWt0THR6eFJPa1ZjZXoxVFpqbkZGdUxMRWN3d3BsOGkwUnlkUVRQcUU3OWJnMVRTV0Y0dVRRcEVpLWhuMDhmT09OdUlxaFpxaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
+          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3888,19 +3888,19 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Inscrições para recebimento gratuito de calcário em Santa Cruz começam nesta quarta-feira - Portal Arauto</t>
+          <t>Indústria de fertilizante negocia subsídio ao enxofre para enfrentar alta de preços - AgFeed</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3910,41 +3910,41 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPaE4tUFRnbGVkVTVWT1pfRlhDZ3JHQmo3YjR6aDU0NFhXODRWVF94YXgybHgtTWZETWdfcUxOYUdzNjNYUUhVaEJZUXVGMWlHZUdrQ3pDd01pLXZLNHM1TnM3WGxnQlktaDBuVTRYWVdFV04zdDBKZEF3OVU0Q0NkcHFaRkNnbENXV29tMHRiR0FMOEVfd1BodFRidDFJM0ttNURQOF84SGV5VFFJSHR4clhxdmh1OUp0ZjFidnVjc0ZDeDJGcVQzcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxONnhnQWZIM0h0SjNPU1JoQzZoMXgzY0FmdmRZYVVCZXVvZHp3RkxVUnhyelJWa3gzUWJQM1dEQ1I3VWUzUTFyMktmVU0wMnlOLUdaV2tjZ1lkRHhIMDdUX3lKWWtLZ3Y3R1ppa3UtRDBlejJhMVIxYUwyRVU1VFVFSk5td0JWYnRIdkRSTk5YMWVnT1c3V093Mml4YjRmSllxN0JmVlhiWmN3R0VlRzJybmZRM283QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Importação de ureia no Brasil atinge menor nível em dez anos, diz Rabobank - Globo Rural</t>
+          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>23/06/2026 04:00</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPNjdCU2M2dTdMN2NKU3hKVC1jWkFPTjFBd0RDZHd0X0U3OU1sYVNhWjRWdzVtaGM5UHNTOXgtcWpzWHFWVTJoNy1oMzBvekR4NW5GbVZTX1NmYmZLTlU4d1lRaXZJZGNrUTYtSlo3cllmekJjUWV1TU1YVnNocTQ4VkZkaXRqZkstNGY1WHBVZ0pvV1ozSHlsaUtDNGJPRDNHUXBMRnZ3LUIxcGNnTWxYU21ycWt5ZEtaR0g1SmZrRl9VMmVNanQxaGxJbTPSAdsBQVVfeXFMUHhsM2xrQVJIUnpfbjFCWEFDTThmUFJOZFR2dEtGdnNwWDhRLXV1WVdxeU10YXZtd1lHMnZ4VVd1cUVzR29sY29hMENsc1FUYVN1VVIwUjcyTzlhRE10RVkydWl3NTB2MF9SOFVNbGhXUEhCd2NJSFdSeTBmc2dac1NoN0tpREYtS29tb3ZuZ0lrdmlsV0NUMUFNR1NoeXV6WFpQNmpUZ3FvRkJBdE5vNzY3MTdjdk1kb0RuTE5xU2w1b1FxR2x4YzZrd2MtekgwTzJhUHBnN3UtWjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Expectativa pelo PL da renegociação de dívidas emperra o varejo agrícola, diz Mosaic - The AgriBiz</t>
+          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNN3A0WWpXR1M2UEhQQlhXUk5GbGFhMXlFVzZtczVnSW9wYzMxeFROWEpUU2tsb2xmSTQyUFdDTS1oa1BoU01GNy14OElqaGlEVXhNSTRkczhTSmdiUEQ1TGdXMUQtMHVFWHhPa2p3cHluYnhpUWhMNHRrcXl5SFI1dGtyN0hKeFd5b3dVcHNLc2cyMkRycFRGWnJLT2NGZWlLRXNwY0N3X0FCWWJseE9xcEF4a2xncHFUb3lSb2tMUFJMWk5JOXh1Q0tQSG13MEhfVlNBb0h4OXYtWEpQNjFrS3JYQmd4aW1M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
         </is>
       </c>
     </row>
@@ -3983,56 +3983,56 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Produtores rurais podem se inscrever para receber calcário gratuito em Santa Cruz - gaz.com.br</t>
+          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>23/06/2026 04:00</t>
+          <t>22/06/2026 19:10</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVG45N0p1WG9vdGlfX3Q1YUNZWkFmYmJ2cU1DUHFGbEZqcHJkYnhSNWxtQ01PT3N4S3AxVzFnVllQcmJfZUZoZG45a2JmM2Q2RFJGazZQeWJYTlJTcTdtUm5fcl9YRFg5ZEtySDR5QzFBX2dXUThWQVJ1bXdBME4wc2d1R1o1dFIzME5DVTFCQ0daUi1JbUwtZWFFTy1VTWNMQVNHeW04dlHSAa4BQVVfeXFMTWxhNlNVMXpuVllWUDl1LXlOVV93Q3E2RHpEbWJaZEF6T1NIbHFGRTBRdy1XT05EWDloR2ZNQjJSLXJNaHhfcUNZZUsySkp2UDZyaEZPT0hwMHdXWGRMQVpYdFA0U2tYcTFzYnJjOVV3bHAwQjBmR0hZUWxiN0IzODRlWGR4Rno1bWpveDFZNk1HeENPUXFSS0VQdGpZMmpkd0FJdlNFT3I4cWNGd2Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Visconde conquista a Copa do Calcário 2026 - GF Esporte</t>
+          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>22/06/2026 19:10</t>
+          <t>22/06/2026 04:00</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPTUpHSldydzZmQ25UUEFKS29naGtpa3pOMzg0WXBHSnhuZ2ZyRlRCbF90R0hrb0ZCMVB3aWNlX21ZLUxPT0ZfRC16SUJ4cExSNjFrMk1jRXZ4c2lmZFBqaEx2cC1YSzhxYTNmZzlPVTNWZXFtMGZKZmFEU2Y1RXFxMHZueW03VVRaR0p5dEU4SFhxNHk1NG5NTkdYTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
+          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4071,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Produtores rurais poderão receber até 12 toneladas de calcário sem custo em Santa Cruz; entenda - Portal Arauto</t>
+          <t>Preços dos fertilizantes despencam com fim de interrupções no Oriente Médio - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNZGk2NEF1NE1XWjZ6LXdDbzFCU25uZFlac3V4SENTNVlUTDVIVG1SVWlkMnhTcW9zemZJXzQyeFFudFROaTcxMGlpazA4SjVuN1Roc0g2WkxvanFJOWRJT21XcTFaS1RoM1ZUc2JaNlo3N2F2OTRlYXBOd1N6cVhYMVctdmRSR2d5d3VZS0dKVzRVSDlSMmRnZFQydDhfalJLUTBYcGxMamdhOFVlN01iNlNLMGlFMUNWb3o1ZUxOeUFZVlVoQ0gwem44ODQxaWM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOWVZYaXFVXzYxUkM4OVhCXzdzd1JicHdJQmF6cy1wOHhTX1p5NUNKS2RndEZWMEtVbUlCaURtQUhlVl93cF9NdzNLcTV4NEJJWTJaaW5tLTBHOUl3OVJFbXRJY1ZVTnlJUExfY2E4a2hwLVVUWExaakhSWFc3RHV2T0l0Y1dxYnh5aE12bklILU1ySzU3MmNRcHNWczBNUHVhYVRueUdsQUplSDVkcjNsck1GVF9uMXQzdWk4?oc=5</t>
         </is>
       </c>
     </row>
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ureia despenca e volta aos níveis pré-guerra - Agrolink</t>
+          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>22/06/2026 04:00</t>
+          <t>21/06/2026 04:00</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQSGNkVDd3UG5tUk1aMHVUdk5yMFZIZUlONTROU0VoR21mSGJTakEzX2hQeUtYWXlfQUFHeXZNZWw1d3AwLXQwSE92YXFuRTFhb1pROG5aeDR1aTF6cU85eTdMelBxNnpob2FtUnZQQWJvWlBEbWNWMDNLUlVuMmN2OEFUVTVkeFNFSU1OTGdYZGNCMkZxdVFCVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Principais exportadores de ureia para o Brasil em 2026, até abril - Farmnews</t>
+          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4130,29 +4130,29 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPQkZnLXNRb0ZVWkxHckFMZVE4c3paNXJDcnU2SlZYbDA3bkRDYzlVOFJMVUxuS1hwVW5GWjJEVzZVTTMtT3hPd1J3X2FBR1hsZ2lHZjU4TmRYUGxZVVRlcFp3djlHNkhUZUNWUGpUS2hsTFczTUlLLXN5Mjl6R0JId21Pb0p2V3FzTEVfQ1JhTm00b25fZzFJVGhfMHM1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia: perspectiva após fim do conflito com Irã - Farmnews</t>
+          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>21/06/2026 04:00</t>
+          <t>20/06/2026 04:00</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNb1dTZU45Ulg5NzZPTUFZT0JnV2swWVJkTERUb1hDMy1faHZ6RHFsdzJXWHNCeERXdW1iNl9MYXV1WlhjVWtNWlJDV2xWWXJIelJjTHFETjgtbkZaWXBSVndiTXJpWW1SaXBnN242ZGlBX01jWGlvUVgyTUNXS0RsOFg1WU82c2U3T2FvOHZQMUZoRWRnZkhTbklsSi15TWtz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4186,83 +4186,83 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Alan Trindade vai apitar a grande final da Copa do Calcário - FERJ</t>
+          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>20/06/2026 04:00</t>
+          <t>19/06/2026 04:00</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMEpsNl94b085dkU2TXVTZTFRV0pDZ2FoZzJ3Y3d6ZU1fMk11TVJzWEIwNzRZQmpXbGFyNFBWOElBOFREcmRWZDZGNVkwVEVVaEFQZy11X09VVVBzdmJ5U09CNzdxQ2VuQjAxT1NRSkZzTGZPYkdpSlUxSTFET1lOLXVFbUNicTlVbzhMdmk4WnQ5clpnNjJsVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim Cimentos, entra no mercado de foliares e investe R$ 300 milhões na “mistura” - AgFeed</t>
+          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>19/06/2026 04:00</t>
+          <t>17/06/2026 04:00</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPUWJ5VkZXQTJ4VjNNaWw2R2xKZ3BtLUYwazI4QzVZeGJzUnlESXFvcXFreEdDQVZnT0ZnMS1LMzhfWE1zTVoyRGp4ODlDdHppdFU2N3R4Y1RSM2k0WFN5OU51c2hHZzJfZldiWnlMaXJTM0w3dF8xTmZGM0FnSi10VXFTT3EtakJVR2dJUno5NzNiWHhpWHl2V0hBR0ZEQUtoaTlyWndNMjdMZEdVRHpIbF96aXVJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Acordo EUA-Irã derruba preço da ureia no mercado, diz StoneX - Revista Cultivar</t>
+          <t>Atualização Chaos Cubed - Minecraft</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>17/06/2026 04:00</t>
+          <t>16/06/2026 14:20</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPeXVPMHdlb3dCNlk1NlBBNjFmcER0XzF0VVpVT2hmTDVqZDRpZThJOHFYdGlNN2pyMTFuZ3ZySjJTRWdLSWdCb2dkWVUtZW9WQkRtSGl2cEFxWFJBSFRvQUlKQnFYQTluTTFabWxvRFFPSHJ6eG5BYVBUS05WX085OFlCVEUzd0JKNEk0YmdMV2dqRlg1dnhtTFJORUlITjZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Atualização Chaos Cubed - Minecraft</t>
+          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>16/06/2026 14:20</t>
+          <t>16/06/2026 04:00</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9iNk5LM015QjM1VEdzU2F5cDlKZHNJVHZfLWtuR1FyVWtfUUdzN0cyOVdJYWNPXzVWejQtdkRXUDhPc0ljenhLaGFzcUJ3b25UMzluVjc5Rzlwb2pRbXFSTk1YTWJuMDg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
         </is>
       </c>
     </row>
@@ -4291,22 +4291,22 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ureia cai mais de 40% e volta ao nível pré-crise com avanço de acordo entre EUA e Irã - Notícias Agrícolas</t>
+          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>16/06/2026 04:00</t>
+          <t>15/06/2026 04:00</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxOMGREaHlncEZNM3ZPbjY2Mkdjcmp3b0xIYnNyd0ZrQ0ZIU1VOd1Z1SzlZRXRWYnJVSW9YN25rTVI2dV9BbkpxQ3ExTnJET2laeDJxSEJhTlFmbVR1NjJLVGVXMlRwN1pONGprSFhTeHVfeHFhaTh3LU91dml3ZnBkU19QMDRWeTlvVmZVOFBzTkpYRWNXVzgtS3ljUXVRYkVRSFlnX2VrWHQyWl83RUxZaFBNZFNkTEJsMmdIVW5EaWJ1QzFsbEhTNG1Ia2ZaVWItOG5vMndxaVlZMElfM3NmZXUwX2U0bmRVdEHSAe8BQVVfeXFMUHU1T0d6VUZOVnNHME1ySkpyV2NsbmtiTHBjZjIwVHJjRHBXRUR2R1pleTZjT1FBZi1CbUhxNnFTUUJUZ0xBZTZ5NG1KWUUzcnVpMHZSNkYzWG9NcGI2OEpuOFdCSllRYTlVa2hXMEpnRjUwTTV5NTlmQ21FOVhEQTFVZm5wdEU0akc2V0hNdV9JbFNCSGxlWW1DN3lFa0xIRmxSdldQR1BwYmJ5RDRzMW5kek1NNllsZ0I1VDB5WEhTNktSNGdqb1RkV0xWZ1NadlBPbmx3dXh1aUNHcVRTWk1Sbmw0NnFJbmk5R3JlYmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Fertilizantes mais caros pela crise global elevam busca por calcário no Nordeste - Movimento Econômico</t>
+          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPb2k2YlpLQ3ByYm54MXAzMk9FbFBXbTVYYTFkWkpvSi1hbEtBcERXSXI5QVVxd2RiVVdTTU5MWGM4U3k0Y3J1b3FwNnFRVTRlNC1uUGZFdHZ0eDNzME0tTHJ6RDJKd09wNW04SnVUUTV2TC14Vzh1c3J6RjVmUHIwN1J4dVloX2oxNjljT0pCRk9iMC0zZTJfWHFwdlljek5uQ0s4TjVVR3dLbHJzMGpYNzNpdjFUTFRXcjFzcHZ5M04zcGFxQ2JRQk9BdmZxQTY2SzlGVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
         </is>
       </c>
     </row>
@@ -4362,17 +4362,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Visconde sai na frente na decisão da Copa do Calcário - FERJ</t>
+          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>15/06/2026 04:00</t>
+          <t>12/06/2026 04:00</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOUDdiZWgzRUVPQVFSZEl0d2hfbTVoMmtSR0k3UTRBMjlVTEFqS1F2cHZrRXpVZ3VtbVExb3R2ckx1TWZ4T3ZPWEQ5c2l3bVRWcU4yNXQ2cXphcVpyaTl5a0xPcEhqRW1Yc3Jyb3VVeDB1dTJlamttamhEN3pJZ2plcDBxb3JUcGl1UG9vdUNYMTc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
         </is>
       </c>
     </row>
@@ -4384,29 +4384,29 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Programa de Calcário entra na reta final e deve beneficiar mais de 600 produtores em Patrocínio - difusora95.com.br</t>
+          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - Prefeitura de Juína</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>12/06/2026 04:00</t>
+          <t>11/06/2026 04:00</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNbXkwMlBGcUY3Tm1nUWpFZkp4X1Q5VmlEazBKQ1R3emRpVnVDZjJLNG8wOXVhMk05YTdVenF4akpxbjJXZ3J4c0QwR2pueHJyak5sWDFWOE1wWlRKZ3ZqRl8za1ZLdF95QUE3SjRyVzQ3ZTJVUnlueXIxMnJ6WklKSWU5U0x6MHFaVkRPU1ZqYXp0aUZsWmdhR1d3YlJET1lNV0JWQlBMaDJDTmlYTjQ2eGlTdUt4ckdMMlJEd05HWWRrZDRuSW4tMnpTaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdUstNlpDWGRsZW9BeDl3eVdXRHpKejc3dmpLMFRjdmhaLTdzOU5QUldHRVI4REN5VWpsN2doUTF3dXJoR1laNnZ1Q0FxU0ZhQlUxQ2xfUnVtOFVUM3NMNWJtS0lfOG5tcjREcXdCYWV3TTA3QmRIZkJOTGt2a1JzeU0xdjUtTVFocGFWRXNjUTZJMkZQRkJRQ0ZpVWlPS01HejZnaXFZZ201RFNQZkM3eDd2dE1GbzZiU0ppaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Prefeitura de Juína inicia distribuição de calcário para pequenos produtores rurais - Prefeitura de Juína</t>
+          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4416,51 +4416,51 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQdUstNlpDWGRsZW9BeDl3eVdXRHpKejc3dmpLMFRjdmhaLTdzOU5QUldHRVI4REN5VWpsN2doUTF3dXJoR1laNnZ1Q0FxU0ZhQlUxQ2xfUnVtOFVUM3NMNWJtS0lfOG5tcjREcXdCYWV3TTA3QmRIZkJOTGt2a1JzeU0xdjUtTVFocGFWRXNjUTZJMkZQRkJRQ0ZpVWlPS01HejZnaXFZZ201RFNQZkM3eDd2dE1GbzZiU0ppaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Usina Ipê contrata: veja os cargos que estão disponíveis em Nova Independência - Andravirtual</t>
+          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>11/06/2026 04:00</t>
+          <t>10/06/2026 04:00</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNLUdjdzBOczQwTk8wWlNCb2pMbXppNGhHR2hkWm8xTUxXWGhfZS0zVTR2RXJCYlRyaVZLZWpPZGROTkh1OTRkU1psb2F3WGFCeHl5Umt0Z3ZJX3owcGZIZ0ljSl9BdmY1cll3d3FYNWdWbkZGZWZRS2lLOGZBeG8zaWkxMXBFMWttckdkSEVYSVhOaVdMUm1aYnlCZmthRHBWTW8xMEdzMG5xakhmQW1LZzlDem1VRnZ6eFZ2R1ZQcnpSdU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Governo do Tocantins fortalece agricultura familiar com distribuição de 60 mil toneladas de calcário - Agência Tocantins</t>
+          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>10/06/2026 04:00</t>
+          <t>09/06/2026 04:00</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxOdnJQWjZ6cnBCdGlCMjliVDZTeGxBN3JmdEUzT1VRM016MmM2UWFPVkx1WFo3UjFFRm96VF9GaVBnSGk4YkJPWHB3TGppemN1S3pGNDJ5VU9NbDUxbnVaanRMUm5vUTN3VzZ1MzhzYXAzT3lVVzU1Y3dJR1Z5LXRXZHdQRnhZNHRHdW1LR2c4NFk2RmxQYjFmV1d3anVDZ083R2RSSDZad0FmbGZhUEFweWhxbEU3SnA2ZGJwU3hac185SDJJelZYWGxXUlJodnJJVFA1TW5zNk45SFJoX0FsNHNtQ2JYZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4489,12 +4489,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
+          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4504,19 +4504,19 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Próximos jogos Copa do Mundo 2026: como colocar no seu calendário do celular - Exame</t>
+          <t>Queda do risco da guerra no Irã derruba preços da ureia - Globo Rural</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4526,63 +4526,63 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQR1dUblpzcG93RTlEeS1RQ2FDdERVVHgwVGF0YlFLdnZucnlCRi00TUxPQ0wwQkVqTU40QXJVNjJxUlVqOXdDQXhwV3Z6dWdjX2NLdXdlRHlyc3FpRUxQTTVtbzBTVzA2N2Z2dTk4dnJ0MDIyTnpCZXVZQ1R5VkJGQ3pjd1ZiYzZ0ejhhdmhpODFRRzF6LWxtRUVxcms4TFN5ZVAyeXoxM2J1Zi1LTWg0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd3dXSDVlc3YwbGl1RGwzVEhSRXU1aDdzejA5dzlraE9ya3o5SjExSGI0Vlh5YnpmTVhxdmo1ck4wSVNxb1Z2SjhBNWVOT0c5RmNHeEpBV2dEaGFUMU50eGZuOVVLUVctMjZuVjRRTFhjRmFRSzlmTDJ6dlgxckhIWU1kWW01ZzM1Uk9WMy1qVHQwR2lJZ0JGVXc5aEFWMW1PX2QwUl91WXd2VlRudS1saElmbjfSAcMBQVVfeXFMT2sxaWdqbDNtdEdvb0FneVF0OVBWS3NpM0RwMUZ5YWVpMUJBOTVCWWdac1g3eGlZVnVIWEtta19jWFdkYjVLbFJIdzRXM1hiTFY5Z2s3dkpiVExyZzYtM1pjZkw5UlRlYzVyaXBCcVRrRGpQcFZndW5UeUJTeVIwY0xreV9LbzZicllRRkdYdjE3QkhwTUFETWdqdnJ1Z09FQXFzQThpT2RjTVlwN3lSYXRHTGpnNEQyM3BWeHdJaGg4cWFB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Preço da ureia cai mais de 30% e alivia pressão sobre alimentos após choque da guerra - Bloomberg Línea Brasil</t>
+          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>09/06/2026 04:00</t>
+          <t>08/06/2026 14:33</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNXzFFRXVUUkQzY1F4TE5zTUtTMEtBM0M4UE1HTF9WazN5RXBYeVBnekxhV3RBVUM5bWhfdy1UUk1kWkRLYkR6YVV2VVIxZzVWdXMzYkpRNExqSlNGYWFaNWEtTU55RExMVlUzWkxVSHpsWFA5XzZjaU1uZ01hQkV6Um50dnZ1Y3BhZHV5SzFOX0dlTkM5azlqdHQxWWE2bmV5VEhMckY3NFJsVDVzVVAzVi04Um9XNFpBNzUtYWhpMFNhZ9IB1gFBVV95cUxOVXVKbXdHM3RhdzdIWXpFN21kRl9zQlZDU3RYMlhVMTVEU3FXWDBBd1hQa0NueVhsSmJPemlmQVlDT3NlbnJKa3hOTnhCajlmU2N5U2Z0NFljZ0dmeHljT2R1cGZQRmJESFZRLVNGcE04by14dkEtei1tQTBtX0lUZ2I5Q3BXNU85Z0V1RDV5eHZFM1FpRHkzbUdrS3kwQXo5WnFkY1dxRUpEMTZjOEdxNmE0aTZ6TGxvRnA3eXFQSjB6T2VuUWNPdmdGRDF6SGdRQlJ6WXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Com conflitos se arrastando, oferta mundial de gás natural e enxofre segue restrita e preços, em alta - CEPEA-Esalq/USP</t>
+          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>08/06/2026 14:33</t>
+          <t>08/06/2026 04:00</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxORC1iTVJMYlpNR2J3LU1md0ZhOFZ3NF9kamV0YmRNTWZfYU9xU0d0R0NXWGo1TndlcXBOamRXWm1OUHVxSGFNUjFiaE14LWprNlBibHRfMDVCd1ZEQ3hmZS1RNkZycl9lb0djN3dwd2JWTEdGbGppSmk3b2JqbVY0c2p0R09pcFpHQVFiNGQzekxUZVFwd0JZMVRGRE85bC0temhncE1OWm5ZVTBkbFhzNEVYMGpfb2JjQkJXMEJZVzZ2T0h3aXBVQUdMOXJaRmlfMmpWOGtvVUx0QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
+          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4592,19 +4592,19 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Visconde e Monerá estão na decisão da Copa do Calcário - FERJ</t>
+          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNdTE4ODV2amJMQVVTaUd3bXdPa1psaE91azdMNDIwTHJSd3NDdDRMZEstX3pzWHBmdXlhd2d0dXphTlNYelc2T19zVTRJVVJmWktXRDlac2Q0RVoxeWQ1TTl3R2NnVkRHNS1pWTljYm8xSjRzY1JrUV82SldFNEFsRkp5MjBDdjdSQnhNRF9ibmxDUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Monerá e Visconde são os grandes finalistas da Copa do Calcário - jornaldaregiao.com</t>
+          <t>Ureia cai 32%, mas compras seguem lentas - Agrolink</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4636,19 +4636,19 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOb2tvdUhDbG0yZzRQc0dxa0l1eS14YzVtQjdEdV9CVUF3LUZXMUdreUdJcHUtWkhIcVNtU1E5NmNfcC05LXQ3aHBJaGNqOUxMZEhtQ1hYNWVKQmR3U3lzNm5fQ1ZiLXNvS2szVU1iTWVLN0hkazZhcS15NGdUX0YzZnFLcnlyeGVxSDRnbFNURndKR29IaWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxQN0l5anBLTS11NTdjc3huWTJtZWhGSkgzLUNRcEdwODFMeFpSRTBfZEdka3ctczB3c29GSjNvY24xbzRVOGVnS2xXRGRoRm1YR0k0bkQxb3RxV0I3ZDF6WlpLRjBzbEM4M2Z4ODZJQ2swSkV3X2xYLW1LRDQxc1pyX1B4MGhGNHBhbjlURDhxdlBhUnM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Empresas ampliam vagas e buscam talentos - Portal UAI</t>
+          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4658,51 +4658,51 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxNNmJmTzczLUFGbU8tQ3dxY2RFTU1aeDY4ZVVQSXo2dlNUbzBHY3lmd2IyU2VzVk1nQTFYdTBxdDRLWkxQNTk1elR5ZkcyWUk4M1F1cDZUekYtcGhpZXl1SHZPel9vT19YT0xGLUIwdkVNZUVrZTczaTdXdU9kNUd5eFY4aU9oQ0JtVEc4dXFBNmNCdWpUa3V3YUg3M09PZ2xEYUlDd3VSS0dfSEhRXzlhUlducmpoSkx1WG5rZVFOLUhlVlNGRHpmNUFhdFVuRWNXR1V0X3hzRUoyc0k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Final da Copa do Calcário terá duelo entre Monnerat e Visconde de Imbé - Serra News</t>
+          <t>Clube do Livro: A Próxima Democracia, de Silvio Meira e Rosario Pompeia - eusoulivres.org</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>08/06/2026 04:00</t>
+          <t>07/06/2026 23:34</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1uYVlFb3dGSV9VTGxhQTVScHhYZkVBR3hhN3Qwem5hZU5UWmpOUTlkTFBVT2MtYmJOcEZEX3BGYzM3eHAxYTlORnFpdXA0Rk5LVzdPcHJ0Rm0yaFZXRTI0U2d3dnFLN3VmdFF4dUZJWS0zY19BVVNDMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQalNYQXd2OGFubnBVeXhzZjJFaHMtVS1nWnJEMnBOdEZjajJrMWNqaS16Wm5DMkVyc1l4YmZrV1VtbEI2MTVlQkV0Ykc2N2tweVZ3NVg3ZTNtbTNWNjRTeFBpRzJFZkZLS2gycEJ5U1IzUDNZUU82VmtVRmJRRkR5ODJPOF9VVm5zZEpUNGk4VWRjRWFuLXdOVmVaSTMzUjBFSmdVdnI3ZHNKUV84cGx1UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Clube do Livro: A Próxima Democracia, de Silvio Meira e Rosario Pompeia - eusoulivres.org</t>
+          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>07/06/2026 23:34</t>
+          <t>04/06/2026 04:00</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQalNYQXd2OGFubnBVeXhzZjJFaHMtVS1nWnJEMnBOdEZjajJrMWNqaS16Wm5DMkVyc1l4YmZrV1VtbEI2MTVlQkV0Ykc2N2tweVZ3NVg3ZTNtbTNWNjRTeFBpRzJFZkZLS2gycEJ5U1IzUDNZUU82VmtVRmJRRkR5ODJPOF9VVm5zZEpUNGk4VWRjRWFuLXdOVmVaSTMzUjBFSmdVdnI3ZHNKUV84cGx1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
         </is>
       </c>
     </row>
@@ -4714,73 +4714,73 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Fraqueza da demanda leva a sexta semana consecutiva de queda para cotações da ureia - Notícias Agrícolas</t>
+          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>04/06/2026 04:00</t>
+          <t>03/06/2026 04:00</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxQNU13Y2pGel8wdnA0OXNQWWNNQWFTSDluTFpDUjFlaFFzNnZlTFc2S0RYS3BaT3NUZVhLR0R0VGc5VGxoRUFjVUxfSjVCRDZsLW5nTGlVWXBCaWUtczVFVlpPN0tTOEgwb2ZKT29MYWp6cUFUektYVmJyRWNTV3Y1b21BRUpMYklhZzdyMEhGbzZSbkREcS1MOEdEYnFxV0VOOE1yV1dseUh6bVJVR3VGNE5xSFF3RmVpNm5neDFmM29lNnZWLUIzSkFDS19hS0VqZWoxWWRNY2RHMFp3ZTVEVWFlbWpHZk1Q0gHuAUFVX3lxTE1nZFhKbkZGNkJUeDZoZWQ1NmUxVzAzTjRWVmhLTmZVaVNjM1BaYTYxdzdSUzZ3OWc3NlM4TjJJVzc0bmpTNjdlOHBmNWhpdmhrRE5RelhUYXdMajJRakU1RE5tZlJZeVZmX0hkNWw4c0xfRjFseUtmMXdzZVJoUWN6Q09BMTJheFZSMC16dUJYbUxUY3Z4blRtaVhTQzhxemFkYms4bTRRWW1OTThVZmRhQzBPVGZTN21zbVRUUnNCVXVFWjF0eTJ6QmJrN0gzaWZMZTVGaVdMVXZ1TVhET24ydDY0bWpkNHJ3aW5sa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ureia recua e fosfatados seguem sustentados - Agrolink</t>
+          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>03/06/2026 04:00</t>
+          <t>02/06/2026 12:15</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNM3A5LWx3T1lNOWVsYXFVUFBUd3hESks0cXV0bDNLUTlxaFlsZXNOeHRJaU9vSDY4d1did1ozNDQ1NEN4eWR3Y3JoU3pBZnlTMkxGQzV6QlJWYXl2QUZRRFFTdk5Dd1lpaWJnX29uMkxIS2phb05IaXJKeUh2YnNFT2hud0VjOHE1ZFlGVUtSWXBvT1JLcWVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, devido à falta de enxofre e custo da matéria-prima - Jornal Araxá</t>
+          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>02/06/2026 12:15</t>
+          <t>02/06/2026 04:00</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeGt1SzZTRTQ4QkxZbXVuRmlZQWJIWlg5RGZkX0VuVTk2ZkVzMERUUy1CZ0dyU21qZTZQclpTd0ZUaXdMb21VZGszMHVldE1oYWI3UlhmZjUwV1V4em9zblNSd2lRT3c3eGhIdjlnOWxnanl0Sk5keW5DZjQ2cUYyR0RSUGZaU1NhNkFEYUw1TDVpOFdjRnZZLWVvNUlxRjZRZlppSHhFVFJoUGxNc1pkb0ZuNUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Tudo igual nos jogos de ida das semifinais da Copa do Calcário - FERJ</t>
+          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4790,41 +4790,41 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNZGFjM1JnOHMteTdBanNpN1RhaDJ6SWsxdGZCWFgyamtLYlNKazU3YmhBWnJqajFzZk9WNWRSNTRERklLUVVxTWRqWENTRFlmX0EzSU1vU3V6dk9CN2M2YURvUkV5UDRsNmdCSDV1T2xUVzF5Zktubk9wRWtGSHhFQWdkYlBBcE5KUUx3NWUzQW5mMkVTY3lCTlFmRUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Ureia mais barata, mas não o suficiente - AgFeed</t>
+          <t>Enxofre deixa de ser subestimado e se torna pilar estratégico na fruticultura - G1</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>02/06/2026 04:00</t>
+          <t>01/06/2026 04:00</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQNERlNFpxYnhTaVVMdkhzcG9RWG1rN1M4T0VWR1lLbmRGSE1OR1E0UkhxMUw5ZGtJWjd2dmJabHZ6eWF3UFRBZ2JfWDhjS1gzaTJUSWVDd21BY2tuN3ZTcmNqMGNsZjhuUFA4RnNld0pPZmtwTGg5ajZsdllNeG5WaFlCbTlUREtUcmhudEx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxQd0lEN0lwUl81REtIblJHeWQ3bHVXWFZ4RFN1UGVWa3ZEOElINDFVeVBEZElIN0d0eGc2b3RxeTZrdThaMThmWHl6aFlkUW8wVTBDYUE4dDRSSzYwc253NWVmVWtiamlCeEt5SmVqa1NyVjB1eGVCdzQ3elB5N3B6ZjJLVmpnUEpVcjVIUkxMOFdQUzVHc0xOdlVaeGJTVW5peE4weV94WlJTbld4NzQxZHF0R3lYeU4tYi1kMzQzMTlzVmtLUDdPRGRZQ2JLSXFMbmdHbjZ0dTJEd2ljT1lyZmJHZGFXbndIVWJ6UDNXQlFNejFKSlJXaUlkX0FrM29vMVlEWjJNZXd4bGPSAZoCQVVfeXFMT2NaQnpsUDF2RExvbHRMZHM3dWhJQVFPX2p3a3FUejB0djlRaUFMM0duYjJmRjJKWWFnRmNScXJMNnh3VUd4QXNHbzh3VlM0dlVDSVZGc1l3eUNKZmpva0IwQzFORWVjM0NZT01RSHBxYUlOTl8xU1hlMHFPVkRvczhEbm5xTDVoVjFNaDNiRUdodmdEQmxBU0xNTTRtVVFuenVoZjFYODBEclU2cFR3NkxBR3dkaTEzb3BlbE9oYUhIRmJNSm9RVlFBLTV0aUhOTHMzalloZXRCX3NLbVVjOU55WGY1N0hVVXI3UUNsVU1DbjFnV2p5V0VPOXZHaG1td3V3TGxGTmw2R1VwQ0Y5UXkwTkpsUGI0cUh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
+          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4834,19 +4834,19 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Copa do Calcário: vagas para a grande final serão decididas no próximo domingo - Serra News</t>
+          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNem9RT0xBWGhHc0dKc0t1NjBWaUdkVGxVcGhRbE1GYmU2WDV3WDdMQ2ZfQnBhZGQ2YlMxZFo4NmsxR1NLeWVJbkxHdFRmT3VIVnpNRlZrVjktNDZYR05fQnVPYzJoQkpJdlhQVTRuSDAtWTdfT3JWamRTUGhOQW9xV2JkSFllT1UzTnNMbk9vaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Enxofre deixa de ser subestimado e se torna pilar estratégico na fruticultura - G1</t>
+          <t>Nutrição e proteção: enxofre ganha destaque na fruticultura - G1</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxQd0lEN0lwUl81REtIblJHeWQ3bHVXWFZ4RFN1UGVWa3ZEOElINDFVeVBEZElIN0d0eGc2b3RxeTZrdThaMThmWHl6aFlkUW8wVTBDYUE4dDRSSzYwc253NWVmVWtiamlCeEt5SmVqa1NyVjB1eGVCdzQ3elB5N3B6ZjJLVmpnUEpVcjVIUkxMOFdQUzVHc0xOdlVaeGJTVW5peE4weV94WlJTbld4NzQxZHF0R3lYeU4tYi1kMzQzMTlzVmtLUDdPRGRZQ2JLSXFMbmdHbjZ0dTJEd2ljT1lyZmJHZGFXbndIVWJ6UDNXQlFNejFKSlJXaUlkX0FrM29vMVlEWjJNZXd4bGPSAZoCQVVfeXFMT2NaQnpsUDF2RExvbHRMZHM3dWhJQVFPX2p3a3FUejB0djlRaUFMM0duYjJmRjJKWWFnRmNScXJMNnh3VUd4QXNHbzh3VlM0dlVDSVZGc1l3eUNKZmpva0IwQzFORWVjM0NZT01RSHBxYUlOTl8xU1hlMHFPVkRvczhEbm5xTDVoVjFNaDNiRUdodmdEQmxBU0xNTTRtVVFuenVoZjFYODBEclU2cFR3NkxBR3dkaTEzb3BlbE9oYUhIRmJNSm9RVlFBLTV0aUhOTHMzalloZXRCX3NLbVVjOU55WGY1N0hVVXI3UUNsVU1DbjFnV2p5V0VPOXZHaG1td3V3TGxGTmw2R1VwQ0Y5UXkwTkpsUGI0cUh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxNNXZUSWJtVHF1b0dTb1dGUHNKNW9MZGx3ZmxQdU9Nb1AwWnVHamlscFZkWnU2QmU1MGtfTXZPeGZmeks0MGFMX2NmenU3NFlPTndHV2tIV2UxRnM5VE9OV1pvWnN5YVdCUm9VZlUzbVBHcmJiSVk1MVpyMTVtTTRnNjl4VHpkcDhCLTBULTB5MWpjMDBSYkN5Y2NWSW9TMVZZX3BuY3hoSGNQVktMWG9sdTBfbTJQdUd0cmpRWHNhNUI5QXNhVjBPVWFYSnJPcUJuOWVra1gxN0hvWHBZbmNGZFFPYURHUzRKMDJMbWtEeFRKd9IBgAJBVV95cUxQWWtOaldSSjlUcDlPc0pTYjBwTkNmaTlfNTRDMjVkbTlCMENQbXRhZUlobHFTZ0JXZlU1SFpvZ1NOT25RNVZwS0hITEItN3JzYThweEFBM0p5cHdBU0RZUUwwSmJTbnphbWE5UV95eEJJWDM0TzVoV25qVVpGV25MeVBhTHU0N2t3QzNUbmxqeW9vWHNQS0FaTWc5dU84T0dvZl9xMy1XdUlOOEVfRDltWXlGd1ZwbUNYYUZzVWg0N3F3U3laQXVYbjRhVDJzOVN6dU9HX3hYRmhaZkNQM2l6aHdTc1hLUm1hZ2RSM0R6NFhXNnBpeXlJeXN0aXJyOUhs?oc=5</t>
         </is>
       </c>
     </row>
@@ -4907,12 +4907,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
+          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Ureia cai pela sexta semana seguida no Brasil - Agrolink</t>
+          <t>Preços da ureia recuam 25% - mas nem isso anima o mercado - AgFeed</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4944,19 +4944,19 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTGszenpHeUpYSkdXWW16LWIzWG54YVBRR1lvNElURnZURHlYUlJ5a3hvR3ROTVhiN1RXVDVJTzBPOHRrT2hVc1VsWWdYaHVUaW9nRWFCaDJFUHJaUk5XZUtrQ3BibGxqR3JRWklEbE0tRFM0cEYtcTUtNEtvaEV6eFQ3WmY1SjdCUURkcnhDMG1KRnFoT0x6WE1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPajBDOHUtVWZFN2QwalllTlN0eEhJOG03dE5Ia1JQNlpwRW52MVVjbG5Ya1ZYaGt0QU04dVB4b2ZSdU53blVHcHVVRThzVEs0bFpoY3ZOcjJUay1EVjZXZW00TTNJc19RV0gtdUxtNGVZRFNFM2FjaHk1NkRjR0dGWkVfS0NfZFJzWFNFUw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Mosaic paralisa temporariamente operações na unidade de Tapira - Clarim Araxá</t>
+          <t>Ureia acumula queda de 25% no Brasil e completa seis semanas de recuo - StoneX</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4966,29 +4966,29 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQOHhKWDZBNl9OUTZHSlRPaU5ncGpuTFM0VGJhUERjcXZzNzlOZVNHaUl3QmlMaEtqb010emxIUmQtczV2cTZoV2ZueUctdEhKQ3pLbVVMQ2pEbndGWGZucThPWnhjOFBFMGRMSnRnc01IMjVaWGd3cGxFbXEzazV5T0dHYWt1U1pJdHVyZ2Nn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZ0RlFXX1VzV2k0cnNvMkJWc09sU3ZfQ09uQWlUQ1oxb0wzcTB2QjZaWXlzZnd0bzcxNGJheGp4UmRrWTU1WlVIRTdYaS1Gc1NaaEZidWsyaFlBZE9FcFN6MmMyUDdoX256OEYxbGpVUnJsMXZlZ0d4TWg1UXlidHJha01tYy02WXVGVzR0X0hxWmoyV3RTbXhROUJuLXhMOFRpZm5ZMFNUOEFKalhMNjUyQno?oc=5</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Ureia acumula queda de 25% no Brasil e completa seis semanas de recuo - StoneX</t>
+          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>01/06/2026 04:00</t>
+          <t>31/05/2026 04:00</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYlZ0RlFXX1VzV2k0cnNvMkJWc09sU3ZfQ09uQWlUQ1oxb0wzcTB2QjZaWXlzZnd0bzcxNGJheGp4UmRrWTU1WlVIRTdYaS1Gc1NaaEZidWsyaFlBZE9FcFN6MmMyUDdoX256OEYxbGpVUnJsMXZlZ0d4TWg1UXlidHJha01tYy02WXVGVzR0X0hxWmoyV3RTbXhROUJuLXhMOFRpZm5ZMFNUOEFKalhMNjUyQno?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Embrapa desenvolve calcário granulado com função corretiva e nutritiva - Canal Rural</t>
+          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOck1oOHdwUmVRMjZleHc1UWEzV1B2REJFbXF5ZGQ0enIyaXpPbVZMY1NWcU1FWjUxMjd6MG9KbVVNanBjNDhZcTlmek1zRFczeE9jaFhUcEhzUGpXMkYwOEVjaHNTSURmMG81LUZhYW9FeWZONFMyMjJlb0EzeUlvSzNLYTUyQXYzWEJPdUgwLTR6d3JHdU5aNVRjQXdQZjJrVmozQ1U4NFYtRlZmLXQ4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário que reduz perdas e aumenta produtividade no campo - Exame</t>
+          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5032,63 +5032,63 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPbUFVRVpOaU54dHozMHJBc3EzSlE1c0JBXzZkci1IR09EVEcxejBEekdPYXE4THV0SUtIemQ3QjItVTRwYXpZTHVUV3ctU3M5WHBVbjNJaVhHVnlNVGI3elZmUWlLWFlwZzNETEE0TjRNY1NkYklMYlQwQ1BNN0Z1Y1JsQ3FDZVItSmFuYzFKRnFXLVdNM1BjRnJlRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Embrapa cria calcário mais nutritivo e resistente à umidade - CompreRural</t>
+          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>31/05/2026 04:00</t>
+          <t>30/05/2026 04:00</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNY3VDcDE0TVJIcGRwOVozMnozYk12NFEtRnhYcVVJSTd2ZlpCR0Y4WlpXdmI1QTJaMVAxSDJQc285M3NGSGZNYTNVd001WVVxbW1XdGFpTzJfdlg3Y0lQVHBBWEVqMXVFLVFBcFZaSTVqWmR3eFZvejVZa00zako5Tk5GYk9IS0xNMURFSGZ2clUyZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em Tapira, no Alto Paranaíba, devido à falta de enxofre e custo da matéria-prima - Diário do Comércio</t>
+          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>30/05/2026 04:00</t>
+          <t>28/05/2026 04:00</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQQjJhMWdjMVBkN05lbEV2T1hBOGZqV2FEektlU2Nqd0cwZlEzLUY4Q0FIQ1dQUEtWYW05dFFza3B1QzJ0dVMxaUxCOEhEd0VxU2tidXhZMFVWMGsxeE1CeFliRkRONmZieWRSRDQ5RHVfNWFybmxTU2lJVHZYWENZRkZGZ25tbWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
+          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5098,19 +5098,19 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
+          <t>Mineradora ligada à Vale fecha acordo de R$ 27 milhões por extração ilegal de calcário em Goiás - Jornal Opção</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5120,19 +5120,19 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQUWpoTWRpSkZ2YlpjVWJkbmtHSTROcVdZYVJmcGpwd085QUdoc1dxelhudXJvVlR2X0xvZnRMbjBFRE1YdDRGOTFjVWNuNTJ4bmQ3UU9UYmRSYUMxSmxpWHlJSE9Hb190d3VGdkoxejI5Q1VrSVpfVHp1eFpkd0YzSUl1YjducElqUmhmM1hSNDJHaTZHWHRuVktXY2R2dHQyMU5hNklqcElfSFJjVGc2WFlaQ19ZZXIxVTJQODJwLTJqRjNhbnZjLUNEa1NhQXZOXzhhRlNxdGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Retomada da Fafen atenderá a 7% do consumo da ureia no Brasil, diz presidente da Petrobras - UOL Economia</t>
+          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQR3RBSFpsbjM4bDFaWVBBa1g3eE5La0VVV0dxaDdSQjVUc3c0WjlnbGg5bFFXRWVJQXUxRE82QXJjTzU2TzZoazNNYTJsdFBCNGtOeTZPcjQxS2tQVl9EcVR0YnI0N1ZpY0VSTnhTQUZMSjhwQ2otbTZVYVRISG9NZFZQREpfREw3RUlsOEl3SGJvMHpVajhONUlwTlF4YTVXVGhneTBXV2xoV3ppcFJVb3h1T3BaWVZUUUpZNGdEVnNKeEluXzl3Y21nM2lJODk4OU0zTDhrSGlrU2F3NHZzV2tEYmpBc3pfMlI5X3ZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
+          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5164,19 +5164,19 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
+          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5186,19 +5186,19 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Comercialização de fertilizantes no Brasil tem atraso relevante - CNN Brasil</t>
+          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNaGlLX3NOTUxkam9rd0NRVDI5Rlp5VDlZVjVfMWh2andDSXJGaXhVWEJTaWZ0b3haQ2tBMmFVV3NOVlVuOC1MNzlUNGFtbFRncDZZcGZwZEJmQVNxZl9GTTZhUUZYUzdEREFzbURVaGZnWlAzN1J1UERhbEhvZ0NHNGlDYk1sZFR2OFA2MDUyYVBHeHRtU0ZjLU9TNjNDT2M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Anvisa manda recolher lote de coco ralado após identificar excesso de enxofre - G1</t>
+          <t>Anvisa manda recolher lote de coco ralado por excesso de enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxQeDRscjA1UGJuUmh2b05TWVBXUlI3RjlSLVJ5Y3pidkJjaWtZeTVrYnBfNFczOFFpNFpGTG5SUUxRbXBRS2tCUHZEWTBjUzNHZFJyMGlSYzRzNGl1eEE5Xy1LOW14azE3QUNHdjd1cDF4TEJ0MUNoM3JoWmNsLWkyQ0tqNTNkMHFoSmZBbEFWWDBCNDh4UHBNSWFaN21nOW1QYzFCQWRvcDA4WnhvWGZvV0h5SEppcGdJMWxLREVmdXZzUU5uUkNUUNIB1wFBVV95cUxOUHRpNVVsWVRvLXE4MjR4NFRkN1JiSFVaZnE2X2RQRnlNOUMwWmJ1SkZ2R0ZQWkNVaVh5VGtWclVFUFZkUDQ1SDBTREd0aXAzUkY4VFZ1RnhaZDVZRVBTMXV5NXY2aXJIQWdIUkk4UllaTlNZSlZUcWhLQ19TZUVHNS1zMmdNckRhaU9LcUlzUFVub1R5YzZiU2wzWXlxQlRfdHhsRzZjV21Kem43WFh3VnpJY3hvcXZzRFprdll1U3YtU3YtVVE5OVdJLXBvbzlWenNraUNMUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPbEhqa29HQTVER2pnczg0QVFJclpNcDZJMlFLdDVCb1pnLWdEbGE3clRBLVkzak1SVXBSWTcza19aSlVtZklGV01lM2JyMms1ZElzUlZVSTZDVFNraUxpZDBkd1NYZVFNeXBKTkpTbl9VTlBvTWh3V3ppUm1BSzVqc09xa2x3RHl0MEFtS19jYnp4RGJSMFZKRm01VThReXhLSmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por excesso de enxofre; veja a marca e o que fazer - Veja Saúde</t>
+          <t>O que acontece ao comer coco ralado com excesso de enxofre - 28/05/2026 - Equilíbrio e Saúde - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxNZDQ3Zy1xb2VGTVJnVnRoeUVxY1NMMC1yRFV3RDhKWFhZUGluN3ZPVUxEZEtYSlcxUF8zX3d4ZElaV3VDSXQxOGEwMUllSFNEVmJFenJ6ZE40djdJSWVubWxLVDFldFR2WmdybFp5Y2FjemhkQ18yam5VcjJ0UkVUb3g3ZXJRaTV2R1lIZTVEY3hEb2tlOVFNb0VuVVhPOVlTZnJpWWpWRTRQeTMwMkxfUWxrRDFIQ1h4dTF0djczbTl1QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNN2RIeW9DekxMUFh6Wi04a2g5azFnTXR0OFc3ZnJhUkNOR1hoWUNlRl9tME1uUDVsT1RtOG9wRXNaQURES3ZUZW5Xc09Xck4xQVlUeHUwWXUwa3VOaVNvcHRlcUNvcExYaUdpalZzcWZoNExIUTlkWTFOSG1BUExoY1Nvcng0WkNWMENTQmZKUUFjODlVQ25MSURhSE9LakhmTjB0Y3lqQmQ3WExNT0g5cWNRdnVxTDFLQkwtQS1aVjNqMDVzcl9yMVloWXgzS05GV29lb1QxUDJfNTZSN3RBQXcwNUNFZURqRkxoNw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Anvisa recolhe lote de coco ralado por apresentar excesso de enxofre - Metrópoles</t>
+          <t>Dá para substituir ureia por farelo de soja no proteico da seca? Especialista responde - Giro do Boi - Canal Rural</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -5296,29 +5296,29 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE1hblFncjhMbjEzXzJtaEdzYXQ0djFOYlpDLW8ybnAwVzVTLWh0WlVIa2RwM09UMld3ekVKd2VuZ2IzclNxcmlONjFmbjVJMVZFT0c1N1VxM0J2bjlLSmZMLTF2UTRILWl5NTN0VE1Jc0dkWk1WSG5vdXZaRWw2NW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQR082Wi1qR1lQM0swUUVtTUN1NkhLeXlVbDZJSGFRRjVVaWFEb1hSN3IwS2ZCOVZsLWdvMnFtNFo3aFlGcHlMeUd0LVA4ZzFTWEtyZm81Y1dhZkhCMDR4SHVyeW1tQlpjelVoT1VrbU5LMXRESkprTVN5Z2l4TnJYU0tFTGpiVHlUaFZadWJFeUp2b29qUDV3VXVNQmswcXkxUDdrX2FwV05USVRSdFVMWVBnQXBXMDBfbEVBT1RiVU5SM0ZIdk5VMU1hcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Anvisa determina recolhimento de lote de coco ralado por excesso de enxofre; veja marca - GZH</t>
+          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>28/05/2026 04:00</t>
+          <t>27/05/2026 04:00</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNZklVdWVqSnZBODhORUZwWlFOeXFpSHlEN01yMWd6YW1ZeE5lZXhRSFVHbFdlU3BmT05kTkdZYnY5dE5kelRsdXBDY29aWTAxWjV1ZENBdHhpQ1hqT1d4dHBKOTQxREMyTV94bXQ3MGk5RWRwTTBlQTJrNmF5cWMwcXI4VWZOYUllRElnVm11dW56N1NUZ1FjVkdmQzlsc0xaLW5lakRlVkM4X1JuMzFIYm1wbXBZOHpwZ0Mwb3NWaXhOMkU1UGt5a1NSb3hYZzRnN0FaVmhqZ242Vk9OYlhyd3BKTlgtN0JQWUhxZ2w0b01iSGNBRm5qa1BheFU2S1dV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5347,12 +5347,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>China libera cotas de exportação de Ureia - Notícias Agrícolas</t>
+          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -5362,63 +5362,63 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOTENSOXc1NlM2MkJZRlRZeTRmTGZxeXREZ0NqS0JsRGVxSFFrLWNSWThaTUpnVC1EVENybkxYQkhEUHZOM1RlOXBMNnlOZ0ZpbFZHZWJMSnB4SDRtOEVOa2ktNzN5cEQ1SlhUa09fNWxBbWxhNnZMc3AxbWZvUzc5YVhDeC15YWwyTmxYZ20tMVZGTWloUE9NTGtwWlhYemVVRXl1d9IBqgFBVV95cUxORTJOMzJaT2lMNUNabklSUnNKVFdjZVMycmlOQ2xrdFFVN1p5QmtJall0ZWx0MU13bGVWRFZ0dTd6Y25memNYNEI5Q1A0dHBQNHRhb0J5MmVUVGFEd0xXOHcyelMzYkV4MHlKbXdOQW1SejNjSGZjUjUySG1Gd0N3dEszMURXbnQ0dVVqZzlBY3RmR2Jhc3JCWXpRQmpHUndiWlJXWjZTTUpKZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>COMUNIDADES | CMOC Brasil patrocina projeto Cerrado Imaterial em Ouvidor e Catalão - Brasil Mineral</t>
+          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>27/05/2026 04:00</t>
+          <t>26/05/2026 04:00</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxQRmdvSURuMjZNNUdCMGhXalFZWWhyNVRfaUtEczRyOThEaXQ5WTY2ZWJsNHFpVXFJV2R1X3YxWEFmWXZjQW1DTnkyc2c1MG1Ec2VTSTY1ZWh4SFpObG1EUTlvdFVJdzZ5Uk5FLVRfUXliQjgtUk1XS1pHengwWTBPN0x2MURlYlRhaFBtQ0lQbjE3VG9zVExUNGNnRFY3V2w2b291WC1DODc4R0RWMWNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Pela 5ª semana consecutiva, cotações da ureia diminuíram nos portos - brasilagro.com.br</t>
+          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>26/05/2026 04:00</t>
+          <t>25/05/2026 04:00</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNcE11QW1BUkZZUDUyX1N0WWZzcExyX1ZyMVVOZmN1MHdpLUVTdWhGNWtYSnNFZ0lXLXo0SS1kTm11cGZnTGtOY1RsdTVPX2YxUjZsaVBxUTU3R1NaQTg1ZE1yRG9MVWJiMkh2eEx0T3ItWDJWQndSbEZFMURKX3FQd08xcno4aHhpSVgxMlpka1pzTUxlTUd2dkp4VGZaTF84VkluLXFrUEs1azFKY3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Produção de fertilizantes desaba por conflito no Oriente Médio - VEJA</t>
+          <t>Copa do Calcário define os semifinalistas - FERJ</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5428,19 +5428,19 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQd3NMRG1QdXN1NzBmNUp3bUhRUWpBQ1FZOWxLVzNyUnNLZ1FZYkZDRkhXTEhIWDZFX3FuU1kwckNiTG1VSUI1M3h2RU0zR1pQYmlHVDdrZHJNZ1hBSFVrWm5ySk4ybG5RQlh5MzVqMk9OQnR0TFNWaXFuYjREMHFLU2syNFRfelEzVXBER3dQT2JQbW5nU1BhdjJ1OUhEcW8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
+          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5450,19 +5450,19 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
+          <t>Definidos os semifinalistas da Copa do Calcário 2026 - jornaldaregiao.com</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxPd3lVWExUMExpNnYzRHRkVWcxbS1lV1hMbE9mMHlZTkFTSkd1NFJ1Z3lxYXhtZzNpOVNJTjJOV2Z4UmhkMzkwNmlaRmtKOWlPQmE3ZVhoX2pCQ1N1d00wT09UY0YyTHJ4TFIwRTM3Y3M1bU9QeklBaDNvRWVGdmpoLU44OGpSNms?oc=5</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
+          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Ureia cai pela quinta semana nos portos - Agrolink</t>
+          <t>Ureia cai pela 5ª semana no Brasil com demanda fraca - StoneX</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOem1iVWpuSWx2Qk9PN0xvMVNEaGZEM1kzQWdmeWRFdTh4VjVJLTVNTDhRY1Z6ZnYyYVhkWUNYVm51U3ZNb0JiaExrb2RYcXBlX0NaZGNQUk5KZ1FremQ0NzZTWk5GQXZ6UXBxYm4yRUxTNTRwTDdiRnh1M042a1JCM3VZUXpoVlJRZU92ejA5QV9BZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOemd1bExnV1NEMlMwdGp2clZ0TjB2QlFkemdjNXhrUkJyaWxjd2N5MWpPMDlJV3MtX2FyRDctd1RVLW92bm5MT2c5UnJIUGh4UWpBancxVnJDd1c5WjVKVWktTDZoR3ZaU1FVekxXaDhkNTM1Rm80dkVuNEVNekZ3YllvWVRDLTR5STBvMElpRWxEV2dLREQ4djUwczR6bFFmbFY2dUt1UDhWb29WZC1hMDJDZng?oc=5</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
+          <t>Falta de demanda pressiona e preços da ureia recuam no mercado internacional - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5538,19 +5538,19 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxOLWFOeS1Jbm1MT0FjNVYwWTkxNVI5MVZvYWpFTHdSYkJtcklhQzkwbTgyUU5PX0VlcjZ2eWo2ZVpveDE3ZTIzRW9kVWlELTctbW54eTNodWVQelBYUXJ6bUJWMnZJRTNYTEhWOTFxMGpLa3BLbENKMW1DQ0pQUUdiT1dFb2FPYkJlUVQ0U3JZR05lZTNCYm9jalFrNDgxVXhVM2p6V0xtcXZxVVkw0gGyAUFVX3lxTE9YcUlfc05SQjlHeDViTVhvcmIzT3JNdU5ORnVqek9HdGg3NzhDdjNFY2ZjZHFzNXFDc0w5TzBVUTEzdkI0dmhMMXVIcGt0WDF5QzhBZFBEbm5EbHhLOVgzSEFpZEZUWGhSdVh5MEhNZmJhcFJxVzVQclZsS1pDWE9IVUZ5dFVUdjhlOW0wOUlyQllUR240TGRINXFpZG9SQkNCN3JpSko2MFVwTnRxRVVGdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Mosaic anuncia iniciativas selecionadas no Edital da Água 2026 - IBRAM - Mineração do Brasil</t>
+          <t>Cotações da ureia recuam pela 5ª semana seguida com demanda enfraquecida - Canal Rural</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxOdld0UllhbUlrZ0dxa3Z5TjRkSXI3VTNYcmxENU1CakwyWGs1a2R0ajFKNUtpZV9EZ1V0OWtDbXBVOWZrbUoxcWJOT2ZFWkwxNzhhNnRaYVBGdl85ay0xZUJHb19HNGxkVkczNUdPc2p0eHFBLTdRNlJmdTJJN1hHbFZEOTBGYzMtX3N4Q3BhcEc4N3pEWWVF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNalY1bGttNXJOYUVBSVFzeVNDd2pBQXkwUUhvLVhFZFJYd0kyYl81UHNuMW1pR01sSElyVXJVbTNYVTU0QVV6M1ZTb2M3MV8wbFN6U2p3WkhWd1hlcXFJR2NFSW9DcXYtWC1JNF82UlJSUXRtYmt1VUgwVHhZcDNHWG1qZk5majdOWldPblpLYnloR0NTcWt5dFhXMkNiTzl2emszMG5CczJabUZaMFdCeWNCUlRKQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -5572,17 +5572,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Copa do Calcário define os semifinalistas - FERJ</t>
+          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>25/05/2026 04:00</t>
+          <t>23/05/2026 04:00</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQY2hPQlpoTF8tRzlCb0JEUF8teWEyOWE2Ym1XcXVydmdSNFdqb2ZUNWwzR1lfb01XbmNTZlhGUDMxODJab1czSDRCcEcybEtLRmItdHh5Y2hvNG5SSXpqOTdjTU0teThRM0Q2OVZmYzR4dXJUVU9DLTE0MTBqNGZKNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -5594,29 +5594,29 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Insumo essencial no campo, calcário tem dia nacional neste domingo - Primeira Página</t>
+          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>23/05/2026 04:00</t>
+          <t>22/05/2026 04:00</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPb2RUbXdJZ0xldmZuYlRPRS1tdkM4SEtfd3hnVWpCaTJnVU4xUjZFcTJtR1pRM0h3enJGaVA1T3RueENpSEdyYmNMYV9NZnM5M2NzUjhOVXV2NXFnbDZLOTBBaG9iU2hQU1IzdEFEV1dRSFlfZzlKSW1MOF9BdHJRYmVMQVNfSHpfNUhFaGhYX285MnZRLXBmSEdQT2N6Z1ZvdWUwNUhQNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
+          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5626,19 +5626,19 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
+          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Casa Criativa CMOC seleciona projetos com impacto social - Valor Econômico</t>
+          <t>Crise internacional pode afetar produção de fertilizantes em Catalão, alerta Metabase - Badiinho</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5670,19 +5670,19 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOWHlwcHo5UU9SbmRMZFF6aWxMN1BnMjRXLWNFUDZGYnVVMFZTeHpnWG1ldV9hM2NqVFVkRHAxdHAtMmp3OEVzOEdxV1RGRldNOVozVDhVVUhpTXVCWmZvdFN4enZrZko0RmVydk9Yb3U0QUtaUURVS0NGWU9ELU40ZnFsRjgwNlc1YzBLQi1PcXo3WDNfWmhrdTlJSEpfZkVyajVGTHFCOUpjMGJpZFYwVkZERW1FeFFfMm1UZlRMa1B2UdIB0AFBVV95cUxPcGNGakszQVlpNWp3X2FGdHdHRUpzY0hxbjJQajVKUThjSnZsbHV5QUY5ZFJIZFkwV0RvejZWNnNnQlZjWHI1Nmk1OFRWb29vb21qTXQ5aUtmNUgzY1JTNktuTjg0Q090S1R4VFBsVWFtYWpCMmIwel9xVGtnREZxYTNfeDJrQTVBb1RxOExCeEZDWkhxVnpCaWR3VzlSRTlvXzFuWVJLZEJsSUJDN1NtbDhGRnNrOG5NOGZNOFYyME5vUDJvdlRBRFhGNXctNFdp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9UOVFBd2FaZHdNSjBOeGVrdTZ3dnBwaWNxVEdCSEEydTROLWhfVXYzdHB5UTdPUzZsN2JqbFVfQVItV1htb1N3Z2s5Q0l6cVdBYjZlSlZ2bVZ3WFBUX0ZtaU5EOWJ6dTBWaHcxaGNwRXF6YWRvdmhV0gF8QVVfeXFMTnU4U1hjc0VldVhHQVBQMkNDNm5fdFNNN1FDN1hzNDdJWU1DazJiNGVzM05BYm1XamR5eWJQMEg0QXJRQUJOU01MeWdMNEVUTUhZdVduQnZDZGJGVUNHbFJsTWcwMDFTd0lYLUkwZnczTE1PZkZvcUhTUmsyLQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio traz oportunidades para o mercado de calcário agrícola no Brasil - Sistema FIEB</t>
+          <t>Mosaic e Inpasa fecham acordo de barter para fornecimento de insumos agrícolas - GlobalFert</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5692,41 +5692,41 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQcktOOE9RSHdxNlg5anFPdkxFbno0R0s0UGc1UmVQTkVFTGVrVTcxY1F0b1Z0SFN3VGZiOUU2dUd6TGhGQXNXNUV6NmpJQVBBRW9Dc0tSSkVUeVRHNGhzQ1Rpb2p1eVNrd2dLdzNWTEI4aGwxVVYyNXdiUldLQV9wcHBYVl9RZHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNanViVXlRQTdDUHdhS2VpT3RscTREdVpDVjdSRG50cTVUR0YtVGFXWEwxTWVvVDlCeHBVNW9iQ2hkb2Nqb1hhZTdxR0VoWmhOb2VYSHFpWEszR183bDFQblVMcGFGbVZEMVE0WVNZclUwemJ0a1ZfVktDYTRBa1YzelI1ckNYNi1GTlNYRll0VW1FRFB2QUlnUzA0WWJmM3c3ZTNBNFdnU1NaUnZzZHE4UU91Wl9SSXMzVEt6b0hxdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Severiano de Almeida adquire distribuidor de calcário para atender contrapartida do Programa Terra Forte - Jornal Bom Dia</t>
+          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>22/05/2026 04:00</t>
+          <t>21/05/2026 04:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNWTNLdW1XQmxUS3VCWUJicEhjN3p1SWRhS2dRRkV6VkVGZ2JTWHdhQjVlVjFGUTF0NjFTbU50QWlPY2hBdE5tcTlZYXgxLTR5Q1psTk5rdzUxNHNCZU95V0NwMWxJX2NUdXU0cnFLaFNvd3VnbGlSV3NVbWhBWWUwZ0FlQmZXNzBXMnRvRGlhbk0tRW1lbWhqd0FfTXRmTXJuOEZTN19XdkRTQ25oZl9zVWVBN1VPa2pnUGdkaEs2S1NWTGEyR2lsaXFyQ2Y4SS14bWM4NFZtazlSWHN1UDBwRDJUaEw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>SENAI/SC conquista 4 pódios no Grand Prix SENAI, competição nacional de inovação - FIESC</t>
+          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -5736,41 +5736,41 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNd09RQ1FuMHBlZlRaOGpYbVhPTmFIOHVSOVdHMHRSVG8zSU5rN3dJb1Z0WXBzNER4eUstZ2pZM2lvTEpjdW5ibm41V1I5ZmFjUkhWLVBmNWJBMjM5azVHY0VYenpkR3dMWm8xaUFfSFdYX05LdzVfbmkyc21IRjM2ekdHbzdqVUtIZUl4VnBnTUROYmhCTUhwOGhmWmlQZEQzUVlfWGg2TmsxTlBTY2J2NFR6a1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Obra de contenção de erosão protege margem do córrego do Enxofre, no Jardim Conceição - Portal do Município de Piracicaba</t>
+          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>21/05/2026 04:00</t>
+          <t>20/05/2026 04:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPbmRVNTdMOUJWUXZUT0V4SWZubnFTS2VSTmt1VDJfNnUzdDQyazM2Yl83TElJN1Z4blg2YTdiV1Z4azJWcVRCQlJ2NlU3cGZua0ppS3ZJMVVlNjF0Y1ZMNGU4c1RHVTNZWWlPVWQxRktWZ3NaMVVFdWR5TFZDVF90aEJ2SE5FQlVFaFZkQXNXaFJiSUY3Z0F0Zk5SaVYwVFZIN3VsTUhOVkIzVUE3SHcyTmc2TE42SEZiOTBSem9aamk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
+          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -5780,19 +5780,19 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
+          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -5802,19 +5802,19 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>AgriConnection e Mosaic lançam Fiagro de até R$ 100 milhões para o mercado de fertilizantes - AgFeed</t>
+          <t>Dia do Calcário Agrícola: o insumo que transformou o solo vive dias de consumo estagnado - Jornal do Brás</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -5824,19 +5824,19 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUmlJREVBVDhtRldoNDVjX3RoRkNEYVB1QU13RjFmNmV4MHFNRnp1Qk0wdENJNU41Yk9aVTVNNURDU1V4VUpfczlXOFhUYmlfYUN3NnNnSncxY2RNYWFJQlBXdEZJRmNmSnVTeTRDcmhtU3FzNVdybzliOUJwTkFONTV4MGFydDlxakwtblZiTzNlOEx1cHJxd3BUTlhrYjRyR3RkSmFKc0EyTXRqRDhqV3ZoUGd0YXMxdWxkVjJjTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxOMEhDZUNyR0d2RnkxOVdKcV95OGVVQUNFTFJtMllSeEtXOTZyd0Q3NG93eTlPU0pzNGhPMlZMUzhCaTI3bE9Ga3ZlejRQMmlmT2JnZkY1NzgtNG9NMjRCTzU3bHJXcjdENTlucnBWQUU2STQ5LXBFdzlWR2d5blR3YmtMTmhKa29QWVAxWEpMWjZxWFRUT1prX0RiOFZSR0Z3bnMwU2RMaHhQZndlc0JjcGJDb2RPeTJLX1hhTWdCSTBGUWRzSnhqYjd3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Ureia cai 14% em quatro semanas, mas preço ainda está 43% acima do nível pré-conflito - Agrolink</t>
+          <t>Calluz aposta em calcário com alto teor de magnésio - RCN 67</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -5846,41 +5846,41 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNcDRET2JCb0V6aVhxVWROTHZEY1Vkcy1wSGFONnVQZGFqY1VmaU1hVFBFRmRIYzVod2tvNm42WlJXVXhxMXB1am5aMnlXYnlnY0V5QU5pWU52TUZaekpsUmJtaXB0NnJEaUpXSUtsMjBrT01KWmZqLVdrWTc4MDVxM3BfWU9KVHhRZHA1TFdGeWtMeXF5dmVDTXJfU05qYVdLSERnZll6WXVaa3ZDOFhWemRQck1YM3lkMkVoXzV3dWluc3c5MTBNdFJvOEFmZlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiekFVX3lxTE90MUpQNDhERWltS2FYaVNXZ3NvZTNaRmVXMFo4OUZrbUFmODR5REtNSmJDOVd3bnFqTnRZZHctUXV3U2N2OVg2ZDkwRGMyUjVJUkwxX2dSYWdoZ05ZeTNXQnBfdHE2SEY3OF9BQkVFLWVUQW1fejZWRVRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>TECNOLOGIA | CMOC lança projeto para levar inclusão digital a comunidades - Brasil Mineral</t>
+          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>20/05/2026 04:00</t>
+          <t>19/05/2026 04:00</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQanZUMi1FN3JGZDNCVXJ3dTJvYUdrYXlhMnJBQV9ka3QzVXZnZ0t2RFpQaEFndUNPOTZzMHlEXzI1UFlsaFlHTGJDTnFhU2RXZ2JfRFdWMVVieTZmSW96Q1VTVWdWZVgzSW1xTHBxeFhydUZUY2tqZTRMQTh0V2RMOTFycDJoMGl0dVVDaUZXV2hkUVFoalFOZGNMeEVsUlVQWjZrcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Uso de Nitrogênio e Enxofre para potencializar produtividade do gergelim em solos com baixa materia orgânica - Notícias Agrícolas</t>
+          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOTkFDUk1KZS1WdXQ0a0FHc0NMZnhqU1dteW1RYm43Q05kb0JOOFBHUkx3MDR1UHI0YjgydUhrM0FTNWh4ZWNrQWFQRVZmSEpXaHpvM1Bnc2RheW02Z0RHcnp6SUpySlplWXR2bTdENUh0bGpaRDh3QWsxQlhldjBaOW1GTWk2S3VTSFpKRVotN1VWMF9GWmZpTHFWcmFoakNfRUZFdEgwcm1yX2FpVmUyVkd0d1J5RU1CMlJ0enItVVVqalE4NFNJSE1DYnpqOE12XzZIaFVMd2QzaHpuTGsxSWpaeUdTeDJnT2c0ZnJpclV5UTVzZFFpSHpSZ0J1WGNQTXBlYkJkMNIBjAJBVV95cUxOMl82dFkwUEdHOHB2VTNUOXhERkRIMm5DMFF6VlRyMzZPSk9XbFczUmViSVdubUo1MVNPQzdhUmRWeWhGR0U4azFoNUdxNTEzem9RMERUSzZvNjVFbWwycUJ3LVotOVJjWER2SXRHTTY5VEdGcUxaRmJIR2x1dTV1S29qcTlHbnQwRzlmblJfcHlMXzFaNlkwenpReE50NVh0S1ZLSmtfRnczT0NFTUhVeG9TbHRGeG1zMjE2YklWNzM2azVsem0wTGJ0MURoSHA2a3hOeFRQaHdRZ3E5dXRPd1phb1dIYjdJeEVNbEY4bXZDRFhGdnZYaUt6WWFISDAxRkdmaE5ORi1pcjkt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
         </is>
       </c>
     </row>
@@ -5919,44 +5919,44 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Demanda enfraquecida derruba preço da ureia, mas relação de troca segue desfavorável - Canal Rural</t>
+          <t>Conexão Cultural – Jornada ESG chega a Minas Gerais, Bahia e Maranhão para conscientizar sobre sustentabilidade - O Maranhense</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>19/05/2026 04:00</t>
+          <t>18/05/2026 14:18</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNWHFYa0tMRUlRN2NycUdya2FNQzRVaU92UFc4Wk5NcHNUOV9MVHlIUjJEWXhSQjZ2ZGFuQ0ctNU9ES2U1RndpeXRQMFRrYUlHazJkazJ1aUhfN2hCSm8tc2VZd0kyVGM5MmZqTWxMZThsNEQya3owZk9ZeWo4U0VrY1VfQ1g3YklGbVVRVklaLUdCdmEtRklQSXpsTnF5TWRDbklfVGpFTGp3VnlVc3p5Q2VaMlRYTThiUlB0cGNTbmM3Nkxs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUHhsWkkwMlFtdl9jNVN3cXd5YlRZc1kzQVZ1aW02X1pUZFFKUFUyNHZkNVlBZzFfTHo1VmFleU1pU2JNakxXZ083RXNvUzRXY29aS0IyeE45S3FmUlJ2MW1pYVhSRjlhSzRiOGxyNkItU3dtMVNYX3o1RnVQVUc5QUlYdnJhWWVhc0dRVDVCS1cxWllGNGR5R3hLeHZNODJhakRpWjFpNFRIRUxfdFUxMmJYTHdaY1piVHdWc25pb2VRSVR3emd3aG9MQUh1UQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Conexão Cultural – Jornada ESG chega a Minas Gerais, Bahia e Maranhão para conscientizar sobre sustentabilidade - O Maranhense</t>
+          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>18/05/2026 14:18</t>
+          <t>18/05/2026 04:00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQUHhsWkkwMlFtdl9jNVN3cXd5YlRZc1kzQVZ1aW02X1pUZFFKUFUyNHZkNVlBZzFfTHo1VmFleU1pU2JNakxXZ083RXNvUzRXY29aS0IyeE45S3FmUlJ2MW1pYVhSRjlhSzRiOGxyNkItU3dtMVNYX3o1RnVQVUc5QUlYdnJhWWVhc0dRVDVCS1cxWllGNGR5R3hLeHZNODJhakRpWjFpNFRIRUxfdFUxMmJYTHdaY1piVHdWc25pb2VRSVR3emd3aG9MQUh1UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6012,17 +6012,17 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco, Monerá e Altense garantem vaga nas semifinais - FERJ</t>
+          <t>Cidade do século 9, suspensa sobre falésias de calcário, atrai turistas no Mediterrâneo - Terra</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>18/05/2026 04:00</t>
+          <t>17/05/2026 18:07</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPNHZMQkhrMlBjTmpobDAwc0lrUFNZd2NqZnlFRzhDU2VfdThPNF96dW5UckVacHdhVWZJTlhJQzFrZ215NTNZaXFTaU1oanN2bTVJR0RVZFpMWG0zUm51My1wckdVTWhJZmJVSV85WUhHNHJxakd1bW5iWTU4aXFWQmkzZnBfa0tad0Exdzl5eExNN2RLd0JpUnU3WUdRNi1vaDB3SEVOZHE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR2ctaUFlZEp1YkFkMlpnTlZ0M3ZOUXF6T1FBZk9iaWpCM0plY0QyMkdZdlZzcXlXbDJpZjFfc3drZ0pTb1dWUEw3N2VrNG9WRmxhSWh1S3hMRnhpdms0TW5kak9udXA5aVcwZmNocWpmQi1yYXhZUlZZQmZmaWNLUnkyZ3FKVU44YzFBTk1lbEh0NS1VZWhiTjF6RndjTWhwYnhBZEE3TjEtWFRXWF96a05sMGhETDd5ZkVyZ0F1N3ljLUZWUWM3WTVwQksxR1E1ZmtKSTlLR3JqRWdUX0tMZGVoMk41SjZXRDc0QzZTeENuUkN1Yk5YSDRBYnU1QTJReHg4WG5n0gGGAkFVX3lxTE1HZy1pQWVkSnViQWQyWmdOVnQzdk5RcXpPUUFmT2JpakIzSmVjRDIyR1l2VnNxeVdsMmlmMV9zd2tnSlNvV1ZQTDc3ZWs0b1ZGbGFJaHVLeExGeGl2azRNbmRqT251cDlpVzBmY2hxamZCLXJheFlSVllCZmZpY0tSeTJncUpVTjhjMUFOTWVsSHQ1LVVlaGJOMXpGd2NNaHBieEFkQTdOMS1YVFdYX3prTmwwaERMN3lmRXJnQXU3eWMtRlZRYzdZNXBCSzFHUTVma0pJOUtHcmpFZ1RfS0xkZWgyTjVKNldENzRDNlN4Q25SQ3ViTlhINEFidTVBMlF4eDhYbmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -6034,51 +6034,51 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Cidade do século 9, suspensa sobre falésias de calcário, atrai turistas no Mediterrâneo - Terra</t>
+          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>17/05/2026 18:07</t>
+          <t>17/05/2026 14:07</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR2ctaUFlZEp1YkFkMlpnTlZ0M3ZOUXF6T1FBZk9iaWpCM0plY0QyMkdZdlZzcXlXbDJpZjFfc3drZ0pTb1dWUEw3N2VrNG9WRmxhSWh1S3hMRnhpdms0TW5kak9udXA5aVcwZmNocWpmQi1yYXhZUlZZQmZmaWNLUnkyZ3FKVU44YzFBTk1lbEh0NS1VZWhiTjF6RndjTWhwYnhBZEE3TjEtWFRXWF96a05sMGhETDd5ZkVyZ0F1N3ljLUZWUWM3WTVwQksxR1E1ZmtKSTlLR3JqRWdUX0tMZGVoMk41SjZXRDc0QzZTeENuUkN1Yk5YSDRBYnU1QTJReHg4WG5n0gGGAkFVX3lxTE1HZy1pQWVkSnViQWQyWmdOVnQzdk5RcXpPUUFmT2JpakIzSmVjRDIyR1l2VnNxeVdsMmlmMV9zd2tnSlNvV1ZQTDc3ZWs0b1ZGbGFJaHVLeExGeGl2azRNbmRqT251cDlpVzBmY2hxamZCLXJheFlSVllCZmZpY0tSeTJncUpVTjhjMUFOTWVsSHQ1LVVlaGJOMXpGd2NNaHBieEFkQTdOMS1YVFdYX3prTmwwaERMN3lmRXJnQXU3eWMtRlZRYzdZNXBCSzFHUTVma0pJOUtHcmpFZ1RfS0xkZWgyTjVKNldENzRDNlN4Q25SQ3ViTlhINEFidTVBMlF4eDhYbmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Copa do Calcário 2026 começa em abril - FERJ</t>
+          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>17/05/2026 14:07</t>
+          <t>15/05/2026 04:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE11Y1dOay0tTWZ4bzdMS0dUbEFxam5TLTBoeXVtbzFfQ25oZm9FSzgzSW9nTmZ5MGdHdFl3OUM4RUR1M1JMN1Z4SzRGYzZiYS0xcWlYcU5pTE1mLVpFNi1DUmUyZXZ5SjJac1lyamZkWlI5Rlk0a3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>BARRAGENS | CMOC Brasil Unidade Ouro promove workshop de segurança - Brasil Mineral</t>
+          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6088,51 +6088,51 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOdDFyUHVYU1pJeTZZNzNxUlR2N0RyTlBIaldQT1BORENXVjZ5QmYzMDM5Z2NTUGg4Z0Q4aEtJWktlUS1Ed3c3WjJqOHNwZVhWLTN3c3d4OFVXUWJBNndDa1V5YUliYkNpSWpYN08xWld5MjJUVFVLRmRTVmNfQktGUVppWE9sRExYMTdjZUwxQkdoQmVpUFNsaWdCSjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Reunião discute bônus e estabilidade de trabalhadores afetados pela Mosaic - Prefeitura de Araxá</t>
+          <t>O obstáculo virou o caminho - CNN Brasil</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>15/05/2026 04:00</t>
+          <t>14/05/2026 04:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOa0hzTkNxSFM2TDh6d24yeVVEb1RzU2dvOTJRRmR3OHRXMl9yNjk2TjNhcEQwLVF4TlBRME9OUVR6ZmFVOTdNZVF4MGZWNDU3dDl5bV9BWk9IcXlUMTZqYmYzUnhibHRQei1WeklNLU1yNkhwRmJqNjBOTi05QkJoUXJsZnJqUEtFZXlIREtZNVBic1N2RkJVMWVVb1BwZGRGZGNodXBDbUNUS2MydU9EUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>O obstáculo virou o caminho - CNN Brasil</t>
+          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>14/05/2026 04:00</t>
+          <t>13/05/2026 04:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPY1JJbEVNOFRhMXg1R2FSNk43TVlIb0NUUGhlUlRERmxGYk5EZk01OVI5X0JxZEh0QU12OHJqUFhvRHJXNGZjaU4zcENiMVZnMDdjdk5HQmNpX2VvVFJ0OXVCRk1fUnNmTWdLdjFoc3RoYmQ0X0dVM25nWXJnWS1sazFhREZubTkyWVBldEdoMThKVjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOcnB4VWxYOXVnTVhBMjJoMDcwZGZIdHpnMzZ2dmNNelgycGxSdGpPcDcwS0ZGdW9JODJZNXlZcExhRmZGTloxdlYxTnJlSktSWTQ4Mk85ZWhObFRIN2VGV3lpSmJpeGNwbGN1ZG44VHoxSnZpaVI0VFV2TWJkSWV2QldxM1U3VWpLV0ZQWmkzeVNrSEhxR25SOU1jdFN2ZmJWZ3c?oc=5</t>
         </is>
       </c>
     </row>
@@ -6144,29 +6144,29 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil no menor valor para abril em 7 anos - Farmnews</t>
+          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>13/05/2026 04:00</t>
+          <t>12/05/2026 04:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOcnB4VWxYOXVnTVhBMjJoMDcwZGZIdHpnMzZ2dmNNelgycGxSdGpPcDcwS0ZGdW9JODJZNXlZcExhRmZGTloxdlYxTnJlSktSWTQ4Mk85ZWhObFRIN2VGV3lpSmJpeGNwbGN1ZG44VHoxSnZpaVI0VFV2TWJkSWV2QldxM1U3VWpLV0ZQWmkzeVNrSEhxR25SOU1jdFN2ZmJWZ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
+          <t>Ureia cai após meses de valorização - Agrolink</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6176,19 +6176,19 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Terça-feira 12 de Maio de 2026 - RRMAIS</t>
+          <t>Mosaic tem prejuízo milionário após encerrar operações em Araxá e Patrocínio - JM Online</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6198,85 +6198,85 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxNeURCS1JiQlhQZUtzbnpfTGxYdXFESFN3MEtOQXI5N0oyU19nbTJxY0tMMkhDNm05cTlfVm40UUhKUHNFYWVFRldqbjRDVTNycFJZOEx2Ti1UMmcxeEg5elhNUllPaXFpSDY0TEIyY2FLUllmOVBPNWJzUTZpdUhUOWxEWDdWRlpzN0VYblhHaTMyNHNaS0JlWDRDM3dFUkxiajdkVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNQkZGXzhCdVRrM3pfOEFZWF9YemljbG94ZWM0TEt5MmVRZ1plcEpwVjNhZGl4S3BnMEhjMXp6T3RPVFlxNzZZQS1ZNTlGUXVEdktVdkZaT3N6dUFyNEJtM0FRQ2p5SVBoY1lxY05FODRTUlhpOWdUZTdqRURFODhVa1hoOXZRWkVva2R6X1E5LTRVT0trcl9DMnZuWGJSdG53RjNBVzg4UC1NVEZHTFVqamt1UUI1QdIBvgFBVV95cUxPM3BIRjRldGZwM3RMSXRuTmk4S0NodGdXRmFZcEJHaTgtYkNRTEl2VDFoYnNnZkxndHB2YVdNX3ZmRVEyWlNhM1hheWFuNDh1Qlg2b2IxMkJMNDlDQnVkaUdRWURfQ0ZtZENVRUt0cHhPZkY2UFlDcDdTTEFGeG5CQlZ2OUU1bnhyMjg3cFBNQVlMZTNLU0tOUVM0TzRrUlhmS3V6MjlLR0JLT0ZQZGhydkwxQ3RPS25LWkQ5UTBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Ureia cai após meses de valorização - Agrolink</t>
+          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Prefeitura de Paranaguá</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>11/05/2026 13:42</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOamEzNkdxNEZfcGNucldUQll1RjZYQzBwZE1sYlh4Ty1MaFdpSUZuckVHTk9uVXU1WTRPLTRLZ2Z1eEVVVU1Wa0haSXZURmhycm0tTEJubGJnZEE3ODRaQmt6bUVkUVlJTkVJWDlTUUVxSWZid3RzOHBhelAwZ082WGs3dkxnMXVwaU9PbQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Novo revestimento de ureia controla liberação e reduz perdas - Agrolink</t>
+          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>12/05/2026 04:00</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQZ01QdFBLLUUtYkI4VmRsYkpIMF9KZ0x4QV9fWGR1ak1YWTQ4enZhMkFCbkQ2dmJFbHgtVlRObml5X1Z3VWZVcnlrd2xSVFlJdzl3ZGdzTjNKUnM1b1pacXlZRjhxZ2RrNEZXWmVaZHBxdzZuMGFyNFJaVEhnVmtOYjJiMVV6enZUODk3bEgzdzRBME5rMkQ2a1NIbklNeGVmWlJ6YWZUamYwQTB4SThBLWxXMzhFcG1jLXFYR3Y5WFd2d3pFT2psV2ItaXRDelhYeURN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Prefeitura de Paranaguá e Mosaic inauguram unidade do programa Horta Educa na Escola Eva Cavani - Prefeitura de Paranaguá</t>
+          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>11/05/2026 13:42</t>
+          <t>11/05/2026 04:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE54NVh6Qmh3SVFMbFV1Qng5SGdpT3JPSXVHNmt4WDhxdVpGV1l6T3VyVHR6WXVsNEtSX2FUWURvSnNmZzFVTmt0WE9ReEd2dTZvQmpuMEpBSnFncjA4VEQ0aHFCdU55cmM3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
+          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>“Não há fosfato suficiente para atender à demanda global”, alerta CEO da Mosaic - The AgriBiz</t>
+          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOVDBiNGg1Yk1uby1oMlVYeW1ZU2VVQUdUUlNNRXYzWUV5OF9tV2wxdXJZWnNQZ2Jpc0ZRNW14UmwyMF9mSVM5U29iVnZqdkhGMk9ZaUN4VzZNTzA0NTlNX3JJTnVMSDNlc3p4M1F3Ml9EX1AzaERiMzFNQjFJVDd0UUtjanZzNXhSVTZoN09mMl8yOGh2M0dYTXpwV1lScGx1dlVxc3dERnkxeHdIRnM4ZTVpU29abkNzLXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
         </is>
       </c>
     </row>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 258 milhões no trimestre - CNN Brasil</t>
+          <t>Mosaic registra prejuízo de US$ 258 milhões no primeiro trimestre - Valor Econômico</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -6352,19 +6352,19 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOZC1GeGtLMy0wY2l4ay1zQ3RUblZncTFoTzdEM2s3b3dQeEdWQjZ5X2ZDLTI3VDNJZkdwQTl0S3N2UGN1OUw5Q2Vla19aS0p1RV91R3JMN0RzOVd3UGJnNGh0N1BCckRvSndoMmxYMERNU2RIQ0wwRlR6U19nb2h6bHJoWEEyeWxIN0xrYnFfdTlFT3VMMDlrMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNDNrdFRsS2JuRFptTkVYV0YyVUtodDQ0c042RjJoQy16R09COHFtYmUyekVpc042X25qN2Nkc2x4bmFlTnBSa0htTGVCSHk1bTBMcGs1UlRWaHJLV1VzaTZJNy1YQy1VQ2w3T2tCOTJxbEt2OVB3X081VDFoVnlod2lCQVdQa2RSZ2dHd2JBTjVJTUJOUVJEQUZFVW9POTRhT1IwRm1YbzFKUHN2VGRlWmJJOXB3anM3Y3MtWmI5N2JKcFJy0gHTAUFVX3lxTFBVMWFxcFVLcTAwdDJ4YU1mVlh4MC1Fa3RKSmZWQ0poM01heVJ1MnRJczJJcm9NT244T2ViX0p4ZFg4QURiM3FMLUh1WEJmdTE4Y0Y5cEs2Q3R1aDhPX0tvRlM2QzB5MXFyS3drZll4al9FanByZ0FZV3hNMlZja1VhV0stY0hpejczVzZrbGxyeEVBYkRVaWFCbmdwWW9Fa3FCb0YydmZiNGxsVmUyLXNNeVpmRV9XZG5LaGRGdmRqN1h0ZXFXa1VPZUVhdmNOMFQzV3M?oc=5</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lhoist avança na jornada sustentável com operação de caminhão elétrico - Jornal Correio Centro Oeste Arcos</t>
+          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -6374,73 +6374,73 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUzRlUV9RRTlBUlptdlZCSXNGbG1laThEN09iMTh3TkF0NUxHcTV4Ujd3bktsME9mY29RT2lUaXQ0dDhyeTBHSTZzM3R3ZldLbXhQRUxOd0ZsdndzUm1pSXUwZTRkY0Jfbkp1V3YyTjIydFppYk83ODhoRUlVMlNOVWdNem5LcS1qRWZ0bGlGVGdGcnk0clNVbGpKV2VVOXNs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>COMMODITIES | Enxofre impacta aumento do preço do níquel na Indonésia - Brasil Mineral</t>
+          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>10/05/2026 04:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQVkZIWHBTbDkyUzZ6RktMXzZBenVZRWFfN1NTeUxRaDJGSkxTVmlmamFpM2ZxdjlTQWV6WHJtMG9EU1Jzd094RnpXQVZDQ0lQWVhTWXM2bDYtNWRNYkdpcFlhWUtGN0tvWXR4SXJXUTNlcWhKQzBxWXJGalV2Zk1rX1B4LXpyNEN0b3lEWkZwQ3lLUnB4VGM0ZnA3clFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Demanda fraca derruba preços da ureia mas não destrava mercado - CNN Brasil</t>
+          <t>aumento de 4,62% em um único dia! Enxofre atinge alta de ano novo - Sunsirs</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>11/05/2026 04:00</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxONnJwX0hzX1RaX3dlVGxVVjVBczRMV3Jtd1dBaXBNeU4tVUFJLU9iNGNPY0JKSGFxUjBUVDlONWNvNDRrd1NLOTFWYTJPNjFhVGVIUW4xVDNyWlE3OVlmWjhQWUgyZk0wOU56bTJfcTJ3dkJCYU9Ub0JSUVlMWDFCT0txUzU0ZlJJNXpTMGlnRUw1cjhwd25rYjAyNjBvdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE42S2VCOFZMWWJZT285aGYybkdYWWNVOVdIa0VvWVJNUnJDSmJsX2JSV3RNaDVFdW4wSS1qRGUyTVE3eGhXM0tfRS1JLWpPUFE5Q1VoMnJIejM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Macuco e Monerá lideram a Copa do Calcário - FERJ</t>
+          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>10/05/2026 04:00</t>
+          <t>08/05/2026 04:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOWG5SM0pRYV8yeVhlRzFwVlBLUG5XRmNYTWpMMEdaRFd2OFlBT2d3WHIwcmNJMVlWRkNONTI4b0hpeVZrdlVxc01uTEoyUm92WnQ4R2JSTGx4M1ZnaWZtRlB2UkFRZjRybjhwaWdzRDB0Ym1sdy1vRGdDN2k0V1NtZXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>aumento de 4,62% em um único dia! Enxofre atinge alta de ano novo - Sunsirs</t>
+          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -6462,85 +6462,85 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE42S2VCOFZMWWJZT285aGYybkdYWWNVOVdIa0VvWVJNUnJDSmJsX2JSV3RNaDVFdW4wSS1qRGUyTVE3eGhXM0tfRS1JLWpPUFE5Q1VoMnJIejM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Carga de enxofre é derramada na Rodovia Ayrton Senna após acidente entre dois caminhões em Itaquaquecetuba - G1</t>
+          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>06/05/2026 11:23</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPMjJXYVBLSHRScWpkR1pXa1F4R1Q2R1N5UzczQ3JGSkxaaGJrOUc5aGVzbU4xZTJ6WVVBMTVJeWJLS0l3VmlUMExTT09oUmFEbUR0ZldLTXUwSmJ2UkR1MFVCUkN2dzMzLWxtTkNfOGh5aFdyNjJzVUM2Wkgyc1dfcEJDUnZCQk4xUUR5cjZpT2VfNHlxVUFZYVphTTNWd2Y1U1NUTy1fcnFIM2p6S3dpR1BfMHRKeG1yS2ppVm5sTmMwZk3SAdIBQVVfeXFMTmVyUjFibUtlTnhSRkRwbFl2LVQ2RE9BdTdQRUM0Z2dSUmF6RnFRUlNrS3pIZzNBTy10NDdEWXBNYTVJZlB6X05CeTQycjdjelI4c1VHZ2QxRDdia0s5NFR0b3p1aGZPUi1RQlBiTDlRY3RLekdXXzBBdzQ2RUVLRDRhNGxlSUZBbjJXVlRKRkV1ZjhxXzlkanRqZmdERzZYemJnOFRzRWNLTHd1SnIxSmk0T3dtT2NhWHJiTjRUM0ZUbkVIdmZUS3R4OVJueS1LbzRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Carga de enxofre cai na pista da Rodovia Ayrton Senna após acidente - G1</t>
+          <t>EUA ainda precisam importar ureia - Agrolink</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>08/05/2026 04:00</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPVURlU1pkY2xFUkxKczI2WGNkZnJBMk1MOHhSRTI2ZEJWMUhfdjBFU1F1TGpMbUl6eVkxc1FWOWlheHNpN1hIQ3NRejI1Y2dsbHZwTS1fSmlJZnFtWWZuM2gtUUZhblBKdGFMelF1cTdLN0xJUWd2dkh2UUQwWGlBUGgyTDdtLWtVRXJrc3FXX3pmZENBb0RKc21MVndkUHR6VGxYM0RjN3FMelhpOF9zQmgtTkNnNy01QVl1ZFg2eXV1b3MzdUxFYTFPeUZWQdIB3AFBVV95cUxNNVFUeU9TN3Z2S3N5M240dmZOTmg3VnNjX1p4NzZkdXl5NU4zc0dFbGEySjJ3enNQb3VPSkdGdGJBVHVBZ2dLa3hxUnNsX1JPQmNiX2RKVEE2SE1KemhlbnhPLTJRc3U5VnRFeVpXdThGNFlXZDk0YjlyazlxTWNfT3o3R2RfVVBrSi1TNWlJQjQ1VnY2b0tienVBSlpvbHhJbWtCLU0xamNJWTRMLTA0bmFLZ2dhRm1SSm9VVjI2ZmtobWxpd3J5aDNFajFOODJ2U3NyVnNJNjFLRzQy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Memórias do calcário: Château Pavie Macquin renasce em Saint-Émilion - Revista ADEGA ·</t>
+          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>06/05/2026 11:23</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQaC1QaG1CQnVDUFU4N2JNTUp5Vld2TzBOZXFsdDU4UXZ4c0tDZXZRX2hGVDl2UlRoTjFEN0VCNlRrUU5qejV3cUpkcW1XdFBmcXlNeWVCSU9qdVV1TWpRdUlNZEstaG4yd1hrTHJSbmxLZkJGSF9zUXlyM3FVZjhHaEdROHVMeWdqLVNuMVRnMmdkOWpRMl9xQTlwa1RKNWlvLWRybHZrUDJ0bVBkYXA5atIBtgFBVV95cUxOQV9OR2ZkY0wtR0pvX05MVVNxZm9KaG1Cb3BCT21WMHFoak1kVF8zYlBSMl9NeTVrT0dubk5uWFVTMENMemQtSDJwa3p0TC1oejhEdmRidnBHNzB2OV9LUHVNTnJueTNFUi1GRm9wSnZwdGVJTUIteENFOHZ2czhFSllaMFk4aF95LVVtMXV3NGhqeHZBbmxBZkRObzMwMjMtUmRaN2dBVldfZGt0ZlRXQmZDejF0Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>EUA ainda precisam importar ureia - Agrolink</t>
+          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -6550,51 +6550,51 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOcTNpc1B0OVBQQ29VaHJMX1oyTFJsZVdIQ2wtN3pYcEsyd3A1S3U1TmpPb0NZeFdUWWVjS2ZZT24wYlhib1l4dFZ6OUFhNUp5Q2QxLUpDdU5SMjh0QUtJc3dfdGl0Umo2SlJ5M08tbVYwT3czRHZERFZBUlpOM3IwQkFlTTM1dGthN1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Alta do enxofre pressiona uso de fosfatado no país - Agrolink</t>
+          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPUUZENVBnUk80LW5TNnBRdFNyeU12V2xuTnpKT1k1dk1ySmhXWmJZU0V4SDF4dnduV3Exck9vUTI4SU9OX3BROHc1NG1Jbm82S2FQVTEzdE9lR2xwV2h2ZGhGWGJvYW1tXzdNSHR4ZGExRWU4WFRXZnZkb2x3UWV1OFFPVFBVTWFibkZDLVZCMUpKRExEa2RyVUdsR3pCT0gx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia para 2026 cai forte no início de maio - Farmnews</t>
+          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>04/05/2026 04:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQZENuS3MwY1NDNlVENVlLT3FhbGpTMUZacGNmc3lKR2NINjRRdkNGUndsRW1QaEhPVG1yMkx5eG5mYTRpMENzbXRVVVlZSXFPQnJKMF9UbjBNeW1xTTl0cXdjOEpMQk5CaktWT0c0anZvVEFwQkQ3LXdhRWkzNXN5eE9yTldTUzg5Ul9QLWo2WWZDbk5BbUMw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcjJSS2JUOW9EbGNBMlhnOW05Q1NodTh6Sks5a21QYzFJTGRGYnlmamIzMmxfNVNaOXRqQVA1OTg4NENjVHZ6U19FVjZSYjQwOG11Z0o5YW82VGs3ZXRaQWp5UHJqSk0wVHRZcU11R0pZaVpMZ1J4ZC1veVFpd1puc0V5RWdqQWE0VXhicEd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
+          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Preço da ureia cai pela segunda semana seguida e sinaliza perda de força no mercado global - Agrolink</t>
+          <t>Preços da ureia começam a desacelerar após forte alta com conflito - CNN Brasil</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQeU1RODBJSmxweldkLWVpUHpmcXp6OUhQQUV3T2I1bER1c3k3ZFRPb21GaEh5OXZucGhEOEFQVGdyUTZlVE5rWFZTdjdFQnNkS09hZUVsc045b0pBRV96QlBYVnQyUjlVU0ZlNGVRZFQtblNyVTYtbnpQeTVQaGVsazVOWWhCZXQzZFY0SElsWlBVSEZNWU4yRG1ub2MwQ25vSGt6OFVQOG9FcXNIbUx4QlJlWnlTTXQ3cVRTems3dGxwMklFTEpLWE5lWTlYXzJNalZJMXlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPd0VHZGk0YmpqT3Jzd0hnMVRySDYzYU9wZC1ieXJPc1dPX081SkpEdDZNUUNBYUJMWlNNVk5mQVp0eEdPNVA3d1B2d1VTREo3QmJvYkQ1YjZfdG9zMHgzTnludnA4U1VFcUNCd1d0SjVzWDdYd0JNM2xSLWs1czZmcTVPZllkTkdDbFlPblQ4MEttaUdySWo1enhoakxocEk5SVpF?oc=5</t>
         </is>
       </c>
     </row>
@@ -6711,22 +6711,22 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Rodada quente e com muitos gols na Copa do Calcário - FERJ</t>
+          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>01/05/2026 04:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQcjJSS2JUOW9EbGNBMlhnOW05Q1NodTh6Sks5a21QYzFJTGRGYnlmamIzMmxfNVNaOXRqQVA1OTg4NENjVHZ6U19FVjZSYjQwOG11Z0o5YW82VGs3ZXRaQWp5UHJqSk0wVHRZcU11R0pZaVpMZ1J4ZC1veVFpd1puc0V5RWdqQWE0VXhicEd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
         </is>
       </c>
     </row>
@@ -6738,17 +6738,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Após disparada, ureia perde sustentação e inicia movimento de queda global - Notícias Agrícolas</t>
+          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>04/05/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxONTVhVThiOV9DeDdTeWhZaFR1dmZZWm5GMmpYSXR3SHFBT0U3MWItc2xEcGRPZVBLXzRvbmNqY2J3TlcxM243aFA0RElmS0djdmhzTC03bnZjQUotUnZkQ1REcExJYmxHTUlkZkxyOGtWUHpRZC14eVMtSGszNndqWTc2R3VhUlZhQnFYQXUxR2ZUdk01MUxFUVlKaWMyX1NBVWFtbU1rNnhMNTBfYWxoTm9wX1daT3MyU1ExNTlNU1pOb25FbGFBSy1QWFgzX3hheDRWSVdfNTlXRnPSAeABQVVfeXFMTnQ0NzRKRFItenRCVzlHMFJMUWNBem1GQ1lTWkdHZm54cy11cURxamdwMHp5MUJ2bVZmWVRoWThDejhvTVlWYU53OHBpMTNmYnZ1ZWNNQ2xDWW5ILUVmUDJBMktfRjRYc3ZSeUJXWU5PNEpKUDFoeU52RmZSRlBZcUVXV2p4Q3FCel9iTTU2aVV6V29nZXdTNmdlMnBxUWFqNWhtbnc3ZmpqZm5IUHFvYnJueFpzMldlcnBxSXZHbUxjNHdTRDFCRl9zSTBpdDJGWGlHMmpfRkVxRm1sOHJmTXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
         </is>
       </c>
     </row>
@@ -6760,17 +6760,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Petrobras volta a produzir ureia em fábrica de fertilizante no Paraná - Agrolink</t>
+          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>01/05/2026 04:00</t>
+          <t>30/04/2026 04:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQalJiUHVrZVg1UlJ3RzBYSkI4QllFcll4V2pPbmRZVEhYalpUdHc5UHgwVmRTZ2pqbEpCaGlIV2xVc0RIN3NRM1BlYmxSdXlzR3hNYkU0TThNazhJbXNZSnQ5SmdNbEpaODBrX2sxZlFOam95NUI2di03ZEctcDlJUDlEMzFIMWNIdzhHMXl2eG1wQmhQTmNHMEcyTXh0R1NQQUliRjdrendYdXpDWVA1ZzFkRnlqU3Y2SVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, unidade que estava hibernada desde 2020 | Empresas - Valor Econômico</t>
+          <t>Para reduzir dependência externa, Petrobras volta a produzir ureia no PR - Monitor Mercantil</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxNcVNQNzR3X3ZiZC1IbXR0Q1U5M3d4TXVWcTNMRU1GOGhOd0pKYkpXeUpnS2VkcHJieWpNVDhUdnpDeFlud29jWEFSZ2Z1MjJIVE90QmpIc2NSbkxlbG5iQW1xeVZsU1hiS0RrR2hDTDVmU3duTFpBTGRjbGRtLWdjWkF1cnFtVU1YRkN4VTNOU1JLZm5hakh0RWFsblV2SlNhT1d2djhINGN4MTlSX0xfZXBncFRmbUVVdlppWFlhSXF5T2xuMnFiNWlla1VkcFVPWi02WVNkOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNaFN6dXlpRHRuQWNMd3NybU45VF9fdkNMQnpOTmd2bGhMZ1hYem9qMmlnNTFNNWM4X0RYak56XzNpaW01NFJtalZ2TFp6STNGanpKUEhLREFkejZackdaRUN6MmRUS2FteUxpSmFpTlpfTG5oV1JncDBqZjFCaFpCRlIxeWVaR1J1blJrbkdZT1cwUVd5ZW9nRlozVlRObWR0Q1ZUMERRQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Para reduzir dependência externa, Petrobras volta a produzir ureia no PR - Monitor Mercantil</t>
+          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNaFN6dXlpRHRuQWNMd3NybU45VF9fdkNMQnpOTmd2bGhMZ1hYem9qMmlnNTFNNWM4X0RYak56XzNpaW01NFJtalZ2TFp6STNGanpKUEhLREFkejZackdaRUN6MmRUS2FteUxpSmFpTlpfTG5oV1JncDBqZjFCaFpCRlIxeWVaR1J1blJrbkdZT1cwUVd5ZW9nRlozVlRObWR0Q1ZUMERRQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia na Ansa, em Araucária (PR) - Agência Petrobras de Notícias</t>
+          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -6880,19 +6880,19 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQZUpEZngwb2IyTnlKcmZ2dFFGUkdPLU51QS0wcC1laTUwaktaVWtfa19lX3ptZ2hLUnhvQWpBdUhBLWZoY252VGpUTFUtb05jU21zZjdhcXdWY2tPRXBXMWt5TXJoZ0VrNko1SWs2MWQyeWtMX1BWeXA4aElIb09odjVESV85Ry0zYWRRVXd6b1JRVEFxQjlBQlIzVHp5Q3dXNkc5ZVRZbUtYb3UyRGtXd2RjREZEWXh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
+          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -6902,19 +6902,19 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Petrobras inicia produção de ureia em unidade no Paraná - InfoMoney</t>
+          <t>Mercado de fertilizantes vive momento mais difícil em décadas, diz Mosaic - The AgriBiz</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -6924,51 +6924,51 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOR2lLUEZxMlhlTzhWUGp5WmZaaFA2RV80WkpYazZtVXd2ZldSM2ZzaFBHNnFNTFpIZ1JVLTdZWUxnMzJMOERZTHV6SXN4ZDJieFdqS05ZWFpvbVdMVXRqNmo4VWZ1OXpMZDl5bS14UjgtQ1RtVmRFZmZmZmg4cXhlLXptYjRjMzNPTEEzNFNLRUxCRjREOTRoLXJR0gGfAUFVX3lxTFBnQUE0ZEJtcV9KYXBNYXZzVXlQSjRaZzFfWlRKcUM5R2hHc0dYUkVnM25TSFQteExCc3FZODF1WFhNcGk0VExmcUx3M3BFejYtNENYUmpwYWtpQ2Q4Z0JJd3RUbUpqMFY5Tml5LU5vZUVMb0praTRCSFY5UmJDakFlcy1qMGxFU1FtbnRId3dxTnJJUllvWmdCM19kNGw1cw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNZXpsRmRrRjkycUpIaUJaY1V2cWxzelVBZnAtTm5ETEdJY1lQTUUtTHFVMkNBTkZyem9xVHUtS1cyaVpmSHdnc3doMTdFWkdGTThsbEJNU3dFSDVIRjZIaUlxODlHd2F1cUdJU3NuTGpQT01OMUN3MnhkR3o4S2gwd1dMMWR2QV81X2tOZ21PS2JIbU5STlAzT1hNV0wyczdVbHlLMGtFVFVpYXlHMnFyNk1UVmo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Ansa retoma produção de ureia no Paraná após R$ 870 milhões de investimento - CNN Brasil</t>
+          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>29/04/2026 04:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPRVZqOUg0Y2U1WWVlQm55NTlPcXdFMVFzM1BMdjJ5V3NRNDNsZ0dGb0JDVGU4LXlOSEJ5SUk2UXpOR0hhZ2pVTER2ZzBCREwwRWFaeWZ4ZkVweHQtbjhRNndfMUhCZnpDcnptcmNsYjBqelFOem5IZHB4UW5hcGQyRWdjUFpjNk1OT1BILTV0bk04VHBrSTJrTU1uLXFfYml6elA3OUVuUC1ya0QyRlBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Fafen PR volta a produzir ureia: fertilizante na fábrica é comida na mesa! - FUP - Federação Única dos Petroleiros</t>
+          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>30/04/2026 04:00</t>
+          <t>28/04/2026 04:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPcmtibVp2QVZDY19yQXhVZC1ybWpjb0dqUXhGMlo5OFhodXpBczFOWThhLTc3RHBvdHNxVU9iSXZyQnVMdm8xUmtWbkNNcHRTWUYweXNpcTc3bUI5Ym56Z1pzckdTazllVFRzTzVrLUVJYm5ydDlkXy1mclNEdTlncWVFN0g5U1JfbnBoTmVzTTE1eHJCVDdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -6980,39 +6980,39 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Mosaic vê produtor mais cauteloso e reforça aposta em fertilizantes biológicos - Estadão</t>
+          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral News</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>29/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOaUtJV3gtWHNiUFBmZkJObWRoUWs2eUFKakh3dzhRRVhWcERRVDR5Mlc3Y3JCMUpsLWtWNW9KLXEzdkdiWEtQTUJxVTRrNXVqbzhCeGotdEM1cV9udEVwTGItQjRCZzV4Z242cFhULXVVV08wb1ZHcHhPLU01QWR4SVh4bTlqRUpsRWlrYjFWS3lVRTB3blNKeG14Q2VHU1FPTFRlcjRRZXdEUDDSAbABQVVfeXFMTTNmd01RNXBKS1ZYUllOYmYybzhnY1gyZFYwUnFVNlpyZFJNYlNwMWNOcG5Zd04zOHhnNlVZLUh6eUw5ekJ5XzZNbi12aGktMFFNY2ZEUVlBb01XY2VIMGhRTUQ1dU5sTzhfNURuOHhIclppUWdXOG8tV2UtT2w3ekZMUUlOMG1SVkpOS2VGS2plX2dMc09KNVdJZzBrdmNWcGREYU1LNldDYXl3WklhUTE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Unidade da CMOC assina acordo de US$ 1,7 bilhão para desenvolver mina de ouro e cobre no Equador - Valor Econômico</t>
+          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>28/04/2026 04:00</t>
+          <t>27/04/2026 04:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQWXI3c2c1Nkg5UTVTWkJ2QTVPNEd1Tmt0aUowbms1aFFrbEt3VTdtYTlQYWpNS0RiNVR1NU45ZWR6enpSdDhSbHZVNDNsSUdjSHJxbmxSUWt3U1NieGMtYTU0RDRtWXV2eUowSzdyem9UNUFfcHQwbXRqc2FldjZacDl0MVhFYmdJek9IWVZKWlRLbEoxUS1aTmVFdERsNHhhY180MzhhcERmWlhZZzc5VkhoSENab3JFUXM5V1pJUnZ6MVVWeVprbkpCUzQtTXIzRGtfd01rRWtQXzZFQUVKZXdSONIB8gFBVV95cUxOcEN2M0tCSFEtSVA4Y0ZtQV9EOWlFUERlR3JFb2RzZHFZVjVQWTZyUk9DZC1tTFpFcU8zeGNMR2pBRzl3ZDVKRElVa0RTTmxxZnNSWFJTNHVxX3c1b3FBX3JSLVhKcVdQY05BT1hRQ0ZibWJBWWttX2hDUjFFRk1TRTNBRV9DbGRSZHZkNlFIMkwtSlJNMkpoNTNGcVQ1ZVBSSDJpeW81eGRIT3B1aHM4alhLVkJPREk5cnFBdjdSSzZkMk9tVU1Oa3Fyd3ZrZWJKTXY5bDhFaWxfT3djU2FSdVpjclBXWHdLUml1MG5Ic2xHQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
+          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Copa do Calcário: Macuco lidera e disputa segue acirrada após nova rodada - Serra News</t>
+          <t>Macuco vence novamente e segue na liderança da Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7056,19 +7056,19 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNVzdyNUh6M1JxbnZwVjlaS0Z0Ui05cjJWMkg0bDlOWmNSeUFJYlNMMDFJT1VXSDMxbVlfWk1UYWJqSGNpOXVXQkRfMnBXN2FycUxjbF9HbGczY0x3MmdQekEyWEZNV3RkWFFkTlMxb3h4TmRvb2VDQU1STVd3aEtxbE9uZ0ZNT25lNzVVa1FDSWdWQXpGZjA3aTNaS2YyTjBI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPeVpoTFlKbDN4ZXlpQk9ETTNhUmROaVJFWEJqcklXb2ZyWUZhSzFRTENuZjg1aUxkaEgxSVNTNTc3a0ZtbUFkUUdCM1VCaTM3a0hmbTZLemZfN0hFT2t4TmM0SWVlQkk2S1BJWnVmdjlYUTFXWnFzU2hXS3FHZVNMMGxoUzdMWG1OMkY1UDRzYlBpVXJDM1IxT0RVUTBnQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Mosaic participará de audiência pública para apresentação de Estudos e Relatórios de Impacto de Vizinhança em Paranaguá - Folha do Litoral News</t>
+          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7078,29 +7078,29 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxQaWZoSTZ5YmdmWE41TjhTVkdiVXpuX2J1aElCUkZhWlA2Z0xRbEtMSVl3N1NOYk9xYjlBUGhtRFdocldac0QzaFdEejdNR1FqRlZuUnc3STJWWlcxQVJrVTctZUFMTGVIeUY2MGh1SHA4NllFMDF5VVdzU0phTHNPaDRLVHRjRVBvMEJPRzk5a2hiV3ZKWmhKSlhSWW52QWpJdjY0THBKb01maGc0bTNMN0ppUFZXSzFoWXZHTy1GUGswZFhfVU5wNHBrOWhkUTdkZlBReWxMRHdyRE9RMzZwenhqakhXSVhIaVBKekhRT2pIcG9XQXhHQXJiMFo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Ureia acumula alta de 63% com Guerra no Oriente Médio - Canal Rural</t>
+          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>24/04/2026 04:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNeXdPY2EtX2lWTng0WWcycU1zNjlEeEYtd1RiVmFpd3Y4ZzJOeGhpOUdZRnBSREVDVFBVM3g0QkNNRFBfRDl5V3pmRG1DTzFESWgwQzI2amx6NGpCR0FVM3JTMC05cDhtNUtEdXotU3JLMzNiQkJpN0dQVmRkQWZHSTR3OVdMNUVFQllvdm16b3E2MUctQjN1MTRFQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
         </is>
       </c>
     </row>
@@ -7112,39 +7112,39 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Uma nova Mosaic, com menos ativos, mais bioinsumos e “sem plano de deixar o Brasil” - AgFeed</t>
+          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>27/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxQOGk5c2lwZUhVRXBjb2VSNW5xU283VzdIRl9JTDU0RFk5bEZGM0ZxVEJaaWJERkp3TUtNY0FxX1NpTUlGSWxYTzl5RVRxcEdid0NNaEhDS3RXTjQzQkp0ZjFlNGhsUHd4V1ZjaVBXZWFTMS1qMjctLXZGcU9xeVdMTGJMMzZDQkVOUlA3TU0yNl9hSDFyejloZHRXT0lfRUtlN0g2S1JGQjdSRlFaOXkycA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Margem do córrego do Enxofre, no Jardim Conceição, começa a receber muro de gabião para conter erosão - Portal do Município de Piracicaba</t>
+          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>24/04/2026 04:00</t>
+          <t>22/04/2026 04:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNRVJObFdmcnE3SmlfbERhbXhJa2hkd2taSzQxcGVjSFp1bGpSWjh2a25nanBtNGRsT0JYS0xvQkZlZ0JxSF85UktCU3hyN3RBbVpPZ0V2dGd4Q0RUMEp4LTVqT0pkcTNUZHlHTnFVeFZiWmozYUtqNnhkY0VWTjZxRmh4RzhYTkd6SS1pYUxoVzJZLURDOEZwbG9EeXdwWXpCNHpkYTFCQUVYRlNYV3RscldENEI5QzhqQ1BFLXZoazZSU09TUEtvbzkwdmhsbElJUnkwRg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7173,12 +7173,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Vem aí mais uma aquisição no setor de terras raras no Brasil - O GLOBO</t>
+          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -7188,183 +7188,183 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOR1otWkdBQnhyYm10RnhmcW9jVEZlNGtDMWdkMTZVbFRTbTVCRWxYNkVWeWdnc0FwTEFOLTZPMGI5ZFo3bjkxdUgwdk04NF91blVDMk95S1BMWkg1ME1aTF9wOThmSFA1Z0hqYUl5X0ZVNS1nMHVEejhHS1FNdl8yT1FmNWhyR2JrTlFncThDNTJlOXpHUERqNklYT2RVYW5ReC1nZFh2dnAwNDd2SFdxMTZTOS15U2N3ZkpVM09CWHbSAc8BQVVfeXFMT0xXcVV6WXVXbmo3NUhJMjFyVnBLTUdubUtWMVIxNFhpUEhhMDZ6dUNkelZ5WjZWb3U3b2g0WHdXX2dJTjhYdWN0WjhkS29ZTXdHaEZQLThyLXFuakhPUXVMdUhZc01NOFhNZHFNcDRyclZENndiNnl2OXVoOG83RTFaMG1KaEVKenBhTzdLQ0FXelNvbG5aZ3NmVlRyd1V3cUg0Zm5lZHFHY2gxX0EtdG9vVER3ekN2SEJraXRLekEtRWhrbEFZZndLOGRFVU84?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz ureia disparar e segue pressionando preços dos fertilizantes - Canal Rural</t>
+          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>21/04/2026 18:42</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOV0xwZE9OSUFnQ0FXRzZvZlBXamZsaHRVT3Z2T1l3YlhUb2dmTnIxanhJdU9YOW1NMWFFQmlQWTlPc280cnRTRjZJVXpDWWZGUmlMaW5jbWd6OXE2VHFTZEs3UXp3cVFEOEphZWZXRVR0NlVHT3BGbHBQN3V0UVIyYmt4bURHdVJCcDJ1d2tJUzFKVzVQdDY1eHQ5ajFPQ2MtZzhwdlNGanozQjAyVVRpMk0wd0xJSmxCRGxHZmFqbTBjUEt2V1J5UG9fTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Brasil negocia compra de ureia da Indonésia - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>22/04/2026 04:00</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE5CQ1VCQnRUSzZMck1GX0xzeC1la0x1dndMTUJYTkNnMWR0LWxOMWMtQngwS3QzN0U0VEFTUUhfekhESDBXcVZrTGdnR3hoWm1ib1dPWXpjRWdlWTNXR3o4VVR6ek01ZnlLQlhxQXhHRkdSZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQnFTQVFGck1DaWNqWmRkcW1KY3dLTDJRNFRtNlRtREVUdHoyLXZyNWlHS2k1bDlBMzdyQnVOZVhfd2FqUXppTk9BU0Q2azBNcWxGYzlweG5NWVdGR1NpenFnMGdZSDk1QWVtMVdXNllwZElMQWFfZ1Y3R01RWkxSeWJPelZGSkg3dTlNUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Potássio e enxofre: os pilares da alfafa de alto rendimento e alta qualidade - Tessenderlo Kerley</t>
+          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>21/04/2026 18:42</t>
+          <t>20/04/2026 04:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNdWRPaG5oTlo5V0E4aG5RRG1CeTY0YVNrbWVFZndXMURZNTU3N1IxLVYzWEZMaEEzYmk4TXk0d3lYcVQtcExUYzZORlZRaENDNkZuVExMOEhnQ0MtRXozQ1d1U21NbUlWczV3dG53VlZhRU1WUmh2d3J5am9Fd1JoMGRJYjhRcVJjVWpUUU05QkJjQ2ZNYnRBS3FvMVVXMUQ3ZGEtOHVPOGVFcU1jRThuZVFaQTY5a3prQURWendYNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Macuco vence novamente e lidera a Copa do Calcário - FERJ</t>
+          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>17/04/2026 04:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPQnFTQVFGck1DaWNqWmRkcW1KY3dLTDJRNFRtNlRtREVUdHoyLXZyNWlHS2k1bDlBMzdyQnVOZVhfd2FqUXppTk9BU0Q2azBNcWxGYzlweG5NWVdGR1NpenFnMGdZSDk1QWVtMVdXNllwZElMQWFfZ1Y3R01RWkxSeWJPelZGSkg3dTlNUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Mosaic reestrutura ativos no País para manter eficiência - Estadão</t>
+          <t>Importância do enxofre na agricultura - Tessenderlo Kerley</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>20/04/2026 04:00</t>
+          <t>15/04/2026 19:32</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQYmstUHhzM3FUS2ZwQk5iRHEtWmpqYnBMVW1RZ1dpaVhQZVltbUZtU2V0eURVTGpLaGhYQXBLTTNacUprNDU2UGZkS1VQU09mN1RoZWpBMm9Da2dyOFZhU2hhUXdvTGJab2RJZDV1akZnN3pvajZhMng4NjBIZktUaVFhTmNNSlNucUhZMTdIb2YtdmY1X1VqaUNoaGFIaEtwOXFyWGxyLTBpT0w1dmtqeDdXTVAxX3dIZGfSAb8BQVVfeXFMT3lPSFRFUERhUmtkSHU4NV92MkVEY3RwcXlOY09mWkZnVG9RQmN6eU51Q2FyRkJXV0JGbGxxV3MxcWE4U3otX0pkUEhZWWp5TDBfZnhITmM1OUowVk1JeDdfbFd5cGQ4dW5PSWFfcGlQS1E0Y1hZRmpnUlNKY2RSU1d6RV9ZTElRendwTGluT0tFQ243b1NoZkFSSFo2RS1SM3FzekZvbDhsRGkwTGttR1dRUGNKRlBJM3I4TGxhOTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbVFvNXFNcE9MU25FN1hKS25KaUs0TWdEMnZJZHhsMVZicEUxU3FhR2RlN0UwQjV0T00tX05kSjZuWEdxVWd4NDNkTWR3VF9HLU14M2xEUC0ybEVpekEtbWthUDN5ZFZiN3ZxeUlNT2Q5TFJwaGxMYTlOMjhWUWEteXpIQU1DeXM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Prefeitura de Araxá e CBMM firmam parceria para aproveitamento de mão de obra da Mosaic - Prefeitura de Araxá</t>
+          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>17/04/2026 04:00</t>
+          <t>14/04/2026 04:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOcW9Ja2xnSUxXTmNMNnhTTjBsS1dHSFZwa0FFbFI5TEQ2UlBaTkYzQ0ZyMjNHQXh6NVBFLUpweHAyc205TDV6M2tHZjgwS1E0LUFiZ1c0bVlMUm5VRG9QeTJHUmFHLU9JVFFvdTM5RFhuOE1SNTVIUjhwb1lFWUNLTnVPWmViRFgtVlFoWlFmTkN6UVNPakNmUGN0RXNYSzE3RTlCdnNjbFhvbUMtcXhwV0ZUa0E5QTdUZFNieXZTbHI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Importância do enxofre na agricultura - Tessenderlo Kerley</t>
+          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>15/04/2026 19:32</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNbVFvNXFNcE9MU25FN1hKS25KaUs0TWdEMnZJZHhsMVZicEUxU3FhR2RlN0UwQjV0T00tX05kSjZuWEdxVWd4NDNkTWR3VF9HLU14M2xEUC0ybEVpekEtbWthUDN5ZFZiN3ZxeUlNT2Q5TFJwaGxMYTlOMjhWUWEteXpIQU1DeXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil volta a subir em março de 2026. Preço dispara! - Farmnews</t>
+          <t>CSN apresenta inovação sustentável no Vale do Café - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>14/04/2026 04:00</t>
+          <t>13/04/2026 04:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPczdiWDNkX2ppUzNiRklsRHVVemRScDFoWDRoNXcySHFwdnlPenhmN1JKOEdtUnJhNnozLV95bmtFaE9sZkg3WVlUcWRodjdVT0NYelBZbC1YMl9obV93ZmdLSmh3Y2lMN3Fzd3AtTjI4bmFWZVhZNVdDNGpjazI2d2tnYUpBZFhRMW9uX3R0TUdZME05UXJWc29JcjAyYWJ3c0pBUUlXc3BNZ0U2aVc5Y09SQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQW5tN1NZako4UHpaYzVCYklISkM1ZWZxWEJNazdiTmdSdi1aWVBFZXV3bTQxeDZlTHljTWNiblhsUzQ0LWplMTFnU2lCak90d1dLbXRRM1lBZ2xMUGJOUzAyeEFiendSRXI0cFVYMWlZMTZXVXBtZE5VWlJqSFpVbF82S2dKdw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7393,66 +7393,66 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>CSN apresenta inovação sustentável no Vale do Café - A Voz da Cidade</t>
+          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPQW5tN1NZako4UHpaYzVCYklISkM1ZWZxWEJNazdiTmdSdi1aWVBFZXV3bTQxeDZlTHljTWNiblhsUzQ0LWplMTFnU2lCak90d1dLbXRRM1lBZ2xMUGJOUzAyeEFiendSRXI0cFVYMWlZMTZXVXBtZE5VWlJqSFpVbF82S2dKdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Copa do Calcário começa com grandes jogos e celebração dos 24 anos da Liga de Macuco - FERJ</t>
+          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>13/04/2026 04:00</t>
+          <t>10/04/2026 04:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQS3Nfenl1TmpwNXFzTDhyTXJOM1JLeHlmRENybjZrWUpqak9GbTR0TDZ4dDJuQmw0eUhVWC1TVE43SHg5RWNUbTlFUDhWX0xJYldYZTZPUkNaMHoyS3lwVW1fSGZtbmFhSlNGU2xVZTdrNDg5MXVXeHpNQ1RnalI1ZWhlbkRySVZTcVdjMGtEMVFOdTJsU0t0TERPcnROOFkyWFVERDVTWVFFMUU0Ty02SndibEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona toda a cadeia - Agrolink</t>
+          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPVHdRX1FTQlk4azZQcGd3bERfUThfTENPWmZ4bnNuVkFCaEZDUlk0MmphdFBsdnZvam5jWGdZTDItbllDZzBNRHNGRmdTcGRxa0loRTVEYWhFR2RKc1FiUzktM3NXN1VJQUdDWFVPY0hPTzJDY0M3MzVYX05TLXhrUGJqMXNWaWYyZjZneFBpSk1UODRWbUJDaVZURFJkT09TNENHUmZn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7464,17 +7464,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>St George tem interesse em comprar ativos da Mosaic em Araxá, dizem fontes - CNN Brasil</t>
+          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>10/04/2026 04:00</t>
+          <t>09/04/2026 04:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONlhxcHQzelN2ZlNmOEhFbzI1SFN0TXdwbFNLbHk3Zl9WSEg3c3RTZFhvVWpBUWt1TnBoYjR5TG1SUDlRakNZRy1CcktIaFpyTWJicEdpdlN1dDVCUHJrR2JpLTJhbjFzTWE1RzYzUDc1VGo2ZDI0MHMtMDlaUXhVNUdLZmZxTWFsYW1ERm94bEVkNlZiRm15UjhLZUJlcjFaV1lqcW1JeGRmZmVjelE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
         </is>
       </c>
     </row>
@@ -7508,17 +7508,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operações em Minas Gerais e reduz produção de fertilizantes - Canal Rural</t>
+          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPNnVZeUNJdHBJOThrQTk2UW9EeXBQcFowX2p1TnlzS0I1Zmc4RGhkMkZIVXJTbUdsYUJKUGx0Y0ctTlAxUU1zcGNGU2ZxNWppSFRsaHU3aU9nNS0xZ093bkV3UlB3NzlVaXVDYTBCeXRJSmVoNUlSaktHRHhDbWF3dFdqSlpKOW9BU1pncGVBM3htRUVDbTZJVWo2S2VuQW1jWk1RZGlOdlpZM0RKZVFFMGVrSnBzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
         </is>
       </c>
     </row>
@@ -7530,17 +7530,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Mosaic anuncia paralisação em Araxá e Patrocínio com corte de funcionários e queda de 1 milhão de toneladas na produção de fosfato - G1</t>
+          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>09/04/2026 04:00</t>
+          <t>08/04/2026 04:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowJBVV95cUxPYVNQbkdxNThhSW1ydHJLMUlzcjQ1eE1vbFMyZVZiSVkzVE1KbC1lcEVYZnZnV3lLNW1wWG03VzJ4OWdQTTBBRDlDUzI4NXlmYlhmM0l6MjhJY2Z6Z2tLbjFHVHc1dW9aTlA5OEd3aEFaN2Y0MXlIdDNEM1BCQ3NqS1ZidzMtc2VSUWhBWVk0cUJIY2V4VWRsQnQyM1lPTmMyTEhFZmZ6ekNpQnFhM3FMRi1adFJpMmhjQWNVVWNZUFMyNnplbEgwOTZUZXg4d2hFYW9TUUJacldTbzR3QlVjRHpIYkFZZmJJRUJVdmRzdmtwbjE1VXdtRVd5OWlCOTZVZ1JidjgtQmdoOVYzdlZ0QWZqUVVYZDU5dU1rU3FaSjNvcWPSAbICQVVfeXFMT0NZVFdGbHgwUkYwU2xxM3RTWVd1YS1UdkVlc1VfS3pURUU5OTQ0NzVmekVFb01UUjVkbkVrVWJXaWZ5SUtNQTlfQWx2NWJ3emd3bXR4WkFEUmg0Z3hqa0RnLWk1YUVmZmNTLWpyQmhKSXVGM2pEbURiaDNHa1BDa3RvNGtoX3ItM2p3UEVoVXdHSjg2T0MxZExiVTk1RFlJaENuQU5hMnpabFZ3YTZ1SHZ2OVRjV2h4amRpVVBhYXBPZWVld1BkWVVLVThVVDBRSy11YWNWT01RV01MSXJYNS1aV29YUHZVZl9oazhEajBad1FkSmdKS01FcVlvYmxRcUtSVVR6am1qYU9UZHl4Y3o5ZlE3THNDb0lOMFIxVXJBOUF2TGVrSUJzeUlyMUFpczR3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
+          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
+          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -7584,19 +7584,19 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Mosaic planeja venda de ativos e paralisa operações após impacto do enxofre - CNN Brasil</t>
+          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWjZGTlNiamVJY2FzNVQzeG1ScDYyZ2JadVBQOW00WFpNYVNVWG9aVXNXS3p1b1lXMFZVVHNHNktHLVZmUS1teWlzWVhwVVJXV091eE91V3BiZ3E0emdVTzA1NW5LZlVxRnhKb0tmcE9kLU5ZaGhxdlZ2QjdMcXEzZXRWN1paZGhxYzNxa3d4ajZwSDkwR0Fvc3ZHYmgtandQbTF5eU95MFZEMEVjb0U0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews</t>
+          <t>Mosaic vai paralisar operações de fosfato no Brasil - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPbVRRUEJ0RXAyUWZwY1VnWXhDNTB2emJUa2VFVU5YYTZJaHJYSGlIODNkbExvel9VRldvU2JWbmdkTmZkZ196Z0hnUHpENFV5RExqSVNwTHByMlZwZUEyT3NLMW8wUl9KTFNiTFctNHozd2MzM2wtY2tTSElvRFhlQmtBdTgtV0trS1pjTWFnaFdwby1uanJ2MVMwcXltb2wwbXhOWUtYdWJuNXhLZ0dhYU81eWZ2UEYxQ19CeGV30gHDAUFVX3lxTE9GaWdoUGlIQVFfTWJGMlZTZ1JvLWZOc0JuTXJtekhTazJwc0lnam0yMVNFdGgzRGpoNks5VWNSLUtwN252d1FEcGwxMEJ5M1JjZTJGeDFwVUZNMThLVTd2cFVCRG4wUFBUNUtYWkZGV0lFdzVnQzIyZEZ2RWdSelRHUGxBYTJLZlJuWWI3eHc2NmhIUmVKYnNKZm05bHFkQ2RST0dTOENEblYtZDdaX204azg5V1BPdE9sMXBNZlhpUU0tQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Agora é definitivo: Mosaic fecha e coloca à venda fábrica de fertilizantes em Araxá - AgFeed</t>
+          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -7672,19 +7672,19 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQVVZOR05sajZPcjc0SGtxemVRUVFyVnA4UjlZVlktLXppRjY1ZzVVZXBMbnlwX2VLNXpNajhWeHJMb3dqYWhlY3d6ZkhMdnVncWpoS18wa0p3UUxzZnJXN09NNDFRYloxaVc3QXI1bWVwZVpfWC1ES2Q3SVFzUVVockJyZkhOZ2dXN19TN1NvNVpXaWVQRmZTYlJVRkJqVDAtR3dnb29LX0pNVU00OUxCaHdFNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Mosaic vai paralisar fábricas de fertilizantes no Brasil após disparada do enxofre - Bloomberg Línea Brasil</t>
+          <t>Mosaic, fabricante de fertilizantes, vai paralisar produção de 1 milhão de toneladas de fosfato em meio à alta dos preços - InvestNews</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNSnRVSDBoS3ZweUtqVkF5TXZldHhZZ1VRVXRkcW81aDNRNW9sNTVvTG9lZ0Z0U3dWZC1hdFkxblFmNjZ1ZDZsS2tvY25oazRUcVRkb3lSbUxwZHFJUGgtSFVOZWU0WU5JeUs4SG1hYWpUQnlvZ2F1TzgzU3ZqYV9iNEVld1dKaU1pdlRrX0FpbTBMNWFTclFsOTA3RkMwUjhCN1RxODRZSmFJMzlwQm1oNjl5S05Ja1FsNTIwVS1TVdIB0wFBVV95cUxQSzJqM05BZ0ZiSVp6MUtIV0h4U2ZGcjM1ZWJaMXNvMHB1UklIM2hxZE1oLTVIYlpXdVJWLWNUZzZidVZERWZOUHNFa0txdXItQzJ1UWpUWmJpcVdnVEMxazlpRWIxT0xoQzdxakhRQTFmMTA4MnZrckljT0ZYUnZDb3RlN09YQUZ5TWhucGQyX2gzcVdJVzdVTXE3X2IySGl3U19ZalBPcUdwREJmNjZab0pnTzllNnM3S2wxVTJGdE5YSkxVUWd4NGVRUF9xNmhuQW1j?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOMlE2aTNkQ1drWHNGNjhJckFIY3hkM1A2S3lfdkhJbXBtaDN5VmV4NHVPNFdra1FTXzV2ZUprdGNsaDZxa21sWmk2dlpabDJ3aUpROUE3YVdFd0VEZDdscnd0RjAzS3huS1N1Ujh0b01DVld0OUpWUDV4c091SW1kcjBDNFRHZDl0ZTdIMFBlTHRuRnZYenNneG4yUHFLa1BnZEhmY1ZhenhwSTJpb0NFdXE3dDBGVlI3aERwQ0NHWWk0d0JBdS04dFZzbHNySXZNcFp2YlJGNjVCNnZ3YUZtdW55MHhQa29QVnhn0gHwAUFVX3lxTE9IakdwRXpVeExMWDhnSkZFci1UWFRqLTZscWVWcS11Q3lSMmdnX2V4Mm1IUmw5WEF6MURadm1KdEdlLWxMWjlIa3lBNXVJYjVrSzdBTHA4QUFTblNrSV9uRDdLR2g0R3lrUTBSV2hEMi1IVHdHeUxFdVZCNU9xbTktc0xHWUVnLWliZThlUnplY3pGbDBnaXdPTFpicFZ1NEo4RGdjbVlEUW5HSDlIb2U3RUZQLTRlOVBWZVZQZDU3WDR3YkJZbmJ5WHBXa0RZZXIzc3hpbU5OSFo2cWF6M05iZHJUVzl1VWhaRnZUblhWVw?oc=5</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Mosaic suspende operações em MG e mira corte de até US$ 80 milhões por ano - Exame</t>
+          <t>Mosaic suspende operações no Brasil e reduz produção em 1 milhão de toneladas - Investing.com Brasil - Finanças, Câmbio e Investimentos</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNdEZqNHdRb0pLX2tyVWRjNVk0SmdMUEdIdjVMbGFOb25QLXdaNXFBU0w5a1REbXFUcjFKV2lYSUNYTk9UQXV1Q1hHeVozUDdCdWhvXzlhQ0lLM1dYZUZyaDBhNXNmV0xmWHJBMFVqV3BwUkxEY2s5N0FTMkE5ZW9tRG9qbW44WUVyNWF4ZXhqaURvWEFvOXhtV2EzZnJEZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOb1pWNXlKY05IeUlLM2M5NUFqWmYtWEgzYWR3UFh4Y2tISnlBZ0JWVnVfMF9POEFOM1k2dXZ2X0k0Z3FpVzYyNUsyRlJCTEs1Mmw0cGhibGdaTXNrMXMxWTA4VmwwSC00TkREbEJQTk5kekdxc3FFQkN1YmxrT1UxOHhyc2YxZFgtUWNLRXdmdi14SlZZY29CUzBxOE4xY3J5Nm41aDBrYVRQS2JyQUZfaDl2T2d3eXZRd1RUSE8xdUtzT3pQOXdDTmFtc2ZyQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7745,44 +7745,44 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Mosaic põe ativos de Araxá à venda e paralisa minas de fosfato em Minas Gerais - The AgriBiz</t>
+          <t>Cotações Agrícolas para esta Terça-feira 07 de Abril de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>07/04/2026 04:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOVFJXZkVVUUlxUFdTUTY3LURqTi1Xb2ZpY0FMZHJNZjRuSzdyWEFmMEFJYWJHeWxibjhIZGF6MWZEbHMzYzRmU1Z6eVB4WmY5YjlDVDd0bU1RNTRBdXFOQjJYRGQ1SVlFd0xLZ2hyYlExMHBOU3dYLUlJY1U1b2JRYzR6bmFFQ21LNl9peDNCT2JWUl9PTUlTcE9TX09PQm5ZWjhxY2VTX0JmbXRodjg4cXgxSDhYUGVGU0dqZA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPck1UWEx6YWo2Z1RudXN4ZXpOVjhhWEF1WVFfUkM0NWxVT3g5SGpZME1MZWFGUGhYQ2ZOUF9UZkd0OTVDbkdwOTY5V1hUZ3p5MUxYTTI2Z3VVMnFvQ0MwOUJoTUExOEF3MVF5YXhiaWlpZUQxUDVUMzNPM3I0R2pvUzg1VkIyT2d0VndXSGMxTDBmeWVHVTJvU3ZSYWw3TWMtcmZ2MzB3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Mosaic paralisa operação de fosfatados em MG e põe à venda ativos - Globo Rural</t>
+          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>08/04/2026 04:00</t>
+          <t>07/04/2026 04:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNZmtnalFlYUVpZzc1V1FCQWVZR3d1dUR2SkJCeG43bi0teDJkVUZiclItMWp4YWxUd2tyaElmLUlEMzVnNnZsUmFhYzRLcVExdndfMml0SWJqV0plN19ZeGVwbC1JRWJuNjBmZUtXUm1ZTHhxRm5TNUJDN08tOHVGYWtBZjRZRHFJblBVeDhiT2J1UFJtS1ItcVZ2SWQzWmxHWmFYNjlqX0hfa3F4eC1SS2lfR1hNRFBMdWZV0gHKAUFVX3lxTE9xRW5TWVBCc3J3OE9JbGx1NTNnUHJlMVZXek42RDlWeTFHa2R2SXFiY3dwTkNldGZFUlhXS0xzMWdfVjRIVTdhMWdwMGQweHdCdi1Jckx5b2pQVEtZTkc4XzNpellPMEx6N2hOWXdMTjVhVjdzZGJPZEI5MjJQeS1jeFFxNWdMRVpTX3JmNldpRVpXY1ZaQXVaZVh4ZUtxeEQxWklhS1Z6YnhYellTMVBJYjkzcVVtZ2NvMkF3Slh0WmRFZW1ibWRnQWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
         </is>
       </c>
     </row>
@@ -7811,66 +7811,66 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Terça-feira 07 de Abril de 2026 - RRMAIS</t>
+          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>07/04/2026 04:00</t>
+          <t>06/04/2026 04:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPck1UWEx6YWo2Z1RudXN4ZXpOVjhhWEF1WVFfUkM0NWxVT3g5SGpZME1MZWFGUGhYQ2ZOUF9UZkd0OTVDbkdwOTY5V1hUZ3p5MUxYTTI2Z3VVMnFvQ0MwOUJoTUExOEF3MVF5YXhiaWlpZUQxUDVUMzNPM3I0R2pvUzg1VkIyT2d0VndXSGMxTDBmeWVHVTJvU3ZSYWw3TWMtcmZ2MzB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>China garante fertilizante barato, em meio à crise global - CNN Brasil</t>
+          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>07/04/2026 04:00</t>
+          <t>06/04/2026 04:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQUmZJMDZzZzQ4aEhsdDhjbmpCazN6RVpGVXpFM0ZLb2QzZk9RRnUwVUEteXBVbEZpNkJXN3cyT1Y4c2JuM1RJTHJURWZzTV9mSU1fWHkydGRwSnVTcnMtN0xWSV9wNFpvOVhHMnNaVWZjenJLUjBPLTJEenBrX0tCQVY1ZGxTV2hmWjBhV0dyQkF0T1RnMGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Indústria de fertilizantes alerta: pode haver desabastecimento - AgFeed</t>
+          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande - Página Inicial</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>02/04/2026 17:10</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPbXRMZ0dqOWVnR0xjWk9PTFBFUWNBdUd0SUhMOWFNZWFEay0tSlUwZXZTbG9MSnZ4eWVHTHFjRktzZ01ZRy1qdWh4cUdaQmFNWFpXR3BnMjRLcDNLcEFfM1dQSkpWX3k4emZfREtVZUt5OUZCbzhQXzAwLWhBdi1CWGcwd3E0WXkzOEthRlBISUpTUFAxYWRpVmE5ZWdKYXBkYWRydnVmNTRibUE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -7882,95 +7882,95 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Alta do enxofre preocupa indústria de fertilizantes, que vê risco de desabastecimento - AgFeed</t>
+          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>06/04/2026 04:00</t>
+          <t>01/04/2026 04:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOd3piekJKRGJmWE80SVlOQ2NWLVBibnRnc29HR253UlVrNndYQ0F2eUJ3V3BWaGQ0NE5RT0V5c25FeWMwekJxYV9SQUNxZ1NhNTdFQUZDbHF4VFF0LWVMc2lWR3lxd1ZqRGtqM3ZkWHozOElSQlVRYko0WWVaeHJxa2JQREdtSEJOS05iWkxhRkxOZ25RQ3VEMVZIR2xMeVVzc0luand4ZEpVTVNwelNzeTBDa0ItWTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Biofragane</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Transporte de calcário fortalece produção rural na comunidade do Formigueiro - Prefeitura Municipal de Várzea Grande - Página Inicial</t>
+          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>02/04/2026 17:10</t>
+          <t>01/04/2026 04:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRlBlekZQVnQ4X0Q4N2l6VGNpbVJjS0VtSmlHYmZqZTl1WnVTS1RPVEtwSTdCbjQxdk8yNzBVS3E2LS1ZLVFZX19lQkVGV2R2SE5FSms5UEhwOEd4cVMxQ2cwa2NYWTRCRWxjaWVLbkpjRXdfZExuZnh2UFNjUGZKX291dy1nZllOanBtSGlMUU1GTVIzUmJ1U3RLbWplenRWRmltampybC0xNHkzTjBnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Biofragane</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Empresas compram terrenos no Distrito Industrial de Ponta Grossa e prefeitura arrecada R$ 11,8 milhões - Bem Paraná</t>
+          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>01/04/2026 04:00</t>
+          <t>31/03/2026 04:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxQdjVTa3FTVDU1VGZQay1sMlVFTkw3eHRVdXFlVWxrbGtMRnU3aFIyTnpWZ3NEeURSYjJJTDhlWTVOeUtoZWFrNm1zNnRtNEZNVXJMMlhWSFJJYXNzckdOTUxZUjcxYXczMzhqVGFhZHhPemVZbFhhYktFVXZDTzZjZlp6OGJ5czlxdjJnZnB5SzgtMVlpQTI1TmFKSFloZ0lyMHpsSHpQRm90cTdid0lKcmR3QTQ1RUpwS05LRzNJZmdWbm1UZXdGek1reDlKNU1LdzZzbUQ3NGJTQ0ZFQ2NBTWpnNTltU0VNMFdQSy1kM0dib3Np0gH6AUFVX3lxTE40RlkzbktwRTA5SmFTOGw2Ykt0TUd1ZlotUGtnRmpiSGFnWVR4Um95cUlILUwxYkVjcE01OVZreXdGdW9ERmVya0M0MHNCTUpjOS04cVhoSktGcnliRTBhUmdndlJ2NVVDb3dkQ2IwOVlRNHRCdEcyZ3laemtUdS0zQmVpdVBEX2FoVi1MbXlhenZ4R05sSlpNZUpTUkhhV0l1SUJYU1lhUDRnc1MzU2h3ZWQ2a1h2S05DZnlyRGRKbUlVcWFjT1NoNGhmR196T2F0OWR6YWZXaWxjTFdYU1lLMEpnR2ZPZ3ltRERhaGNYdUlJSjRraTdUYUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Ormuz: 20% da energia, 30% do GLP e 50% do enxofre - Agência de Notícias Brasil-Árabe - ANBA</t>
+          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>01/04/2026 04:00</t>
+          <t>31/03/2026 04:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE91akhDZG5kTFBRM2x2UVhuWGZfa1hOZENjNFotbEI4QnRDU2VYaGtjWm5jUHo3MnJWalZQLVdVbnU0SGl5WkNkd0ZBdXFXa2RYSF9DLTBEYnpLa2hoM1dYcmQ4SERVdlFVdjEtMXk1SnVRYkdY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Ureia avança ao maior nível desde 2022, mas demanda brasileira perde força - CNN Brasil</t>
+          <t>Cotações Agrícolas para esta Terça-feira 31 de Março de 2026 - RRMAIS</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQai1ZMXRrWW8zbGNQRWwyOXVteEg3SnVUZWtIUGpJVTFKUmM5VmlkbDdnYWhIN3VDSmR1Sk5mOXVyU1ZSM1hBS1YzUnRkdXh4RkM2aGNTVzQtWDdsb29ab0J2RHFPR1lvWjV6eXZBaU5WbmhYSzBRb2N0ejFaSldHdTFveEtMb2pWZXZMbnlNSmxyU2lJaTB4T2w2QThOSHFqbEEtVXVXUFRaaVZCeHVrdElxbWp0RHA5Ny1kZGphcWJVR0RUWjhfZXJR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQczNPajlCZ1pKNG5sTDZfcEpwMW1ESHJZTF9TSmpkbnM3TVNqTW9BMjNnRUpYUzdkZldzMVI2aG5LZk5yVXBlNGI1MExmd3RJT2lBN09KWW5SSE9YUjRFbFhibkhwc1RERGRtdmZrWS1iYjE5X2E0MnB0TFFJdERxT2YxUVp4eXdJZW01SXU4U3lMaWwwb3F6SnJ4VE1GazFLdGxkcW0yNTBfaDA?oc=5</t>
         </is>
       </c>
     </row>
@@ -7992,39 +7992,39 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Cotações Agrícolas para esta Terça-feira 31 de Março de 2026 - RRMAIS</t>
+          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>31/03/2026 04:00</t>
+          <t>30/03/2026 04:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQczNPajlCZ1pKNG5sTDZfcEpwMW1ESHJZTF9TSmpkbnM3TVNqTW9BMjNnRUpYUzdkZldzMVI2aG5LZk5yVXBlNGI1MExmd3RJT2lBN09KWW5SSE9YUjRFbFhibkhwc1RERGRtdmZrWS1iYjE5X2E0MnB0TFFJdERxT2YxUVp4eXdJZW01SXU4U3lMaWwwb3F6SnJ4VE1GazFLdGxkcW0yNTBfaDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Preço da ureia dispara e atinge maior patamar desde 2022 - Poder360</t>
+          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>31/03/2026 04:00</t>
+          <t>27/03/2026 04:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPZUIxSkk2bGJHRnlhMlNaYW5xVVdiZmctUGhDQ0NFQXlmakJzOFhwN0JrTVFOUzZmeGFaV0dwSUJsaDdZdy1DVEJRR0JDMjJGbVdEelpFNjQ1ZVQ2cFQ3Q1MzbmtrMklTT1p6UDd6MzBQcVVDT215MkluWWJnb0NQbjBTQnFHQXZwNXhGRXF1akk4bDJGMWY5SGF0SkM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
         </is>
       </c>
     </row>
@@ -8036,17 +8036,17 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Corretivo sustentável passa a integrar o RenovaBio e amplia geração de créditos de carbono no campo - Portal do Agronegócio</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>30/03/2026 04:00</t>
+          <t>25/03/2026 08:19</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgJBVV95cUxONG9palBmb3c4cmE1Nm52QjNHZXF0Y0k2UmtGY0NFRlpySThsbVRQQnFaZTZFaUpReWViMksyY01ndGU5WHJqZjNDTG1TUUo1VHQ1OWkwUHVPcEo4dlN5UEp4cXJzTFc4eTd0V1habkNhelNtVlhsSWNuMHhJcGtHMGFnUDdJZDdzT1lJaFFDVHZpSklUMjhQMjJSUndnellMYlVlcG9hczdmSm5uMGpiSXBGMmFabTNSQkJOajJWblZNNGpjS3pIRjB4RHJwcEc3MG1OV1QxZzFYV2drQ3ctWE8xNWdpUVl6MTc1U0hzYVY0T29za1RyS2Z2cV9xY0NCdGpUYVhHamxCamVueTFZaUtn?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a62637111bb4415a383110696fcab4c&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -8058,51 +8058,51 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Corte de 80% na CFEM deve baratear calcário agrícola - CompreRural</t>
+          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>27/03/2026 04:00</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQa2dGQlVRajItTmU5MnBNVHE0R3F2TTlWbHNvZlNSMFJZLXVXWW5pNlp3X0xFSU9OcHltNXVKM3FpTGc2Y3pKZkZxZkFoUGlmdnVrQ3NoSDd3MnR1QXlnakVJR2lQajJ1YjNIR1VHNm9SNV9CSDB5TjMwaXhoNU5VSzVLckpKU2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização</t>
+          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>25/03/2026 08:19</t>
+          <t>25/03/2026 04:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e233b734cabaee823cb4f045c9e&amp;url=https%3a%2f%2fwww.segs.com.br%2fmais%2fagro%2f443607-corretivo-de-solo-sustentavel-entra-para-o-programa-renovabio-e-gera-creditos-de-descarbonizacao&amp;c=17562555972134783382&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Ureia dispara 50% em 30 dias - Agrolink</t>
+          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -8112,117 +8112,117 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPR09odVVVZHhCMVdaUTBiOXJndXB2a3E5V1BsSklCMWJvdmhZM010SGNXc1p5ajJoc1FSUzJWTmNDZGFnczBRYzlvc091a2hTYmgyWXZUWmNKam9ranNtNXBtR1Vmd3p4TlItNXUySFgxMnZPaVd4R29qY2RXVXdJM3ZvOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Novo tributo sobre calcário afeta cadeia do gesso no Nordeste - Movimento Econômico</t>
+          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>23/03/2026 04:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNOUVWbmdNaGJkbmlfVDN4ckxPT0VTYkthLXFwN1ljVkU5TXFXMWo2bWlVMnhnY2hHVm5VcTJpZ0dEYW94RkRwWU5wLU9Tc0J4bHFkblIxNE10M1JNejIxQ0JBYzh4MGFWNm5XVU1DNlpPOVlKV1dXTHE3RWYycEJoM2JvczZLcGk1emZHUVBlR0JpZTNYVURBQTltZVV4LWNiZW1rNGhYVTQ3N1cyX00zUlFjMjJ2OFVIdzdmcTZOeXZoeDJrak5tUzZydFRIY3Iw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Corretivo de solo sustentável entra para o programa RenovaBio e gera Créditos de Descarbonização | SEGS... - SEGS Portal Nacional</t>
+          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>25/03/2026 04:00</t>
+          <t>20/03/2026 18:35</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxORmVta1REUjdPWkExNEhZTGZITGUzbEI2R1Rnak9WLUMxU0pRNUU3VGR6OWJiNl9GT01PZzFKRW04RmNWWnpIbnRFanBWb29IRVktdzVqaklGYWZxUXF5dllNeExCb1hsa1ZVRmJkeEsxdURUS3Jaa1VCRGl3dTg0T1h2Zmp3bWsteDhaSXBYR09jTTRNUWpuTGppVzBQdUs5eXRPQXpvRXhNbW1JMk5mVE5nT21zenVFbXA3Q1JaNVBYalVEdENiNzk3UzE0aEQwY2xV0gHYAUFVX3lxTE9jaFo0ckh1SXZ5OUY2TERFNEtfYW0zRXRfYkVvRUo3dXNwY1VLOW1QYmpINks4UzJ0X1pCcWQ2SG85a1p1VDNMaUIwczBCdGdlRGFvbVhrVmdkV2tMMGQtN0ktcTN1OUp5bWo1Wk1NaElZVDlXMVhRbFp6b29hVF9EbGRGLU9oY3B0dXN1RGtXdlpRcGxxd3NRWEdLbkJPTmVhMi04Z2txRVdWdTdvRE9HZ3ZmQ2RudklnZnB0ZEJyWS1tMnUzdTdCb3Q3allTb3dteXlyN0N6dQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Preço futuro da ureia segue subindo: valor próximo de US$700 por tonelada para abril - Farmnews</t>
+          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>23/03/2026 04:00</t>
+          <t>20/03/2026 14:42</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNcHkzSlA3V284QW9KcWRCR0hnbmpYZVFlNWVTVl93TmRPbG5QbUdLcWliZEcxZ0N2T1JlMWQ0NTJwRXFPVjZ5b1I1V1pzZVdySlJkdmNtTW9jVWlWUVY4dk5GLXlpdjhoSk1MRTZPc0hwX0tXYm9qZUo2Vk5ubjc1bWhUdE8xTnNQRlFtdGtsVEs1T3lzZnZjeVVQMWV5dERkMVZHemxkQ09CdnBWRURXcEdMNXlGZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Justiça autoriza chinesa CMOC a assumir minas de ouro de controlada da Equinox na Bahia - Tribuna de Petrópolis</t>
+          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>20/03/2026 18:35</t>
+          <t>20/03/2026 04:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQbkthazMxNGdTNWUxZ1FCNTZobG1VQjJVMm5nTXg1djFDUHdLVHpNU0VYRWhFOC1NbVkycXBoSkg4azA5Q2NmcE1GWWhBOXprUFVFcDV4Sl85cGppakY3MzljaXd6UWVuYlp2MWQ5cHdpRFhzc00zSjM1blBIOHd0d0E3UkoxX1JqaTY2Q0Z2WGp4bGpDMHFHWm5ZWER1YzN4MTF0S3lWY1poQzF6X3B4NzlsUmstZUJZRk12MDNUNUhocmUzWEJpRkZTY3E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - Justiça da Bahia autoriza CMOC a assumir minas de ouro da Equinox Gold - Estadão Blue Studio</t>
+          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>20/03/2026 14:42</t>
+          <t>20/03/2026 04:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxPMTBtZnN2TkpLMXVZQjYwWmV0bnNQcU5pTlZrMWZVTi1FOEtQT2tGOXBGeVhJczFUaWw0ZUxEeXM4SjhialJZSTVwT0YtY19VUF82TERMWjlhQ214cEJVSW9tV2RmYzBpX2FiRGNYNlNMd0ZmU1oxMFZFazVTRm0ybDZTV3pEX3pKd1dOaFpwdXpsaHVuOFM5SnZNRkFVNXh5Ykw2dktfVjlXdXlZZDlQQlRBLTQ0R2l1TUNNZUtyVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
         </is>
       </c>
     </row>
@@ -8251,56 +8251,56 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Sindical-BA alerta para impacto da nova tributação sobre calcário agrícola, que deve elevar custos do setor - Sistema FIEB</t>
+          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>20/03/2026 04:00</t>
+          <t>19/03/2026 04:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOQUNveWVYZUNwX3BMRXdqRzdqUThDTkNOZk9vVWNMbHNsVlg2N1oxcDZjRV9nVHVrajNfaGVieG5RYVhiMDhjeGxobmdCRmhkQnFDSy1rR2hvbUhjb056WTNZeWpkSGpmVWhlMWxQTjJCN0dqRFRibmZRLVhOb1R5X3c5UmZBcmlYVTNYd2trZUNCak4xWHY1OTBtUHROZVZwUm5UVWJINWc2dzgwOVg2RnJMNFlaZ0p4aFIxdjBfWUZfUi1WaGd0MVJEeDhFa1ByeXhmVThUVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Mosaic, gigante do agronegócio, aposta em IA para enfrentar volatilidade e reduzir custos logísticos - Globo Rural</t>
+          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>20/03/2026 04:00</t>
+          <t>19/03/2026 04:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAJBVV95cUxOME5qTE54MnlMcWFJeS02bUs2dGRlR0VSRWJHT001NEtPcS1XaURNbC1UaGd1Q2hkWld2ay1ITHptMTdBcHRPLUJPVzZWTkR5d21GNHJHZGEwZ3U3ckltNnNQN2x3WnQtT2FwdkJ1eTNDYVFSX2ZreUJ2dFQ3M1pOSENSRGhTeTg5djRfaWxWbC1FTEp5TWVBR24wVlNZNEhLc2N0VVB5XzAxWXZqbHNJU2hTUUQ2dlJRaTRkTGdId3NIREtxdWR1dXpqSVY4V1lQRlJzbTVodXFSOXBpT05RVkdpZmJSNXVpYzJGaUdLcjUwLWQyNGdoMWNlOVBVSU5PQmVjX1o5cmZPN1pY0gGbAkFVX3lxTE5YUjI3TVduTnRpaUdEeW0tYnZvSGpRdHd4MXE1VUtsc3ZsQ004emFwdGU4cFZqQ25XSnVTQjYxUG5DNE4xcHZKZk1JLXNjVk5hMkNuNmJZdllRVW5uQmtGQ0o3UVBJLWp5M0g4YXJPY3FqajNsVWttc2pJNjBFdHpkMVFEYWJvaGZUU1hQMXFzTDNleFhVakdxTmRPTElXTXA4U0xacTJfNFYwS0I4UE42S0wydUtudEU5d0RNOGYtQk83SVBtc3VFeTk3X3BhOHVFanBOd3VEaHYySllENWMxdnhDRUJXd2VfNXdhRDl0cHRkVU1BM3ViMWt2azdDbW03THJ0WGRBQllJaW1aRVM1WEJuSTdRNm9Bak0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Disparada histórica do enxofre pressiona fertilizantes - Agrolink</t>
+          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxOREtjdjl3OVV3M3BodzJUN2tTS09qQjdCaHVYcHJVak9fWlBKcl96ZWlkaWhYSmJSazVXQ3c4LUl4YTU4MXh6VjNwd09JaGRsblVrajRXNTlHUXp6X0V1Y0E1YmYwTXZxa2ZXX1AwNEVJcnpibWRMMTRXcG9ibGRSb21BOGNHMDFxZWJhVnRmeTJ4SjY1ejUzTlVqelJ6dE4xUkFpWkhn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>CRA aprova redução de tributos sobre calcário para uso agrícola - Senado</t>
+          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -8332,19 +8332,19 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPZi01RmRheW9LUVdwbzZ0VWR5YTZHXzI1VVFsTEZ6OXFzaVM0V1JwYXRYdmpoQjExVnRfNEtKVUtFYjVMNy1PNkFXYW91anRyOUhibHRWcTNLcU5UaTBNY3BRdzNrXzdJZ0RQenlYSWEzQ1dsZ3B5dGVKRUp3Vm5RRHl2NDEwRGVFdWZuRVRILXdSYk1qN3l3UnUyMHZyVGg0bHdIM0swOFN4MGdaNjFjMER3Q2hORGlMLTN4Nw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>CRA aprova selo para café e alíquota menor sobre calcário - Senado</t>
+          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -8354,95 +8354,95 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNY2pRTWs2S3NtQlQwenhTVkJoWWpXV1ZYWEJmS1ZBcVRJOUNnYUR1YUJEXzRneGxSdlZFenh3d1c4TXVLaktTSi1Xek5TUEU3d0ppS2s4ZTdBaG9QSzcxV1pmOVpZOU16Tjl1T05kT3lIaHNkRXBtck9UY2xOYnpVVFV1MWMxTjdFbXYzektEQ1I4Uy00MU41dTQ2ODhzV1p2MUpENTZ6bUV4dzlOaXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Desembargador da Bahia retoma negócio bilionário de ouro entre chineses e canadenses - Folha de S.Paulo</t>
+          <t>Calcário para uso agrícola deve ficar mais barato - Senado</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>19/03/2026 04:00</t>
+          <t>18/03/2026 04:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQdXBkMXpzTml3eG90ck82aFdOU0U3Z0pDRWMtd0NzclBRVzI3WTY1by1pVEhkTkFLbjgwUVR4MUZpWXI5S3lOOC1CRVRPaTdNT3dSOEMwZDZKNTdzc09OcEQ1M1RNOTVEVmJBaWhCRGNWRDI3Qldval8yWTdLNG9oek41LVJHeUdKYXRzMVhaalN6TzFCdlFIbzhfMkJ1clduV25GYVVYVmdqSXJRYlg5d2FmdEMtZmlRazdUdm9JWU1GWTRwcjFLNFM0RW45OC1zbUHSAdcBQVVfeXFMTnJkMWwtODlkeXZTdWk1Q1hBZnZNREtzVHZqX3VVQlBOdDY4TTNIQnI4OEVFRUVtaWxHTkNxZlhKOFN6U2RFcE56bU5zMDdUWmt1YmQtZGtXczNfTzllalRhUW9yUjdPbFBFbFpSOUlCMlBaQXI0aEVwRHNMbEw0ckJzbWVlNExKZWUtYlpQRzhUUUR3aGFveFdJenF2SmM5WkdzNy1VRzUyTWNydjU3anVOT3M2X1VsLUV4VWRqRHc4bjJoVGhGQlJlR1dvaE01enEtMVlTWmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Comissão do Senado aprova redução de tributos que incidem sobre o calcário - Canal Rural</t>
+          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>19/03/2026 04:00</t>
+          <t>17/03/2026 04:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQ2h1ODE3WFlWWnVpN3Q0TVAwajZrUXVDbmRpeFFZSWt6WGJXLXNKSVREWFdXYUNQeVprdjlieGxDS0xxU3J0SkMwWlRPXzlvVFZWWTJNRVRvN0dSV044Y1pwMHprUmhqRURpcGRjWFVfaENjX0U5bE1UaW1KNFdvUExibEZad1A3SmpOQlNxZTFselNXMDdRLTdBOGRpZXpiWEgzMS1SN3FLNUdybkxQbndoa0NFT1By?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Calcário para uso agrícola deve ficar mais barato - Senado</t>
+          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>18/03/2026 04:00</t>
+          <t>16/03/2026 04:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNQVRiQWZWNzR1X3FYcGFBUFY0aVBTUWdTWWFsanhzWXh2VDJZN0dKN0ZqUUtoRWV0Y3lhekU3bVliMFQ1TGpwZzFxMGVJQzd0cHdxTUdBTE1JeTBlZzFDOGVPRGxDNWlSaTJyZ1BzeU80NXMtVE5fY2s2ZGU1SlJ1NHBIbUJIQ09UUzZQMHVra3QxMU50R3VoeXE5S1h6WGtnXzNKeXpZbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Com Guerra EUA X Irã, Ureia Sobe 35% e Altera a Estratégia de Importação de Fertilizantes - Forbes Brasil</t>
+          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>17/03/2026 04:00</t>
+          <t>14/03/2026 04:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPRGxicDFFeWhVM3NQa3ctVTBiWG5FOWl3WDE5U3JwSy1ra1hXRlFHMWxvWEcyTTN4c1RlV3hsYVdpWS1GWFlhSWo5SkZVU2dqRUtiOF9pb2RTekUtVHd5X01DWnkzbkZaSUVzTkMzS2VmUklqVzJJNnZibTNZNVhQUU1JczJqTE5wT0R0VHBOUF8yVGQydlN3NzMtZG5JcVF1c3VIazZWTFl1RUZMdzFucG9CVTFnaE5NUnRtWDUwNkJfSGJvQTV0Z2dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
         </is>
       </c>
     </row>
@@ -8454,117 +8454,117 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Alta de 35% na ureia pode levar Brasil a priorizar derivado de nitrogênio - CNN Brasil</t>
+          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>16/03/2026 04:00</t>
+          <t>13/03/2026 04:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOcXBBd3BWMDNLRndnNEhobERBajdfVFA5ZnRZdFdLOTBtZFpadmp5VWNHNDVuNUxZX0owV1dkN3lwdXVra000QzNON1pxZUx0S2ZvLUFGVDRnNkZDRFpaTGdwczAyZ2cxdmRxcy1ZdnlkUXlYVlpRaDY0Ull0Y0xtM21Qbksyc0dRbnd4TWNmRS15dktfV3gwNEZTcUNvV3huelNtdElVYjB4aTA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Santa Cruz irá distribuir cargas de calcário gratuito a 68 produtores rurais - Portal Arauto</t>
+          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>14/03/2026 04:00</t>
+          <t>13/03/2026 04:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPdk4yTUFiZEY4NXdpQUhoNnVZSVRNeThudG1lU1ZYWFVkQmswRmFranBYM21jeDNkYk5fZXVoVENlOVZiSkVxMlFiVk1ndFRKd2dLNFdhaUpNZEJlbG5FUkZYZ2thZlZkQ0V0OHNydDdaZVZ3dHotdVNkaFZYZWFveldzTU5BUV9rSTRuanhkaWZ0dEx4ckdudEs5N3c1cktwSmhTSUs3UnUwM0RDNmJkNkFzUy1BUG8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Importação de ureia pelo Brasil cai forte em 2026 e preço segue em alta - Farmnews</t>
+          <t>SunSirs: Preços do enxofre aumentaram 18% em março! A oferta apertada, a forte demanda e as tensões geopolíticas alimentaram o aumento dos preços - Sunsirs</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>13/03/2026 04:00</t>
+          <t>12/03/2026 04:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQSTZnclR2WFM3LWRESEtlMndnQWFiTU05ZzVOcDdlQ1g3RTAzVklPYTZ0YkF5RGk4MTlGR05pMEVES0pFTXlvOVpmb0ppWHk2YS1ValFtMWUxcDB5WHhpdEpZTmhkT1kzMUpMVTlYNWcwb1RWQzJNSVNxbmhOdWlvT0YzdXRBblFaZlRqdXRzeGFZZDA0anprdXZOQ1k5Z1RyZUplVlJhTWtiQ00y?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1zRHdtZ19yUjNXemtIZmZzVzBKeHBUbUpHeU5UV0JGSjBRZkwtLWtTRnhEVU0yZWZwdURackROcFJrZU1McFpqei1yWnNqNVVjNjRWbVBmNjgteFNIX3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Limestone: a pedra calcária em evidência na arquitetura - Portobello Archtrends</t>
+          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>13/03/2026 04:00</t>
+          <t>11/03/2026 04:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5Xa21Zc0YzY0pUazFLbDJVMmlTYzcwYTd3RG1OcjNNalZVblN0N2gwMV9NczFWZURPa2MwaXNMcmxfdE5seHo0QWozSFdBbmfSAVRBVV95cUxNUEhPRGZuQlpIS1NNTm1lMW8zblJQUVVYWkhNXzlfcVk4N3dfZHRRb0xCcE9IWTZIMHdhNnYtOE4wNjh4YlBrSTY4ZUtVenF6NDdKemg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>SunSirs: Preços do enxofre aumentaram 18% em março! A oferta apertada, a forte demanda e as tensões geopolíticas alimentaram o aumento dos preços - Sunsirs</t>
+          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>12/03/2026 04:00</t>
+          <t>11/03/2026 04:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE1zRHdtZ19yUjNXemtIZmZzVzBKeHBUbUpHeU5UV0JGSjBRZkwtLWtTRnhEVU0yZWZwdURackROcFJrZU1McFpqei1yWnNqNVVjNjRWbVBmNjgteFNIX3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
+          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -8574,19 +8574,19 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Mosaic avalia entrada no mercado de terras raras com projeto em Uberaba - CNN Brasil</t>
+          <t>Conflito no Oriente Médio eleva preço da ureia e pressiona custo da safra em Mato Grosso, aponta Imea - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxOaDhHU1U4Z1ZUcDhvSzBheGZqQUxjOXFvZFpKQWI5Q0pTdG4yMkMxbGtoS0JtdDg2Tm5GQ0VRMC1NZ2tBRS12RFowanRSZ0V5b2F1R0Z5RGw2NlYwbzdoRzZzS2NGbi1PNFV3aHBxRHhsUTkyeFdXdDZKS1QxV2RKdThyU2JGS1E4amZXN05CYjZFS1BpRXAwX0hmcXVVLTgwc2RqUkJFeFlKQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOTnZoc1RsVHBacHBYSTJrZFhacUlvY2h1emtmRktiU3ROajdCX1pHcy04VDJXUndNUWkzMXNfVlJia1p2YVFlbmg1dUd2S2pobG5yOVMyTHR0eWhoU1J1SGt3NlNUUmdUN0JIVjFPV042UDBpT1dDYjFTOTVkVmRLa1Q4anphUWpKQ2J2SUI5R1M3aFpiTmVOVk1wQVhCSFNUM1N5S3RqM0lmWGNXU0RJeUdQbGRQNldncEJid2V6UlVIMmhsUGNmbG1KTlctT3NSOVlnOHRLeW10XzA1OEJYQkhIOHdDV203U0lvWEZIcDQzU3A5Vno3SDFnQW4zWU3SAYQCQVVfeXFMT3NyRl9SQTFZeERRb0w4Sms4dkJNaXlIRVd4eXduNFdPVlgtbkh5ZE5NVUdHU3lEUExlNXdxQi1vMi1ESzQxaVoyRHpTRlBobWlUalRvdVJCNVp4Xy1sSWZzcE1penBXWDRocjFxSjUtVmNGbDkxcTFLOGRGMHROaDU5VVl6TFBLbXJwNl9lZFhDNkdsc21qQkF6WWxEV1dDTC1raEpEZmlHZzVvY1NkbWRBTC11eTdFME83VjBoM1pQRmFFRE5NWDRQQXBGSDFUODR2UFdtTG96V05FX25WTk92ZEU5a2p5ZmN2eW9hME1INzlyMWhWak5tdlZUQkdDaFVWUHo?oc=5</t>
         </is>
       </c>
     </row>
@@ -8625,78 +8625,78 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Guerra no Oriente Médio faz preço da ureia subir e eleva custos de produção, aponta Imea - Canal Rural</t>
+          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>11/03/2026 04:00</t>
+          <t>10/03/2026 12:14</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQMjNJY202OXBERXA4andGUzdVTnZ4ODdOWnZOVU1xUFBIVDR1Tjh2RmhZdlR6VlRvVmc5Q05BSS04Nm9DSzlkQ2NHT0FVc0RCYU5uTDlkbVBfc2ZiV2FFRncxYVBEUHdBWGFMcFQ0bjQ2OFlETDdGR1ctTXlkbkZaUEt1bDNPYlZ1d3RibF9KaEFQMldpeW1rckFyWjBtX0kyTU1LemJtVE9sN3Bla0tiVDl4ZlV3UENHOWU3b09nS0tSOG5OQkE4MGdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>TERRAS RARAS | Mosaic e Rainbow planejam projeto conjunto em Minas Gerais - Brasil Mineral</t>
+          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>11/03/2026 04:00</t>
+          <t>09/03/2026 04:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQbWZYenFKcUV3ejJVdWJLTDYwY0duaXVYY1VhRzZ2UlNuXzh5OTZ6T19QRktEemp4WWI5S2ZqSWlWMVNRQ1FIeGhmVEtWTENVTFRYNWZobDB3blBuc3RTUUFQWnFMaVpLT01YOUhFQXg2UksyUEZMUmpVeUpGdFUtYzc2YnkwRjZDOHJGVlAwclk0cS1fOFJvRS1LN2gzZVR1NGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Mosaic Insights: descubra os novos perfis de consumo no Brasil - Serasa Experian</t>
+          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>10/03/2026 12:14</t>
+          <t>09/03/2026 04:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE83X2QtMTZ3dVdhVHdzOVM4TDFtUjI4TWl1QzlEdjVUR2hFaVd4Rk16WWQtbUpySnBsMHBVUG13RmptX3piN1lXQTBKZHZoNlFRUTZ0VzB1MmlaLTVISXE4RzJKZVNWWTN3WlBtUWpxc0twLWhZSWlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Agricultores de Corupá já podem solicitar calcário pelo programa Terra Boa - OCP News</t>
+          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -8706,63 +8706,63 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOemxVOFYzVUJ5cXJKbGM5eVZQUkpkdEVXdk5DcVlpcnFMYWNYOXdNRzdUdTd0ZGFTeDNjNXZHOFUxemZXMUlKYmNJcHowaktZOFgxYmUyYjliQ1Nsc2ZMUVZ2VW5QU284VUI5bi1QdXpnRGg2aDJtSmZTNGFfa0V6Y2VOQnppSndEMW9UQWNERWdaVnJCb01lQ1dxOWd3UnFNaFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Conflito no Oriente Médio dispara preço da ureia e afeta agro do Nordeste - Visão Agro</t>
+          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>09/03/2026 04:00</t>
+          <t>06/03/2026 05:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQb3lyUUdackIxVkRzVVZNbTc2WlpjbEtYclNqdS00cTM5U212T05Jb0FGN0dWcHFqeXc4WkRqR1hUdU1NT2wwSjZ3bUhXamZTSHFwMUNYWC1PTkRjQ3Q5UkVGVG5mSWlJOG8tcWxfNzZjRUZfNEd1N1drYkYtTFZ1YUxMMkZyZzRqSnk0c19na252TWJYZEFoVjQxcjk1SjFs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Secretaria de Agricultura abre inscrições para transporte de calcário em Santos Dumont - Portal 14B</t>
+          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>09/03/2026 04:00</t>
+          <t>06/03/2026 05:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE9LZXlXbFg1RkYyUW9wZEFjbmY3RW92ZmtMaC11RW8wREJUQWVXTFpYaURxSXlKSVdzWlpkNkRDMGJHejhlNVU0aUpPUFphYjVhVi1obnpROXV6UTFwd2k0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Dono da Cal Cruzeiro morre em acidente na MG-439 - O Pergaminho</t>
+          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -8772,95 +8772,95 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOSElLN2VtTGhnWi0waFhaT2RFM1pjQWkyYVR1WE1kRnEyLUluR0lUX1lRS2lFQUwta3IyekJoOEg5YmxSalNUTFFKTUhWYWNjdTB1Qi1iSnlITWwtYUJkakhYdEJ1eTh6SVpNc3hvNmEyQXJRaDJPcDRIOFYyMFkxVExJakYzQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>"Cal Cruzeiro"</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Mosaic aprova pagamento de dividendos para acionistas e detentores de BDRs - Globo Rural</t>
+          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>06/03/2026 05:00</t>
+          <t>05/03/2026 05:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQMHQ4cjVsQVFTNmdFcHFWTWNSeUxaQWhUY3FvRkF0LUxKcF9oUHprQ0ZPdUhYaFNwYlJDN3pUaTF3YnhPZjVHMkhVNEwwV2NaM0hLTllQa2dwQTUwZTZIWjBiRHFGTWlUallPLXRwU0NndC1YQ0ttbllZVzJkVUl5Tk1aN3lMdTNBeFc1WXd3RlFCcFpMa0ZMNFFFZXR1b05jdXV6TEJvZFZFTTZXVHE2Z0ozaW5adTRZOFkyb1p1ak91MVluaEkyZTFZTDRWZ3PSAd4BQVVfeXFMUG9xZERneW5ycklwM3BUcGVnRV9KaTZsenFUYjRObWthYnRQREpMWUgyamgyWDZQd2FFTUJ3UnlwQnhGSzA1czYxUVgwTHBqTlNuM1hCT2ZkUGwwaTF6SE1hTTZZMnF3V28wWng3WVZRT0xqYlVBYkFfX2gzMVl2ZXk5ajdQUF9NMFgzbTdBa1ZtbTVFUUJxYW5rakFkOW1Qb0hzSjZvZm9CTGhMX08xMDRPQmJEdkxvdnFpZVRoRlJQTW5xV1RpeVVGTUVpcjRqVk44RFNxblNQOTQ5cnlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Conflito no Irã acelera alta de preços de fertilizantes - Globo Rural</t>
+          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>06/03/2026 05:00</t>
+          <t>04/03/2026 10:02</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPYVZhOFowUnN1VW5xSFlObjg1U19vdE16RTRKc09UaU1vclgtanJLLWVSZ3hINjh3QzZkTU5UcFJRbkJTMm1MTU1UZEJEVDA4cVV0eE54ZzZEelFyZTBzTmNaZjhHazNpc0ZHTElIVTJHZ1VySWd3RnlwY3FEMU5wQlI2MEJaTkZhd1E3ZXNYSVZlSEU4cUhqemJsSUlwVTNrZV9nSTlLbHBla2V4eUQ2UGdJZ2HSAcMBQVVfeXFMTWR5MEtub0FYbkRpa0lUUlI0VTlmRE8xcW53OGNKdFhtX2pxZkZoVGNGUUVwZzJyN1NtYklFaEFBTDJmM3RldXhvRFBSSnpVSFhLMUJnWndyNFVKM2p6Zmt3U0JYX19NZDJ2X3hQcVJtVTlLU3BRaldad3BvbzRnWXc0cEhYX2h5Q1hkbmFvcTg1VnU1aFF1bGcxdEZ4RTB3LXYtcS1hRkgyRGJmZThrZzl5dHFzMWFyYWpkTlR4T2ZfT19V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>"Cal Cruzeiro"</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Diretor da Cal Cruzeiro perde a vida em acidente rodoviário - ultimasnoticias.inf.br</t>
+          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>05/03/2026 05:00</t>
+          <t>04/03/2026 05:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPYXI2UzE3ZHk2cnloTXp0M3kydHdldjB0OHJid1ViUWVPOUZ1OGJvbW5uVVdSeE9kamctRTdoWXU1ZEsycHRBNlVMZHUxdHVWdTh1YjB2eW1PUVEwSUZCc2tMcFFHRWdmeE9zN3ZkZEZHRUctdkZYMndLd2FnMmwtSWdOMFBDelpuckIyWlhyS25FMlk1b2luaThiRE5GYjlf?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Agência de Comunicação - CBPM obtém liminar que reverte venda de operação da Equinox Gold na Bahia - Estadão Blue Studio</t>
+          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>04/03/2026 10:02</t>
+          <t>04/03/2026 05:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOdDdnM0xnUnRYb1dQM3hXdmh2MG5VdHpYQks3WGR4eERDZ1BLQTJtamZ0bjVwOWlwVDd1ZF85cjIwWDBVMC01VmVuOFB3ZGpzdzMtQlRxd2daakg2eURSVDlDQXhFTndiZWVEckxzdFJQM0FKbHNjTi02NzBPc0pKdlk5MjRVYUhWUkpOVndSQlRhNEYxME1yUWNsLUdONTkzblV3V1hPSFdhTlFzMWgxWkdoTDJoUTRTZzVpWkxKelN5UEZySmh4V1N4ZUlQYjZkMlAyV2dxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>JUSTIÇA DA BAHIA SUSPENDE VENDA BILIONÁRIA DE MINA DE OURO - - Bahia Economica</t>
+          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -8882,19 +8882,19 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNVGFROXRCUlk3alljZnJUbDU2VnJqS1Y2ZHhheEM0UUV6bERYLWtHYmV2OUpMdF9MUGtDUlljUHg3eVBnamFZUk1GUEk2NTRfOV9YOFM5QndQcm5FTDh0NVlXNGVOVjR2S0kyaEMxTjI2RnBQZWtUMzlvdGlKRUs2QU1HR1pjQmFhYi1xV2hVZUg0bVpqNE54aDE5NGdNcWtDcWYySnRR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Fertilizantes puxam alta de preços de outros produtos químicos para indústria, diz IBGE - Valor Econômico</t>
+          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxOWjd4MFdUanZwVU1jUGhrbTVtempwWEFlRWt3RWZNWlNyQVp2RnRNY2lNTGtYTWFNbGRibVVObUlEVGZXNnZqN1pwYnN5Ul9DSlBjSTgyYmlzV3VseFVFbjlwdjRCM0UzekVyNVF2LUY0ZEpxanE2aFdWdnBuRWJDYTJYUnJjYVFyaUo3dUFtZ0tTS3Awd3BLTjBEcVZfNFpXVlpMSTdCSnc5YW9GNjNTT1poT1RteF9NMVNZUzRzUXdsSXlGX0JYZ0o0R2RDYWZZcXVRVnk3RXV1d9IB6AFBVV95cUxOc1gzenZmMHEwTzFZWkprT2FDd0hTT29qUmZrNFdpd2pxWC1hTXlCZ0YxZkNZdm1sR3E1LTdkWm44Vy1XZHZYT3lRaG5ZY01OdkVyUzZSUEczSFNpSk00YmlCM0N3ZUVvOHNZcy1rMExWNlZlM2VPUTZSRFc5QXhvY1dIdDhBSC1FOVdQUlVTa282Um94ZWtHRGF6SHNVcm1vSGl5NENxSy1TTTdTNkRqcUNKS1QzZTZtOVJtZ24xSDBEUFlibnY4WWtQN0d2aDNpZUJ5TDFpMVBrRHFOZTdPOXE0U1pITlpo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
         </is>
       </c>
     </row>
@@ -8916,17 +8916,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende venda bilionária de mina de ouro entre canadenses e chineses - BPMoney</t>
+          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>03/03/2026 05:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOV0F3R0dXNDk1eVUxZDJ3SF9QQUE0anFSeEkxOEp1a0dfMXRGZ2lRNTgwbDJsSlhJcjljMVJXS3ZxRDFEaUFUWFpYdmFXTE51YllrZDZSY2JMaGRWTTM2eFRxamhkd0hRbUFCVXY1LWpKbnJzXzNtN3JOMHB3dGdZU1Jicl9mTFdVN242eFl1OS1MLVVvdGtyN0tqU19iSHpmdzdKeDROMVltV0tzS0RfcjhFNVVqT1df?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
         </is>
       </c>
     </row>
@@ -8938,17 +8938,17 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Com a guerra no Oriente Médio, cotação da ureia sobe 10% no Brasil - CNN Brasil</t>
+          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>04/03/2026 05:00</t>
+          <t>03/03/2026 05:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYW9TZEpwLW1mVXFiU2xTQ202YWlDdXRJTzZGdTBNbExhTVk3dFFWRU1MeDFOZHRuZkd1N0dmQ2o2MkU4MmwydjNMektWZHBUSGxhZlVZcnZFRlpERXF0M3U5VHBnZHZONWlzb1MxQlVZc1FGUEhjV292Mkw4dXZtR1JDRHVZU1ZTY09pQTdiY2REeF9OYV9qQldLNjl1SXVN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
         </is>
       </c>
     </row>
@@ -8960,83 +8960,83 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Ureia dispara e mercado reduz negociações em meio à guerra do Irã - CNN Brasil</t>
+          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>27/02/2026 05:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNYi1XSk5GWVlFUFlZVzR2UXlURVpUajhfTjd5c0tBUUVqVUkxQy1OVFNfc3M3eDJWdndqSzJSZEJYRTdlTXI2ejdGbmlYQ1pGUmlkMVlJRGtIbmVZeDdNLXM2YS0xajQxc0p1b2pKYjJmT2Z4TGxBU0VoUTAxRlFuYkZNUWVGZWsybUdXLUxrQzNvcFRnZnNLQkxjQTBLTW5mMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Justiça da Bahia suspende negócio bilionário de minas de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>03/03/2026 05:00</t>
+          <t>26/02/2026 05:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxQYWNULVM2dHlzUUd3UDNyYUp6SDZrdGs4VjJSdUllMlJYQWFMdkJJblVjaUxfSGpTNXJ6S3gxOENtQTl3clNIeG56VVpVZkdWNWs5a05DWE04N3ZyZWJySzFRZEZESVhiVEcyMHZSWUVETVRaOUtnWlMwLWNjUXY0Ti11ZjF0UXJ0ODNXcG5lYldORXJuU2JQX0xaTHJBRGxKVWk5QmFwbVd2cUc5Z2wtSk5oNC1vV3F1U0U1WkJGMEhDRHNWVVpBNmltMVBzUTdnV0Rqbm8tcFTSAd4BQVVfeXFMTlE5cnFkMU1MWjZsaHVCdkxKM3JmOURJV25ZSUh3LU1xc2RsYmZhTzNOaEZjRGlBeTg5RFRndzE5X2h2cGxLb3BQYXY0aEc4b0dkbjh4VzdLbmRudXlYUEhwU1pnZVRGODRvY0ltTEsxWkE3OW15ZmZNOTZYdHRuWXN0ZzJMMnppM3h1WnBHSW5XM09QVVdBWlRBZFdzc0o3eDhvc3BUdW05VmhIRWl2RVVaUFRtRGVCWG1iSlFTTkpBTGwyS2RRc1Q4aDdjSFEwbzBsOTJTbU5lN3g3SGd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Venezuela: ataque dos EUA dificulta embarque de ureia - CNN Brasil</t>
+          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>27/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOc1QwVjNFUlRKTWc5LXFXYzh0NDl2RGtrWTEzQWpWc2E5cmZZMXJ3M3N3R0RzMnJQakRDbHVFcUVnV1hYSlJ3R1FNaEJjZFM2a2RTWWx5azVOeW5KZGo2dlNoaS1mUzJnSnJIajRBckl6TmdLX0VOSjlSMUowdjN6bndwaldrSVQtSXhnMVZPSEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Água da Europa deixa o cabelo 'pior' do que no Brasil? Entenda os efeitos do calcário - G1</t>
+          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>26/02/2026 05:00</t>
+          <t>25/02/2026 05:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNSmYwcUxQbk0yTW9FdFhMbDlPRnF0OXNTcVRQbXhIM0g5dGNzbkVGS0lMR2htNXI0dm1uQVJNaElaY2FDOVduemRVb2N5VWRPdTM3WnpISUpaSXItZ0x5N01HZ3d2WU9XVE14c0ZoaWdJVVpUX3FMX2ZXOWNEM0NpdUFFMW0tUW5rY2JpTGRVcXJuaGM3d3dEdmhNSFZmdXFrZDQ2T0ZCTTlBM2Vpd05HbUFDaFNiVzdpSXFXVDE5QndlOXNEVy1NRVk5OGg2azTSAd4BQVVfeXFMUEVCUXMxOWxPekRlX05jVFVRRG50X0lMY0E5eTR3TC1CaWVqc1JJbFZxb0JKVFRiOW1fT0Y5ZU5UWmlfX1ptRnRnTWZ0MjY2TnozVWtLYnM1WmFjdmJZRVhWV0ZSTWRGS2VENDdKUlhMTnRvQ1VqNU9SdUZMUFlOTEJKZGV0SnMtR0dZZTZzNXoxRzhveW50OGZDcy13eW9Za1Z1N1Y4YkU4cF9naGZwSWVpUkpPdERWVS1JRU9CWXVDV0JXblp5VEJIajZjMGU5NnZnVzUzYkdWNGZLcFdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9065,56 +9065,56 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Mosaic confirma quarto trimestre ruim, mas vê lucro triplicar no ano com ajuda do Brasil - AgFeed</t>
+          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOUlZZR1AyRF9aRm14eldYQ3FwYXVoaTdRMHBsR0FpMmJGU1liUVRmamEtYUVIbmN1a1Vkb192b3BxclpiZkw0VzhTUWdJb01Vbm11c1NXZmtRXzdpaUVNamFkR0J3YnVpVnZ5R0pKUWltUGJhajlpMGdPak0tZGdQUUEtZ0VxTVhMTXBxcDhiWEF2Z1BIWnc1MlRpM3hyajV0VDhKZ0xUR1FFVTFxNzl3WUtoWkxfQlRyQnFZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Mosaic tem prejuízo líquido de US$ 519 milhões no quarto trimestre - CNN Brasil</t>
+          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>25/02/2026 05:00</t>
+          <t>20/02/2026 05:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQUlhzbk4yVmMwNGRqVURkaHI5N1FqWE9oNTZ6VlVqYlM4a0Z1T25XZGdSZ2NoVUR1RTVzbXFOOGlCUklocF9Ia0MtMGZXMXoyMzhzRTd5OWJEN3o0Q1U4RU51TVZDbW9tVkZzeXBobjJPVEE2cldCS2N0azMxWTJIOWgtTkYwdFJCMGl4VVEtaFZtUF9mUW50QzUxMjg5NjJrdnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Custos da safra 2026/27 variam em MT; algodão e soja recuam, milho sobe 7,19% - Nativa News</t>
+          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -9124,19 +9124,19 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOWnBBY2Uwc2FseU4zdDQ2aVhkdWdVNXJGRDZJR0tTZ0Y1UWZSREc2ZDVySi1rMndqSkMyWEgyVzVQTGlOSmhKTEgzWXRfNm5zd280WW5BUFhwdFNYemdvc1dqX095TG9kQ3dNSmU3VmdnNFJkMjNBeHZSZEprSzBOVHhLSWEzbDcyZUNnbnY1U0xpLVZTNVBHdEVFMDRVMVlySU1XNHJZQWdwbVJ3QkVuZ2lMWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>CBPM contesta venda de ativo de metais preciosos da Equinox na Bahia para chinesa CMOC - Bloomberg Línea Brasil</t>
+          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxPWXgwYnhxbzhZaGZOZHd3bkxXbUhQa1lOZWxiVFBfVWp2QjZWMW5UVnB3U2d1ZDZfSlRpSG9MSVJlODlhX3VjZ3NERE42OVpnSG9WdHhXdE95Umh0YjBhekpSTkppQ21oWjNEeWFUUkhaRVlIN01HekxWM1RpbWc0dDBjeUxHQU9GZnRTVl9COHFIWE1CRlkzMnFCYTNvRU9BR1NYSGptRzRHVEc2akd2Tkk1UmdiTklhX3p0UEFCOUsxYlhSMkNwWnlR0gHeAUFVX3lxTE1zOExaOFF5OWI5VUdVQXFXZG04cDVEd0NVS1B0ejh0R1UwTFQ2QUwtRDdfR2RjblhBREhmbFFYTVFQLW9zT3R0SXJyVmZXZkl4X1h1bUk3TlBhMTlCNzlIQUJEODhBc2RZeEx1cXBKR2xEeHl4TlN4Z3FnLTVSSG96b0lqbF8zRU9yVlROZ3JwR0F3UUlrMlpiUlNaRTdLWE1jZTJ6N3JyTDBMN3E0cmJlMzNxZi1rbGlBbzBPQkFhczdFRWtXZGRaWllFQ281YWZOWkxYMlpHU3FzSHpvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
         </is>
       </c>
     </row>
@@ -9158,193 +9158,193 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Novo presidente de esquerda do Peru será julgado por corrupção - Gazeta do Povo</t>
+          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>19/02/2026 05:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOWGxsYkZLamdUbENJS0dQVjF2T18xODhVYWNfcHFNZGpJOVE1Q3BWSER5V1R0NXRvalpObHdzcmF0TEMteFJpRjNrV2gxeUVPU2NkSUpjS3Rta2xfNkxkZURnSnhOeDJvY0Q1Q0c1Z1JEZVRwc1RhS1RDX1pLUWVVZEhpSXVRQzR3X2xETHVTVEZvQnZmV3JNblBJYmVHNDgzV1J3VndMUjlPSFdnc1Y2T1RaRGU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>cal agricola</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Um dia após ser nomeado, presidente interino do Peru é intimado por 'apropriação indébita' - Opera Mundi</t>
+          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - paraibaonline.com.br</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>18/02/2026 05:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPay1sZXVrRnVUZlJFNWU0cGtSb1lULVI5R3FFQWhXdTJhblFWS1NwcHh2aFdRX1lYV2pfakFlU0FyTTVqZE15TmRHcGZPYmJJLXZOSHRmR2lCM282NWM5WEhqR2ppRE1kMHhELVRmX0lZb1FXeHlIRFFRT1VXSnM4NjVfNkEzV1MxMlJaZTVNYTA4NmhnZkFBbTJiODNxWVFRYjhFa1ZGamhVV2oxdzhyendSZVRUd0VoeXFOemZOX2RpSHVIbHlJVDliTmJlQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>CRA vai analisar redução de alíquota sobre o calcário de uso agrícola - Senado</t>
+          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>20/02/2026 05:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeWVQYnFWb2NCX2FFS3ltNHh0enBBZFVrS0tCSVJJb3ZBQ1FldnRaUVNQNF91WXN1V0ZNd1JENkVjVzBmVUNwS2RDTTZ1eW53WndKTDdHVWtUUmE1UDktTUsxSjdYMzBiMzJkV3B1aWY0d2VmczFJeUl6ZlpjRXd0VlFZUTlIN2tHQnlrRXlYNzZ4Rk5ZNThGWGtaZV9BSVV5SUVFNS1yREwweS1aQVMwOS1yZm5yQThBaDNVSnZKb1VWV1dO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Quem é José Balcázar, eleito novo presidente do Peru após ‘impeachment express’ de antecessor - Estadão</t>
+          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>19/02/2026 05:00</t>
+          <t>13/02/2026 05:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNYVhsZm1rdjFZbzloczVNbENDbEFwTWxCNjZFWjlmQ3hHQk1TaWRNN0pEcmpXZ1RxY2NUMjBCU1JqQTJhWGdfUDJrLUZ4Nm9KZ1drbklMdWFJNXgyWkZFaE1faFFtbng0MDRZbWFsV1I4d3JSMUs3b1hKWHlLOTUxRUtnOHA2b3o0Yk13UlZjYzZYbDZmM2pmdTJpcXlBbnhnV29tdWFTVjdnZE9femFvSm9CbDl3Yjg2dVFrWXZlTkRROW1xWW9JSU9Cay1wVTJXckHSAdcBQVVfeXFMT2lHdENCUHVjQVlBUDlMQkVkNWNGVGhBUXUtQVJmQUJnNnhoWndMQlZTUGxjVHdYTG1pUHl3V1FkbUlLZmlYTUxKckxmWFVVX2NIRXJfVTMyMk1OZkRwalM2TkJDdzFpRXpIeXRfcDZ6ZDJhUHJRblZuMFA1VFFzcmNsMXpud1lZVGJMZGNQS2l1TmZSNThjTTVWVkVCRUdCSnc1bTh1Ujlua19uUTF1ZTUyZ3o4QXFJM2pJV29UcEdQZVNXY09QZmRQRDg1aXk1RGFqRURDWU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>cal agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Agricultura orgânica: aprenda preparo de calda para controle de pragas - paraibaonline.com.br</t>
+          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>18/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxNS3pzSjFUQ0VKY2VDNjJZVkVHaWZKT2xjclQ0Q0QzaE1ZclpEX1liX1E1Y19iMFNtWTR0ZlBtQnBPSlZjX2lxQ3dPM0FRM3BPOGg2dmdMWUZ4Vmw5ZEtZeG9rMXNoV2JKWDB3TTBPd3poaGJMXzBBUm91N2I4dWcxRmtDTWgwLTBINXQ3MTQ4UHdXbGFWUU9PTHh4Zk01OWVyNU9KMzV1SGRrMGw4ZzZhMkFRcnNEdDJ5N0tZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Programa Terra Boa subsidia aquisição de calcário, essencial à melhoria da produção e produtividade das lavouras - Prefeitura de Lages</t>
+          <t>Preços domésticos de enxofre enfraqueceram, enquanto os preços do enxofre portuário permaneceram firmes - Sunsirs</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>12/02/2026 05:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPZ3RHQm91RjZUTHh5WEhFQUI0d2RpaEJYR0lYM1liUVJPMElqeUg4U3dQY1FjdkJMUU5wS1FOS3RaMGlxUms2MUpMSFZFTVMyOGRrQU9JcERnU2VVNnNJbHljUUhJdjFpVDZlTWl5Vno5clVUR3YxcmZ5VDZiLXJYa0xqc2dJVWttd2xOZFdCN21EdlhiT25EY0ZOclVndGxXQU45UzFFR1VvdjhUZ3ZLV1c4ZkpITndFMk1GSmZiMGpBVVVQOWk4MTBTOUplLWVtUU5qaDFuUVZibURHNjEyQmE3a0FIZ0ttRFU4X1FrME9qdHli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpUHpyeDNlaGFXZGtXb0JTeV9CaWVmTEpQZ19FWmVIaC1kV0J6amJVUzRZRVFOU1ZIVWhaSEtQSFE5ODZ0SEROYnV2OXVINXJnQXpUZ3JTV0g?oc=5</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Como monitorar o enxofre em lavoura de soja no Cerrado - Notícias Agrícolas</t>
+          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>13/02/2026 05:00</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNODFZUlpibktCelpQVkdtOWpPRS1sWGtCZERVZlhpcVZ1MFF2UF83RTQ4bWkyV1ZKOS1FRWhfU1FZTHVEb0NHVWNaUUNzZVh0Z2wtTm9WZzVrcTBRX1gtUHFLNFpsM0g1Q3dfWHYwSlltQkM5V3lSWHF6Yk9Mb2Z4V21Rcl94aGpFMlVtNkhINmpEVE5JTklZMm9MRDAyaG5GN2dDRFU4NTdWaVdzbzRVN19fTUs1aU5tWThFdW1yVdIBxAFBVV95cUxNQUREVU1ScmxfQ1EzbGoxNUNiMzJ6RENlNndmYV9QQ2NFUlRDVG1YVi1TTkVYMkhYd1ZMQmFwLW1ia282WmQwTUdjMTlXQ2E4QTFJT3Myb1gwdVdQY3R4Z3VzaS1HUWgwWmcwRTFxTm5PN2szMUFWOFhkWkVuR2dWWG1haG1QMDM5R2hrUndjbXNKWllkQWZuN3hmcWk4VGthU05TT2NBRTRxVXh4bUdKUW9mT0E4UXpLTjVBY1dkQ1dQTW5h?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Preços domésticos de enxofre enfraqueceram, enquanto os preços do enxofre portuário permaneceram firmes - Sunsirs</t>
+          <t>Marco Histórico: Victor Coelho celebra primeira operação de transporte de calcário pela Transnordestina em Ouricuri - FalaPE</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>11/02/2026 05:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBpUHpyeDNlaGFXZGtXb0JTeV9CaWVmTEpQZ19FWmVIaC1kV0J6amJVUzRZRVFOU1ZIVWhaSEtQSFE5ODZ0SEROYnV2OXVINXJnQXpUZ3JTV0g?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPaU5meFFvcXlxY2VjZ0xRbkt0ajI1cE44dERBYk9LWWRxMW8tLUhSUGxZenU5VWZjYVBQSWprTHhLX1VON2o1RWhVTm0tM3cwd0RJN19GbUs3UlNaOWI0VWhTYjg1Wnc2aFNyd29hSnBxQUJTdHNuUWhLRWN0RjdtOV92SDdBckNoN3BCeFNPRVA4WWtoRjNnd1NVdnRMWUV5MHVTU2lTdVRZVW5lZUlhUm9teExyX1dWSmpnUlJTQ2RHaW42d2VQemNYaGVEZ1k?oc=5</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Empresas do Araripe começam a escoar gipsita e calcário pela Transnordestina - Movimento Econômico</t>
+          <t>Domínio mineral chinês — por Márcio Coimbra - Revista Oeste</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>12/02/2026 05:00</t>
+          <t>07/02/2026 05:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxQX2Zpa2cxcGRrbUREWl9iX0oxUTdIYUZWWXVmNEdHaV9oLS1pcWdLWDhLYW4yMWw3NnNEQlVsU2NQUEdVRlBMWEFuVUtDS0tteEpSTmNmRWMxemZfb1RKVUtEVXptSHV1VkVuMWdEQkdPellZb2tNMEVkQnE5Uy1fdWV2RGhlZ2RKRmxWODhhSWJ6ZFIzNjZqcFkweE1SM0pJOXF0UmxPUTNSZ2ppTndZNHdweGFjMm9wRm1xZXQ2OEZxQXFJdzB2VFVzTTVUak1KU2pIY3NDd0RlR3NEWDczcmhQTVdOZ2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE5Kc01kVmlWMVlaaThURGlzOGZIWkUtZ1QwZ1RfT0pCa20tdUt4RXdFY1NNNDJFVkstdjc4SDVLR3VnRS1zWF9OOVdlQW1kVWZGblJOdXFuMHVnMGVyNEdfVnZuUlhhZ2hV?oc=5</t>
         </is>
       </c>
     </row>
@@ -9356,39 +9356,39 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Marco Histórico: Victor Coelho celebra primeira operação de transporte de calcário pela Transnordestina em Ouricuri - FalaPE</t>
+          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPaU5meFFvcXlxY2VjZ0xRbkt0ajI1cE44dERBYk9LWWRxMW8tLUhSUGxZenU5VWZjYVBQSWprTHhLX1VON2o1RWhVTm0tM3cwd0RJN19GbUs3UlNaOWI0VWhTYjg1Wnc2aFNyd29hSnBxQUJTdHNuUWhLRWN0RjdtOV92SDdBckNoN3BCeFNPRVA4WWtoRjNnd1NVdnRMWUV5MHVTU2lTdVRZVW5lZUlhUm9teExyX1dWSmpnUlJTQ2RHaW42d2VQemNYaGVEZ1k?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Tecnologia captura até 95% das emissões de CO₂ de navios - Fast Company Brasil</t>
+          <t>Ações da Equinox Gold caem quase 10% após CBPM contestar venda de operações na Bahia - MundoBA</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>11/02/2026 05:00</t>
+          <t>06/02/2026 05:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPM0xiM1JFaEhZME4xSTFHTlhycmNXem9RdjI1Zm8wYmY1cS04VHVWUURZWlBRRzdvV2VEYmFsaWxPT3g0VmVYX1k5eXFWUW5KM0ltU0J1amh3UHhqU3I4RHdZbzNsZXJmQk1hV1pFUnZOZnVlazFoN1cwdFhtOS1vWU9BdXVBT0tZSkFVc2kxMnhWd0tEMGFYcExsbnI1dzBqMVBxNFFYeklQV0kxUmJDcVpWNzRWMUdPWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPMFU0djRndUxwdzhrVXI3OVdVamZ6YTlWQVowbGhaSlJzLTUyaWl1SFBkTGFNWUd4R0hDTTJhRVZiajNWSFBCeFBGcTd0aGxyMVpkN1djZkJWWDU0NTV0ZnpfX2xCZ2lDQWZwT3pKa29qOG9qZUFDdjl0U0Q3WTVNR19wcnJFVWc4WWFCZXdkZ1VMZUl1RnBldVN1ekh2QXJOSFdGd3dJRDlMWnAxWUY0NjdDRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9400,17 +9400,17 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Domínio mineral chinês — por Márcio Coimbra - Revista Oeste</t>
+          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>07/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE5Kc01kVmlWMVlaaThURGlzOGZIWkUtZ1QwZ1RfT0pCa20tdUt4RXdFY1NNNDJFVkstdjc4SDVLR3VnRS1zWF9OOVdlQW1kVWZGblJOdXFuMHVnMGVyNEdfVnZuUlhhZ2hV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
         </is>
       </c>
     </row>
@@ -9422,61 +9422,61 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Ações da Equinox Gold caem quase 10% após CBPM contestar venda de operações na Bahia - MundoBA</t>
+          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>04/02/2026 05:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPMFU0djRndUxwdzhrVXI3OVdVamZ6YTlWQVowbGhaSlJzLTUyaWl1SFBkTGFNWUd4R0hDTTJhRVZiajNWSFBCeFBGcTd0aGxyMVpkN1djZkJWWDU0NTV0ZnpfX2xCZ2lDQWZwT3pKa29qOG9qZUFDdjl0U0Q3WTVNR19wcnJFVWc4WWFCZXdkZ1VMZUl1RnBldVN1ekh2QXJOSFdGd3dJRDlMWnAxWUY0NjdDRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Correção do solo 2: Formas de aplicação do calcário e os resultados da pesquisa - Notícias Agrícolas</t>
+          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>06/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ0hBMUJwVjlRWVlXcXo3MHI1M0h3bklvSkk3enp1eTBiM1Y1cjNWMjF3TjBPTFRKQkhPMjUxYWxjREJNRU1vaHVlN0xfcTBpSTdoWlBDZk9UdWV2RDU3OGNHMnppV0U4R0w0VUl4M0ZwT0ZCSzZRVkttZHNFV2t5YWU5N0o1OXJxdXBSQU5vVXlHVW5jaEdxYlJUUnMzZ0FNTzVXbWRyNHJScEg4blBPLW1wcWxVNXpHaTBxQkZkTDhqRnptNVHSAcsBQVVfeXFMUEk4c0ZPT3pFdGZETWNxWG5RWEdJSWI2WnllSnd6SHM1WS1nVkM2NEVIR29kYlhobi1Vc2ZxenpYR29VYkdyV0FzTEJUMHpuYUVNTGpWNjVpNkl5M19VZ2hMc2s3aU9OZkNqTElpV2xfV3YzaGZEMFpMVEFSSXhaQkR6SXMzTVRON0FTS05vMXdLSzZLSTJCZVR2ZzlTcEtDYjhVM1JYNjBIV2syNHU1d2ZBbDg4TkdQWHJVSVVuNWpXMDBMb3hqekZudVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Estatal da Bahia tenta anular negócio bilionário de ouro entre canadenses e chineses - Folha de S.Paulo</t>
+          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>03/02/2026 05:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPVUlXUktSbEdjOC1NTzE1d0ZIVmNad0RVMDE5VlpBWGh0X0VkZkZqSTFuR2EwNVBpNHVnOEtuUWdaTF9DeGRIV0FYNW01M3E5c1ViZVgtT1h1VnVhVFRoZnVRNDNNbm9fVG5FMmVGQTZiU2w4UmlOTXVwRnZIaWhzNjNXTXpEcHRRMGZ3ZmYxazByT01MZXJiRjhLajh6X1VEdjhILUtaZllZa3BRZUZVcGJXTmFCRjF4bDRWWE5FeUQxYlNabF9mMnlvMER1akRaclHSAdcBQVVfeXFMTmFLYWxidHM1czVENlhQTzdaSlZmSUZmT3M4LXZtV2k3ZXBranlIb2F3clBQQ3lIaWpIVC1mNXoxZUYzaVc1cDFLbUR2R0VydTNsZUktcWVKRkZqeGp1TEhKUTN1Z3JpeG9wZjItdzJyanlUTW14WE1yVnE5VmNUa3FVWXNudnNzeEdyUEIxbklVSldyRzVoR2tMcTVIQXEyTm41ZVRMOUpsVmJfdVBLc1RscS1zY1JPYW8tTUlmODdRbm8xMmF5NWV3clZqdURDTTMzVURncGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
         </is>
       </c>
     </row>
@@ -9488,61 +9488,61 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Negócio bilionário de ouro vira alvo de disputa entre estatal baiana e mineradoras internacionais - G1</t>
+          <t>China vai investir quase US$ 1 bilhão para assumir minas de ouro no Brasil, controlar milhões de onças do metal e reforçar sua posição global no setor de mineração estratégica - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>04/02/2026 05:00</t>
+          <t>02/02/2026 05:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNalRrbEVWVGYxMWtjSUJVREZfM254QjYwM3BSLUdlaWlhb2QyMERZcHBrajRVLUtlYmZieXJiUnRpM1NENTdtS0ZKc3R0am45SmNkSTNfVjJ5akMyM00xdC1TYTlULXYyVFEzMF9OSWFNRF9yM0cwVGoyaFdZcmI2QnA1MTRoeE5OeU9pSXNlY2JhLUhXQnMzUzMtY3dmQdIBrAFBVV95cUxOYy1aYldiLVZyWVd0Q1ZMS05VR1pHZVJLb1NqZUFDa1dQR3NRZ2x6WEtSX3dFbUlQalBBa0FmWkNrUVZHQ2lxVUR3T2pSa2s5WVBOQjhFNEMtTW43MmxjM3FoaUxLak5yY2EzaTk1aXBWOVhBUjNLRjY1M2d0U19sekxZQzJLcnlnbDBzd2M5TXdzY2tnYkJYLWxIem5keG4yVzNHcDVDZHdyaGcx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQMkQtMmxTWjZWVEdwcmZYell3OU1VRTl6Z1BTS012WVV3UndnYnZMZ0dLR3pIeElIUndoTlhXLTlQUTVIQnVzcTc4UTgtcm1HSmtjWnhOVkxJdktFSS15dm9jSXpJR19zd1RhcTVzV2ljV21mMnYyMzNoWngyTkt2RmRKN1doQmFEZDAya3BYQ0VOYkN3d01UZkZET3dKWFFSNTdZMEI0bG80Z0pLMXpyWWtQR0ktUG5ab2pISlZVWFhGWVA0cV84RUR6R051Uno1WVd2RVdmQmdiSEhpZ25HQmJjMA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>CRA deve votar redução de alíquota sobre calcário nesta quarta - Senado</t>
+          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>01/02/2026 05:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOeTNjVGxONFNqaV92QmFjbHM5a2VHMHgwNE9sNkV1MzNBNnowdjFiNjhjdm9oeFFsNWdxX3p0Y0xRMDRJMmNRdDV6eEtZOFNwU3V2RURWc2VsMTlVMEZLcXN1aGJ6ZlNMa0hxTDF3ZDhlMTdMSXNCTmw2bGNtZVBEakhuY0NBZjVrUEdUNXFfUk1TZjM1U2hERkl1Y1BaSlZ0QmJVdnY1V1pVSXd2NGFSbnR1ZkdaUDBWREtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>OURO | CBPM afirma que vendas de operações da Equinox Gold quebram contrato - Brasil Mineral</t>
+          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>03/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPNFBwekZndlJnNUxDQjVyNDdDUy1JLWdnQnR5V1hjQ1lXdnNlQldOWHR0cGRWMjJFOVFkTU0tektGNlZZUWdkYm9CNU5zQlpEYnhBTklBYkV2TzJVMWJ6MU45VTluREZyd1lDYVpBWnd2RU1CR0pEZDVITkM0cVZabE5PUkRQeVItQV9VckpZR20xOWwzUWNkSTdwVG9SbVhBMk1XejVwQTh3dXRVeGtF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
         </is>
       </c>
     </row>
@@ -9554,105 +9554,105 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>China vai investir quase US$ 1 bilhão para assumir minas de ouro no Brasil, controlar milhões de onças do metal e reforçar sua posição global no setor de mineração estratégica - CPG Click Petróleo e Gás</t>
+          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>02/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQMkQtMmxTWjZWVEdwcmZYell3OU1VRTl6Z1BTS012WVV3UndnYnZMZ0dLR3pIeElIUndoTlhXLTlQUTVIQnVzcTc4UTgtcm1HSmtjWnhOVkxJdktFSS15dm9jSXpJR19zd1RhcTVzV2ljV21mMnYyMzNoWngyTkt2RmRKN1doQmFEZDAya3BYQ0VOYkN3d01UZkZET3dKWFFSNTdZMEI0bG80Z0pLMXpyWWtQR0ktUG5ab2pISlZVWFhGWVA0cV84RUR6R051Uno1WVd2RVdmQmdiSEhpZ25HQmJjMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>China vai gastar 900 milhões de dólares para levar o ouro do Brasil - Diário do Comércio</t>
+          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>01/02/2026 05:00</t>
+          <t>30/01/2026 05:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWDRpY3Jud3ZwV1RMTVBJQVFMWGt6RDVuNWZ1WTEwX1l2MTA2cnM3VGNzT3dId3FTNm9VdXdiQjNLWnZGbjhONDRBRFMwU2VtVDBsRmlLdGE0c3Rrek5YU3BYR3ViTGt0OWdVV1Z2S1kwLVJXVEJHUDh2dUdjd1dJeGthc1NabXJkcVlabWZaWU1NVm1jeGxLWnQ2WUFnaHBFTUtEc0F5Yw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Programa Solo Fértil garante transporte gratuito de calcário a agricultores familiares em Sidrolândia - Prefeitura de Sidrolândia</t>
+          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>27/01/2026 05:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxPNDhDY3Y4R201VG42YXpqT2loUGJSYzZURWFwTVhlTXB6TUtIZ3ZtSEYxV25LdEU5OXVIM1B2RGp6MUIyM01VUmdKQThSVjQzTFpPR29wU0xGemZheGw3Yk92U185ckkxT2Fob2tPT01UWGU4MFRlRTRnRVViTUZTSzBNYWZQNHZtc0toZE1qRGdtcEVFQmJVVWVSXzE0U3M3ZDFxNWVHc1I2V3hKOFJxRlBxWDFtdEt6N2ZkdEJTekJKOHMwS0N0QmhQMmFROTY2ajgtSEhRM25GWERWdE1BbDZIaW9hSXp3NURDeFdBNXVvaEVCb2ZFMHRPVlJmTHQyaHZwa0VmNDZ0SGdwUW1Z?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Gigante chinesa gasta R$ 4,7 bilhões para extrair ouro brasileiro - Diário da Região</t>
+          <t>Agricultores de Rio Preto da Eva recebem 6 toneladas de calcário - Amazonas1</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>25/01/2026 05:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPZTlhZnRfbDN4VjNpS2VtZ1kzR3lhTTJjaDNHYVktX0JaSjZSdGt4RFRfa2VPZnlqcWtIUW1kRS03V2NzY3B4b2dIOU9lRXN6cV9tUm9HcEJvcXl1Y0haQzRmMnBiVmVPazBhbExtQlNidjN1RHNUOXZHS1gxWHVrM3RwRDUtZHowVm5tQnY0SThNNUtNNUxGVEtSOVZJQk5YRHlQbjVmNFQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPUGFSbXJwbzhHMGZTUlM2Q3FIWDlpTExxVUJ2SVB0QlZxQU5laGF1WC1DZ3hpZEt6QnVqX2hvWGZuMC1XZ0dOcHcybkVjaWlyWlBCTkJNREpZX1RpRDZDTV9LRlhIZUV2Ry1pckNHTXM3anVuMU02UHg5QVN6NG4tOWlZU3UxU1VBVV80SEVVMTVsZEcz?oc=5</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Cientistas descobrem molécula no espaço que indica a origem da vida - CNN Brasil</t>
+          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>30/01/2026 05:00</t>
+          <t>23/01/2026 05:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOMUU2NHlFRDNUSjdSQUdPUllVQi1ZbC1UeEhUTEpiQzhITm8teWR1czBGQ2JYaUZDdEdhS2NxUGF2eHU3WjNCQThrOTV3d3BoNC0zOW1oMnhNY0NiMm9ubXdBVk1xa01IcmpMemNaYjhjeTJhV1BJOElvdEQ3bTM5azVVSDZZejdxU0hwb1Jzbnp0OE9ybkFRWjk0bjBqZXJrNllQdXUtRTU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
         </is>
       </c>
     </row>
@@ -9664,83 +9664,83 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Negócio bilionário faz a China entrar de vez no ouro brasileiro - CartaCapital</t>
+          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>27/01/2026 05:00</t>
+          <t>23/01/2026 05:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNFdxT2RJVUZPMmhHNmdJMU12a2VxWDlSYXNjOWxJLVNCRUFpeS1zd3VGd2ZtVmxqdDdudzBLYjZkVmRGSXM1QWM3cVplTzhNWDFFeDJMTm9rRlNCT1N5dFB2XzRMQ1BjNzN0bVdCbU92UWlpdGtFQmlybFFZc0JkakxaY1BkM2xJSU16NC1EVVJQbXBTRU9ZbXNvaUJ1SHhYTWNOR1p6ZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Agricultores de Rio Preto da Eva recebem 6 toneladas de calcário - Amazonas1</t>
+          <t>Mosaic prorroga paralisação de produção de fertilizante SSP - CNN Brasil</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>25/01/2026 05:00</t>
+          <t>21/01/2026 05:00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPUGFSbXJwbzhHMGZTUlM2Q3FIWDlpTExxVUJ2SVB0QlZxQU5laGF1WC1DZ3hpZEt6QnVqX2hvWGZuMC1XZ0dOcHcybkVjaWlyWlBCTkJNREpZX1RpRDZDTV9LRlhIZUV2Ry1pckNHTXM3anVuMU02UHg5QVN6NG4tOWlZU3UxU1VBVV80SEVVMTVsZEcz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUTh0c1hCRzA4emxnNHhfNnYwdTJaWEg3SlRaLW9pNWdFUGY1U2ZDcnZCOTFZRmtveFIzM3RyTmh0Y2k3Y1hubnVLbElqMkItRjJ5N2FzNEcwcGJXTm9DVU9ZN0otV1lQR2dFNDViVGg3QTUxOEtSSnprS1dURDZ1dl9fWlFhNW9Vc2hmRGpxVVI0TDRaMnlGS2VB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | Equinox Gold conclui venda de minas para a CMOC por US$ 1,05 bilhão - Brasil Mineral</t>
+          <t>FERTILIZANTES | Mosaic paralisa produção de SSP no Brasil por mais 30 dias - Brasil Mineral</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>23/01/2026 05:00</t>
+          <t>21/01/2026 05:00</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQcFVPMXJSRE9mcmNsY0U2NnZVb2RWMkxhWm02dmpteHRLYnhKb19nbkFWdURBakVzZmdLVlVuNDVBbi1lcDhPLXdmUGpHTElRaGZFSHBFSldackR4RmxDa00zTXNIdFVranNXQUZZOXZ2S1kyU0xuMGROcXY0ckE0VWpjS2dleXJjQndISnhWYXZvZHd3QVpqUm1Ud1VWUlZ6RV93SnNsVmZITnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcmlUZDBXN0szYV81b3IyR193M0xrNks3X01wdmhSdjRNRi1DNVgyWGxlZThqU1ZjVVM4bEczaHpJMllVX0lTNjNoYXZNREhJUEhhSGhYRWUyS1pSZnZmcmRCS1d5aHNZeWhJcmdYdlQ2eUZobmRkYXlXY29Od25wU1dPSXRCeXVGVlRqY3Q4RWI5N210THNuSWxZRmVTWDBPLVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>CMOC projeta aumento da produção de cobre e mantém liderança no mercado deem cobalto em 2026 - GlobalFert</t>
+          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>23/01/2026 05:00</t>
+          <t>16/01/2026 05:00</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPQTh3b3BBZjB3c3EyS1ZvUnM0TFhJdDMtcnZjQTE0OWNlaWhQRkl1UmgzYXNkdS1aVUw5TnRvY0pzMFE0UkN5YU9lLUFtNGN0SUVES3FKbEdGeEE4YzZnSWNGUUNZY1E0a0lMMEhsU1ZqQmlFQ2dUdmxKRHRmdDhpMzFTUS1sUkJVTzlWY2VzcFEtZncwUDVYUnhid0tzdkV4UUtVZTRMM2dsMzIzTEZLbUkyZEpnWU5CaWVFRTVWbXRBWHVqWHpoV2o5dXo2b0F2UWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
         </is>
       </c>
     </row>
@@ -9752,17 +9752,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Mosaic prorroga paralisação de produção de fertilizante SSP - CNN Brasil</t>
+          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>21/01/2026 05:00</t>
+          <t>16/01/2026 05:00</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQUTh0c1hCRzA4emxnNHhfNnYwdTJaWEg3SlRaLW9pNWdFUGY1U2ZDcnZCOTFZRmtveFIzM3RyTmh0Y2k3Y1hubnVLbElqMkItRjJ5N2FzNEcwcGJXTm9DVU9ZN0otV1lQR2dFNDViVGg3QTUxOEtSSnprS1dURDZ1dl9fWlFhNW9Vc2hmRGpxVVI0TDRaMnlGS2VB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
         </is>
       </c>
     </row>
@@ -9774,17 +9774,17 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic paralisa produção de SSP no Brasil por mais 30 dias - Brasil Mineral</t>
+          <t>Mercado de fertilizantes "se deteriorou ainda mais", diz Mosaic - CNN Brasil</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>21/01/2026 05:00</t>
+          <t>16/01/2026 05:00</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNcmlUZDBXN0szYV81b3IyR193M0xrNks3X01wdmhSdjRNRi1DNVgyWGxlZThqU1ZjVVM4bEczaHpJMllVX0lTNjNoYXZNREhJUEhhSGhYRWUyS1pSZnZmcmRCS1d5aHNZeWhJcmdYdlQ2eUZobmRkYXlXY29Od25wU1dPSXRCeXVGVlRqY3Q4RWI5N210THNuSWxZRmVTWDBPLVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQTWltdUs2NXZIZjFxYTFiT0JySmVBc3p6SDdfOUFBUWpUTG5NNmlBWmc5VG9BOUdrcHBXalZhaWlnb2FFWVB1NFV4S0RjRGQydTZLUWtvVnJHRC13U1gyTnpGRldEM0VlM0VPTWFka2VIVEZzSENTR0NQLW1EV3M4dUFiellNYlkyZTY4N3h3dWdYVk1ZcTRvVVh2QQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Mosaic aponta deterioração do mercado de fertilizantes no Brasil e prevê resultados fracos no trimestre - AgFeed</t>
+          <t>Mosaic promete recuperação, mas retrovisor está embaçado. Ações desabam - The AgriBiz</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -9806,271 +9806,271 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNd2hsY05pajdmUnlUc0QyWi1fMjBfTW1qMU1aT3phMVRVd2tIRm5XcnQxT0t3TXM0MTdDUDNMZjlwNUdzY1hTYmZSdWR2WmdQV0l5cElZV1ZRNlRQdFFZZEhDdGVsYWpoUTNCUnlmdDRweHV5NXNCR25oamcxbGJVLVhrd2hxSU4zb1R0Q0tDbFpWbVpLV0ZMMnVOM1BvaGFQVHczZktiX1hidXVtSGVkZVVoT3NwbkJ5YWlsWEJ3RXpOcml3VWpFY3F4bzF3VHJ1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQS1cyWFhJeGprcGhNdFZOVHBONHM5SGZOQlFZb3ppZlVmZUhkV2p1ZXBWa2tTU3JxdFVtSmZvN2Juc2NwcnB2MUFjU3p5U1gzRlhzc1V2UVRkOThWMXlKZThxTy1ITnJ4b3U5MTFIQlplc09zOXpCVkhnS3lQbXNuMHJJYUVIWENBcWVaT1VlTjF0bUxLTmRhNTk4aUxLRFNrVmZQcXhUTFZSUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Mosaic vê demanda fraca por fertilizantes no 4º trimestre de 2025 - Revista Cultivar</t>
+          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>16/01/2026 05:00</t>
+          <t>14/01/2026 05:00</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOTkZBLUlzVUxoS3BmR1labWFmVF9uR011UEUzdm9hZ0NOWTJ6QkRBaEU2UFpWbWN1WkRtNktfZGNiV1ctY1pUUjM4VkNPUUF2T2t4RmhzTFZqNU9lTFhSRWt3NzVOZFQzRTBzMU5qcHhTUE9XMkZfYVNrNXB2ZGNSN3F2TXlhaU8yZUZlcC1rR0pQVFdqZmtwU182QjFYbWNrY3ZSc3lIYVo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Mercado de fertilizantes "se deteriorou ainda mais", diz Mosaic - CNN Brasil</t>
+          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>16/01/2026 05:00</t>
+          <t>13/01/2026 05:00</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQTWltdUs2NXZIZjFxYTFiT0JySmVBc3p6SDdfOUFBUWpUTG5NNmlBWmc5VG9BOUdrcHBXalZhaWlnb2FFWVB1NFV4S0RjRGQydTZLUWtvVnJHRC13U1gyTnpGRldEM0VlM0VPTWFka2VIVEZzSENTR0NQLW1EV3M4dUFiellNYlkyZTY4N3h3dWdYVk1ZcTRvVVh2QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Mosaic promete recuperação, mas retrovisor está embaçado. Ações desabam - The AgriBiz</t>
+          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>16/01/2026 05:00</t>
+          <t>13/01/2026 05:00</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQS1cyWFhJeGprcGhNdFZOVHBONHM5SGZOQlFZb3ppZlVmZUhkV2p1ZXBWa2tTU3JxdFVtSmZvN2Juc2NwcnB2MUFjU3p5U1gzRlhzc1V2UVRkOThWMXlKZThxTy1ITnJ4b3U5MTFIQlplc09zOXpCVkhnS3lQbXNuMHJJYUVIWENBcWVaT1VlTjF0bUxLTmRhNTk4aUxLRFNrVmZQcXhUTFZSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Como um sabonete de enxofre virou um hit de vendas na Granado - Valor Econômico</t>
+          <t>Sibelco Portugal distinguida a nível nacional e internacional - O Mirante</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>14/01/2026 05:00</t>
+          <t>11/01/2026 05:00</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOd0MzT0JQQ0NDVURyWFJKaHdOUDQ5c0sxbUM5RmxYVVFjZ1R3X00xNndfT2lMNWx4VjJfOEx6OFVTZE82bVJKMm1sdGVEeHBtc3pXM0djSllfOHRod01TRUEzdGdtNGIydDVjX3IzeW03Rlk2LUdrTTlfdF9PYzNxU3BYZW84c09pSHV4ZHNIM2VhOWdCQXVzSjhYejBRVWxYeGY2WktaS3NuR08yVnl6YnczMFROYktWUG02NVh2YTVxcVlWcGt5b3NZV2FHUTFjMlJ6T2lQR3dIZnPSAeoBQVVfeXFMTkMwSmdaUTlwTllwcnNxNDVqc2hPRHB5WDdROVdMWXRWaGs3U3M2cmU4MWNnNHFRd2dYeVM0bDNER0pKaTFRTThOcV9nYmNLTmU4TERRWmRsaVpzcmxvSE5xUmtmMldaODY0d2t1a280SFVmMXdCcUJYOENrUkxCcC0yWGVBeUZlYXVQN2lnWS1HdFdvTFIzdWJ5NTY2Tng0UlQ2M2RVTmlQTVNGV3RLVWRZYWxfNUYzZjNwalFfaFBIT212TmtiR1hpYS1rN3lwb2dWQzRvRHdHODdSd1Jrcms5X2wxMzdhaXB3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPVl8tSExZS016cjFOUVA5NVhOYTlEQk1rZ2xPYldkczhvbHZEUlJScWJJTnhDVkVZeF9tWmZEa2lSbWRfdWRyRHh3aVRzZmlvSE1MRmdVSTRhM2JlakFzWUhFbUQyZnRHbUFPRVZUYS1yTjNnS3RTZFNwWmVkeTlOX0tJZXFOT3F2WFh3OVFCNUNRZ2diSG5BNUtxOE1zOWhpbkJhNXJmdXk3Ykd2aW1J?oc=5</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>FAFENs Bahia e Sergipe entram em operação e reforçam produção nacional de fertilizantes - Agência Petrobras de Notícias</t>
+          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>13/01/2026 05:00</t>
+          <t>07/01/2026 05:00</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQVGg5TXhFc3VydTJjQ0lfakF5VjFPMTFDNU5LSmllZ0xfVUFWR05INHBQdmE0b1RJX2h4QlN5SzdjTzExYzBiWHVZaV9tTWpjZE9SamQ1TXZVM3BPUTBpd3RQTEFOQ0dQcUJiNHFyMDVJZ0tmR2ZlYnd5U2pINnpwS2Z3TEw0S3R3ZkwwbzNFUzNvVkpzeFVQYkNGRWVJYm5pSnNxekpPSzRBMC0zS0RLdUQzYVpoLVlYcFptYWdqZHBKdVU0YkhReWdJb3hSRklSbzhEUEIxZTJwbUthX1JaQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Combinação Potássio e Enxofre maximiza potencial da soja - Agrolink</t>
+          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>13/01/2026 05:00</t>
+          <t>06/01/2026 05:00</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQNnRoQks2V3lYaVduWHRXZTd0OU5NdUIzc0Z3a2toUW1wMm9XdVFueVlKaURfYzJ4LU54eFVxdmUyTWt2ck80NjJGRXVNM3UxSGUyV2FGRld1WjNZSlo4Sm5HNzdtV21seDVHcllQMGQwRjB6dWE4RUZ1RWNjMmZWU0lFNmcxR2NJUHY5cTBmUEQ2RS1yYm9YLW40aFRWa3hUdGd5UDgtWUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Sibelco</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Sibelco Portugal distinguida a nível nacional e internacional - O Mirante</t>
+          <t>Nova gasolina reduzirá emissão de enxofre em 94% - TN Petróleo</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>11/01/2026 05:00</t>
+          <t>01/01/2026 05:00</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPVl8tSExZS016cjFOUVA5NVhOYTlEQk1rZ2xPYldkczhvbHZEUlJScWJJTnhDVkVZeF9tWmZEa2lSbWRfdWRyRHh3aVRzZmlvSE1MRmdVSTRhM2JlakFzWUhFbUQyZnRHbUFPRVZUYS1yTjNnS3RTZFNwWmVkeTlOX0tJZXFOT3F2WFh3OVFCNUNRZ2diSG5BNUtxOE1zOWhpbkJhNXJmdXk3Ykd2aW1J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPdGFtUGpzV2twUkdYcHRPM2hnZGZUZ2RqUVpLeGtUOGlmbGpkcC1mZUZBOVFoODNSVFNHblFZM2p1UWpwTzFOSjdudEx1RndCUTRMM2FaQlJ2eHBIWmRIbW5qel9JcVlxTEp1ckpPRGdEaDJaU3c4MUVDVHZNNEYtMnVyWkJpakFVbEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Funcionários e motoristas são presos por fraude milionária em mineradora de Catalão - Mais Goiás</t>
+          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>07/01/2026 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQN3V5aEtzNFhjMW9fLW82Uk1DZnRJcUhyZXF2V1N1blNveU1uYVlWaUFEdFBUMGZtd3FudHQ3bkFtVURtUDRMZjg0NkN5MVZDeUxYX2pSbDgySHZrMlRjV1NTejA2YlJ0UnMzcTNyWXhQRDlURzhHeUxUamxoWTFOVU8wTkoxalRjZXFNQ25fUGJMejBZbmR6eFk3T1NxUS1sYXJtUHB1WmpaY1BDcFhCU1BjdkRPTW9iUEZoUm1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Ureia</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Polícia Civil desarticula esquema de desvio de cargas na CMOC e prende quatro em Catalão - Badiinho</t>
+          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>06/01/2026 05:00</t>
+          <t>30/12/2025 05:00</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9IbWRiOHpVZnRSVU1fV3hqRWZtZnllckV5Rm0zU0dNc2VTNHE0UW9CQXJmRzB5cGlYbHBVc2FWZnZFci1HNVlvMnNOazhZTDE0bVpaendGc1Rsc1dhUU44aVFmMExIemJTM2NUVnFaTDBMZU9abklrYdIBfkFVX3lxTFA0Tkt0QXVqSFM2Qk4tV1p4MWRsNDllLS12VUhmYjJKWGp6eDI3aXlCMTlSWHRVS1dGRmdoTnJyQlN0VEJxLTRUMnA5Q2JvLS1OWE5mM202b2ZLWUozZ05qV29IUHd0UUx1aE1UcXhUa21kVmQ1d3dfd3BFVWdmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Nova gasolina reduzirá emissão de enxofre em 94% - TN Petróleo</t>
+          <t>Venda de minas de ouro no Brasil por US$ 1 bilhão reacende debate sobre recursos naturais e soberania - MEON</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>01/01/2026 05:00</t>
+          <t>22/12/2025 05:00</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPdGFtUGpzV2twUkdYcHRPM2hnZGZUZ2RqUVpLeGtUOGlmbGpkcC1mZUZBOVFoODNSVFNHblFZM2p1UWpwTzFOSjdudEx1RndCUTRMM2FaQlJ2eHBIWmRIbW5qel9JcVlxTEp1ckpPRGdEaDJaU3c4MUVDVHZNNEYtMnVyWkJpakFVbEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQRnFCa2dQWTktSUZxQW1BRnVBdzhNSkxZUWtlUFVjUWFUTWhMU045UTZWcTJTQ2hneE9wQ1NaU0t4ZFE5MHNVN3dMNWh3NlF1UW1RN0lDVDFfSzZmQlpuMWhfdG1sQ19wWmdweGFaWDNOSHFhTnB3aEo1dXBpRmhTWGF1NE9RaVdSY3ozaTdYbjAyUndhVzZEX3ZJNXJyTlVjazJWRkpVcXVDQQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Ureia</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Retorno da Petrobras à produção de ureia garante disponibilidade e pode reduzir fraudes, diz Argus - Agência eixos</t>
+          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>20/12/2025 05:00</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQY3I3TEVvZW9PeFVuLV9kZHVEVkVVNlRrV1JyOWtaNmsxazA3aDJTd1VxSEw5azR2bFI1X1FHNUVvV09tUGpBd0x6WkF1ZERRQkRVTDQtUGdGODYwR2wxU2trcDBaOUR3YXJuUW5CS3o4Z0MwUjRUQUZZQzRZLUhCeDRYRWw5UTRfYUQySDJHajd2UEF6VmdjQmtCNEFPanhTNmlVdUxZZFo2VG5yVDA1aVh3R0Y4S1FBbGZyYnRhZGNnR3F5LVNr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Trem com enxofre tóxico descarrila nos EUA; autoridades ordenam confinamento temporário - O GLOBO</t>
+          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>30/12/2025 05:00</t>
+          <t>19/12/2025 05:00</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxNMFE1VEdfT3A5OG1pS25pYzl0SktuRmtLRlJVSzczWlVEQXV3TWN5NmpCb2JrZGVnUVRRMWx6ZTBJNmhteVhLMWVHZENCUUkycldMWExiVXY0UldsVWdaNXJaRDMtb09SamFXbEhqT0FJWXJyWXNPVVNkZDA3clh6RXFpclR0Zy1raS1pb1pzTXFFN242LVJFMjVrb1lSbGV1WUhTU0VtYUFmMzJmb2ExZFQ1eXBLNnVvMTBoNFBBcXVhdUFLTmt2bk1sTHZ4Y2txX0NSbGQxX3pJaW5Dcm5ybHN30gHwAUFVX3lxTE8xMV80NEVMcm9zLS1XZ0lVUERHNWczaDQwMVBZOVR2cW5YS3BmUXphdjJPZzJ6amp0dVpjcmo4bG90a1dTb09ncHFiX2ZlS2FCNXN4NktGM0lrQTZyZXhacTFlTjVrQU9kUFNoU2Z0bWhZdVBnaWVuMnRORm16YXNqQzdqX1lLTERqZGdUSk9TUVFrVVZDVnRLY3Z1OXJBaHlRRkt3MTE2R1NMc0VEYkl1S0FKY0xzT0VXWjJEN05XXzFSb3hILWcyamNDUzBuNzJGamQ1WF9PdmdKTi1BQm5KTl9ZNmdaZ3R4cXFzbXZKaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
         </is>
       </c>
     </row>
@@ -10082,17 +10082,17 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Venda de minas de ouro no Brasil por US$ 1 bilhão reacende debate sobre recursos naturais e soberania - MEON</t>
+          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>22/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQRnFCa2dQWTktSUZxQW1BRnVBdzhNSkxZUWtlUFVjUWFUTWhMU045UTZWcTJTQ2hneE9wQ1NaU0t4ZFE5MHNVN3dMNWh3NlF1UW1RN0lDVDFfSzZmQlpuMWhfdG1sQ19wWmdweGFaWDNOSHFhTnB3aEo1dXBpRmhTWGF1NE9RaVdSY3ozaTdYbjAyUndhVzZEX3ZJNXJyTlVjazJWRkpVcXVDQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10104,39 +10104,39 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Mineradora chinesa CMOC adquire operações da Equinox Gold no Brasil por US$ 1 bilhão - Brasília in Foco</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>20/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxOWFdEYV81d254OFd5Y09QdjZqWFpOcHgwSnZ5c0s1Wnh6bGpiUlJIR3EyQXMwQTd0N25iQ1BLeVh5Q0NOQnJ0bUpxVE5wNDAyX0pKZDF0SmFxb0R6WEp0dU9oeklvd3lxdWhjeTFTMHg3SGRnTkJObF9HWmtIQzF1Tl9IS0sxbHVJbGxLYnpQZDhWcmxFWm1Ec2JmbDM3SEtxZmgteXM3NFpvMGhORXYxSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>CSN testa aplicação agrícola de agregado siderúrgico em lavouras de café em Minas Gerais - A Voz da Cidade</t>
+          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>19/12/2025 05:00</t>
+          <t>17/12/2025 05:00</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNUF9QWHBiMF9mc2pNUU1Vb2xxdEJrZmlvdGRiUlJWWXFEY0U4M3p4YWlCT1ZxeEhOY0trQ0RXcXk1NFg4SlJNSjFwQWNneFhjeWV2dkVIMlZZeVVGQ2xqaTFZT0VBdWJRaWxPOURBczU3NUFpNFV4RVJXTXRKLWRELXhoLVVkbE1pNklBVWZwTkJFbGJLVVlKN1hNS2xrU2RZMmxBUHd0Z240SmVCaldtWjEwTmh5QTli?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bilhão - MundoBA</t>
+          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNSGJzTmhzUzhrSmtfRWF0NXFGaEwtNGJNcmVhMWw1QzF6VmdlMDE2X0N5a1NISzFvajZ1blRnOEg1OWVvMWMxVG0tSWd1NWp1WEk2NTRUYTJ4NFBuRWF2ckM3OWFBWjd0VUZDRUFQT1V3Ynk0NGxkRkJ0YUtRbzNjSHBqYUZOSVNyd0JHS1lkblk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
         </is>
       </c>
     </row>
@@ -10170,7 +10170,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
+          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10192,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Chinesa compra minas de ouro no Brasil por US$ 1 bi - BPMoney</t>
+          <t>CMOC entra no ouro no Brasil e compra minas da Equinox por até US$ 1,015 bi - Estado de Minas</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -10202,29 +10202,29 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOdWotX2N4ZW5EMWYwTU5BczVuV0RiVGd2aWJiSFZrS0J3cGdrX2lYUTFyUnc1TmFNTE4wdFE5OW1KZ3h5VkR3amFVQW9oNmtPOTQxZGQ0RWUwMjlTTmlKN2FKZnJBWFdqRGdjWWJPNGQyZmIwUHhCRzlvQ3B0ZEMtTGFzc3FCMk9a?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNYmxtd1NMbXd3d3lRSnhVZF9GLXd3a0JfMHJhel81U1BQTFV0bl9JUTBPMFdCVVNFZFF4TjN4NWEwa254cV9pdFl0M1Y1UGt3VHhrLXBxTy1od29NaTZUc2ZvdkZva3YwVklDdmFxcVdyXzU1Yy0wT2Jkb3B6cTFIdFplZTBNLXpvLVJSSll2cFBoelpUUlFjNDc5WWc1WnI4ZUdjVWlKcWhLOWctM1JtMlA5QXIyWDllY0RScDJOYV8zYzBvdW5rVVNRalg5YldIOGdz0gHYAUFVX3lxTFBCd3RLUWlLUm4wZnlCUFVMdE05RXUzcVNXTXlEYnZIem9wbG5TaWJPVmJjem5kNUtQSFpjWFRfdm1jRHdVMUlhb1p0Z0NHeE9yVnA2SjdaOWtGRjNWVENxbEZQcWtQVFZHUmpadUg4VVZiUlUyOEQ0NDhqaXZZSi1LWGM5TG5OaEhGcExFQkdtQTA5b1AwdDZTbW9SM1ZyZzN3UU1YWUJTUDhTaW5HMlJ6clloeUthcnJ5dDRjUXJITXNSUXR1VzVBdm5XS1VQX0lPQk11eGU4QQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>EMPRESA CHINESA COMPRA MINAS DE OURO NO BRASIL E VAI ASSUMIR A MINERAÇÃO DE OURO NA BAHIA - - Bahia Economica</t>
+          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNZXVMTUFYSkUwMnlmS3lpZlU2VkczaWFyX1JuRy1FSGhFUVkzb2lpU0I2b19LM0VMSHBDelUwbU14Uk5lVVRSVGFhUGxOSGhZbEtyMG40NUZ5dndaelVvZTZiUktxb2taa2M0czRmRllWTWZ0djYzSDMxa1JZR3FCMlN0N2RsNEdBSl9oeTZ5STVENTVzY2ZSdGtIeU1Fb3o0VWFuNksxV3Y1UWE5b3VwWkEwUWZjdHBJS1BVNGJMVmpLbUItWU1ZcFdFYnczM25QZ1lj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10236,51 +10236,51 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>NEGÓCIOS | A incursão chinesa no setor mineral brasileiro e os desafios do capital nacional - Brasil Mineral</t>
+          <t>Gigante chinesa compra quatro minas de ouro no Brasil por 863 milhões de euros - Jornal de Notícias</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNeEczVHluQ0N4cDRucDc3SWpBNzV1SGdHdUJ0RUg1ZFdCQlYzZGlIM0RZaXd6bHJ3b2tUZjgzWll1dGRiOFN3S09kM3Z3aFItTmkyR0YyRkMtRUZyMGFENUxXOGpCbEdURHlPNVM2d0NJendkdXd1aWtpVUZPSVhtMFFxWEJWMlRzQkx5LW4zUEF3ajRUVU1QVEYtSUFxOHdXa0dLeE1yb18yNnlRYzRwNlBNOXBmdk5vd3B3Rmx5VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWh1d1loQjRUc2ZBZXVkMDdUeElMTVRKc1Z4ZnZERlBhTlJ3LUlrb3VTLUY0XzBLTXozcGJ5LVVlR3hjWkFIVm9tcjdScm11RzgxSWNFZVhNREM2SlBDdlI3RGJpaHRmTzBHaDJuZkRwSDlQbmNtbTZ2MHV4U0ZxeHBrTkdaWm85SXdEVVJ4QmdLbW1hMVE2Y2lhMFM5VDZTejBqMXRYWWNLVXdZeTE1bnRWWmxLb2NQZ3fSAa4BQVVfeXFMT25NQ3lFNTRJSGVNVlJQYjJ2LXVqX2dVaXU3Rkx1cE5XcUdoNlZiZ3BhNG13MFM3TnFNWVBrX0xDQUNxbEw4RjdWN3E4SnVITDItNkJSdW1wRFM1a1dFTEd6SkZ4aUNCZkZjT1oyVUFsa1JIN2liVnV0bHQ2QTVDamlZVFRaYk5nVHJlczViampETVRlYy0yeHhKZkJsOVgzZkZ2bFhTWXpfNmVYWFNB?oc=5</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Alta do enxofre pausa produção de fosfato - Agrolink</t>
+          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>17/12/2025 05:00</t>
+          <t>16/12/2025 05:00</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOMlZBcS1qQl9tcHNMLUh2NVk0SjJ5UmF5YUZxS0cwZGRfUXQ5ZExzdzFOWjRjdV90RkEwYjFVcEk1UnFNTGliTUZuT3JuVWN2U2Y3dFlPYS1YbmpXU0ZsMWFSTEJkSjR1M091RkNyX21Ca016ckUwZTBFd2NXTWUxaW93VWZDY0dHekRLdy02VmdianNt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Suspensão de produção em fábricas da Mosaic faz soar mais um alerta no mercado de fertilizantes - AgFeed</t>
+          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNRnpldHB2SFFfMDU2ZWxsNGxxZklNRlFNT0JYd3k2ZGxYSUo2MlNHcnBrY1BVY1lhd0Q1X1BPLU0xeXprVkw0ZFJYb0VkNkRXWEI4aklPX21NcW82Z3NacVp0ZlJfTmRLbTIxeXBXeElhNnRwdjlaX19GdVlqTTgwMERZMEpUNDBWcTBpUTZKN0lxRUYyRE1BbEtObWpBcjZYLTJ2bVA2dXpUdGJ5d2lBTm9FVFlqRWhiaFNjdTJuWmRTemstTVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Gigante chinesa compra quatro minas de ouro no Brasil por 863 milhões de euros - Jornal de Notícias</t>
+          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxPTWh1d1loQjRUc2ZBZXVkMDdUeElMTVRKc1Z4ZnZERlBhTlJ3LUlrb3VTLUY0XzBLTXozcGJ5LVVlR3hjWkFIVm9tcjdScm11RzgxSWNFZVhNREM2SlBDdlI3RGJpaHRmTzBHaDJuZkRwSDlQbmNtbTZ2MHV4U0ZxeHBrTkdaWm85SXdEVVJ4QmdLbW1hMVE2Y2lhMFM5VDZTejBqMXRYWWNLVXdZeTE1bnRWWmxLb2NQZ3fSAa4BQVVfeXFMT25NQ3lFNTRJSGVNVlJQYjJ2LXVqX2dVaXU3Rkx1cE5XcUdoNlZiZ3BhNG13MFM3TnFNWVBrX0xDQUNxbEw4RjdWN3E4SnVITDItNkJSdW1wRFM1a1dFTEd6SkZ4aUNCZkZjT1oyVUFsa1JIN2liVnV0bHQ2QTVDamlZVFRaYk5nVHJlczViampETVRlYy0yeHhKZkJsOVgzZkZ2bFhTWXpfNmVYWFNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra operações da Equinox e produzirá ouro no Brasil - Valor Econômico</t>
+          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNdjJLdXR0TWF1WVRBWGpwZW5vUlAtZk9scmFlMUxKbWxpcUVKZ2ZkNGJqZXhCVENIRVpaRlBPWE9ycnJteDJnbW1WcmZUVjVJOG9DTjF0andnXzMweFV0anRSLXdjVUllZ3JvYUNLU1U3SnFoRWx4Z21OVnFNQ05nWDZaVVRBQnoxMFVSYm5PQ3AyZlVqdmpabzNCY25qZVE0VkI4NGlKVGEzd3RncWNtX0swakhzYjh5WUktLUx2bjdrQkHSAdIBQVVfeXFMTndraVAxVThDT0d6d0xTbVdRa25WdENfanhibkVOamNHaVFMR3VJQWp4b1RiVmFaRXFGQmIwLUZHVTlTdHcxWnZhZERhRWRyRmhBUFlmakVxRHYtZVJNNW5OS1JuZ0xyVXdWVFVSdDU3NmN5MWt4Zmw2R01fR2ZMNG5fVDB0LVNtRENfdlNZS2hmSGg0a2xES1p4aDdzMk1RODRWaHBjVVE0MXNLcWRfMGJuSHZ2SVhZcHcyZnQ5eVN6UXhkd2ZhZGdzeDc0UzRFUkln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10346,61 +10346,61 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas de ouro no Brasil para CMOC, da China, por US$ 1 bilhão - Estadão</t>
+          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxOb1F1OGg3dHNSNEkwNU5vZG44NVpRZThWZG9MVXpkbU5HUFJnSFJsVFhYdndGOTYtRDVaWV9pcTdFUExMLTRqWlhsNXI5OFBPdEJBWE9EZ3NNaDctVUhRaUNpcWhrMWVxM3dOTWdQSTYxODRQTllKMjF2b0s2QzJhWDhERUFTTEFjWnFEdkVKcnVvQmFxNWhlbFF5aF9LY2hWVWlLTFo2aUlMUUttQnRqaWd1WmVhenp2M2fSAb8BQVVfeXFMUHAwZnJHMlZkOXpSbkRRTVlfejYwRExQeVMxZHlxWmRRRGNOOFdrTXFWNkZKLTJ1bXlVV0N6Z0xhMHR6dUVocHF2Z0tLQ3YxVENvR3VacGhpQUlXbDJqRlM1VldCcTdNWHItSDB2cXJhblhBM29zcjdQZlZnOVNCd0RYQmZ5MHhtS0xEY2ZTSjBCS05RTm1kQWl6MWw4QTU2RnhLZm5WTWtFVkg5UFh1OGdZdDNIVWE5ejRCQ3dNeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Mosaic interrompe produção de superfosfato simples no Brasil com alta do enxofre - Globo Rural</t>
+          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxOVENsYjV0WjhZbTEzUy1kOFo0Q1BNOHRXZ1Jwd1lYMWdFVG5jeUpjVDJKNi1FLVJrX1psN3k2enVQQVBzcmxKeW13X3lUS2NNNHpRd2lGdzhHbkpBcmNscC1uSFJzclpqMmRSSW5qdHNRdDF1eEg3M3ppYTFENE1Wb2F0N1hoZ1IzSTdPOW5xM0h3SVFZbVNPVHJrQ09vZFhDaVVUV0tqNXpCZzlFNHhDcXdfZUVjTzlKYkxWa2h0VVNoZVBzWFpibUVyUDBCRjVvektiTHRB0gHkAUFVX3lxTFBQRVRzdEZPSzcwcXJuZTBLZW8zR18zNDMxVi1HeFJEZVFCcElEa1FHNXg3SERqc09CTWRqcW8yeFJvN0ZTQXctRGxYaWE2SHp3S2NaTzJaMllZYTB3TEtXbFJSNUM3Q2NjUFZIMDBVR2g2NEpfR05ZaEFFZDdXOG1VaHpIdklCY0pGczJkS2NqVTdQVlF4N1dmLXgyeGtmSHNCMEx1cVNTN0JkN19zN2hVWWxvdzgtMmppWnUyVFhlYUtBZ1ZIZ21EYjlYcVRib0xJdmJEV1lGZXkyYXBvc3dqRTNNdg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Em meio à disparada do enxofre, Mosaic paralisa produção de superfosfato simples - The AgriBiz</t>
+          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>16/12/2025 05:00</t>
+          <t>15/12/2025 05:00</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQc2RkWEZTUy1Ea283N19QQlhkUWJ1VE9wYUdJMXdVUGlyWXZwLVhkeTQ3SWVOdFdWMl80MElvczhkeHJFYkZ4LWIxSzhIcEItS00zdmpHT04wanN0Ym9PUnI4eXBwb1RiWFF6WVNGSnNNZXlEX3Y5NFJFTVVuRUJkLS1RdkI3VVVSSUNrbWtlQ3EzQlZkMWxxaVQzSVdiUmZwUERrV0F6VUNXeVFXQWxUcXUzTUU2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
+          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
+          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Grupo chinês CMOC fecha compra bilionária de minas de ouro no Brasil - Claudio Dantas</t>
+          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifkFVX3lxTE9ZTnZqV1dXYWtXTm9wUHlLcGVQVDdSdjdmU0lvOEFFakVKSTZLWnBRQ3gxdUpVSkMzOS1SbU5HM1lJOW9yRXFlYXhSUlJPZnNOVWJuY2hBQjFmN2E1VkRnV0pvcG8tX3hIeFZTWTRJR2NBUnk1S0p3Ul92LVFnQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Chinesa CMOC compra minas de ouro no Brasil por US$ 1 bilhão - Valor Econômico</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPeVcwbEF1S3kxa3ZCVFRSNmZ5NVZqQzFZQm9ONGxTdXczMGRVTi15cG85aG9HWWpiU3JJeVdmQnRwTUw2WUpMZmFyU0toSUxMcE8zaEU1TGxDci0xZEFadW55ZDlwem9pVGhtYkFMZEhKWWktNHBaRjdNN3hrSDA1cmdyUFNfaXVpcU8zVVVWcFAzd0ZEbWFsbGo2aWlmN3BmWWdkRXQzVkpmbHVqYmxyVktuN25VcjTSAcYBQVVfeXFMUHVSTm51SjNzbGU5b0dSNDlrd29ReGhNR1ZOZTdjQVo5VDl1dzRKREhlN1FsN1YyZkZiRF9seXdEdGZuQkRrdFFmaFdUVUhSV3pmaEhKUFRMT2E1S0ppV3R0MG5TRVBDTHQyZVRNcTJidHpJOUs4UUt4VFlVTldOWlpaX3dUUnhYT2ZWSjFiOTNCSUsxekFPWFJva2dzd1dHdTlwb0kzX0FFdUhUcm13UTltVDhZYjhsSU1UcWowS2xnZkNLN3RB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - broadcast.com.br</t>
+          <t>CMOC anuncia aquisição de minas de ouro da Equinox Gold no Brasil - China 2 Brazil</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPY21WSmFRbjB2aU1QUUlkbGgtdW5SUUIyeFhabGpTclNfSHdKbmFGQlJueFY5dU43bzY1R0NtVU5ObkhiTU9jRm1kakNPa0dIOWhsekRnV0VlSnpYLUJCaVNHOXduUDI0enpQczROeVViZGQ1X2kzLWpxMnZiXzh5Q1NSNHJnQ2dSOTlacTZXcjVaOVZSS3hXRTFPbzRzeDBsRFFSM2FERVpLVktSWnVZeTBKbU5DQkNoXy1mRw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNTDdIZDRmYlIyRXdYek5lTldDN1JQSWZybnVkdW1WblZTbHlfMU1maDh5b05ha2VreS1CSG5iYkxCWl9RWm1nUHYzZUNmSkdMQ1hidUxBeUUwc0dueEthWXRCbWp0eHB6NTlkcFhNZnBNcHlsMnZOdDFZV0pZY0szZnRiTzBOMlJLbl81bFE5LUk2Z3VHaUJHbjl3?oc=5</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Mineradora Equinox vende duas subsidiárias no Brasil para chinesa CMOC por US$ 1 bilhão - Folha de S.Paulo</t>
+          <t>Equinox Gold vende operações no Brasil para chinesa CMOC por US$ 1,015 bilhão - broadcast.com.br</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZUltWEM0cWVrRldPLVZLNWgwSEQ1NHdVNHdmV2NrT0s3emloMFZ6Z3RMdmxtV2FVdU5QdWV2bzR4TXlzSTA5RUFFOFFJZzdpcXhIaTRqcGQ0OU82cERFVHl5ZU85NnBGZEN0YWtwang0eE9HbWVTbEhtR0o0X2lCNlZDWkFvMTR6SkZ2R0RDYTBQZmRtd1phakQ3OUdzVGZ1UTlRTzFkN1Q1YkNtVHg4UUhEbHBlaXJOTjYzd0syanAtMHdReW1PbHZlcktXV2h5UGJaTdIB2gFBVV95cUxPRk1xdGJXQzNTVlY3VzJYYmZIRXRWeXI3NXpKRzZ0bGdYV3o3T1VLci03MVNLbDVLYVRhT2EyY1F3VncyTER4ZmdpR1NybHVfclAxeUI4V0NUTkx5SUFXZ21wcmR6dGh1S3RxaGwtaDZicXJmMTk5MVRabVFtdGxXSGdPeWdHSjZiYmFtZ3k3cHpyR1RXTmE3azgtdmlESnFKdWVFOHFIcmpPV2dNeXpVSUhhaEVibzg3S3d3VmhqOXNyaHNmdzRoVjcwUUw3WVpIMEIxMHhBVm0xZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPY21WSmFRbjB2aU1QUUlkbGgtdW5SUUIyeFhabGpTclNfSHdKbmFGQlJueFY5dU43bzY1R0NtVU5ObkhiTU9jRm1kakNPa0dIOWhsekRnV0VlSnpYLUJCaVNHOXduUDI0enpQczROeVViZGQ1X2kzLWpxMnZiXzh5Q1NSNHJnQ2dSOTlacTZXcjVaOVZSS3hXRTFPbzRzeDBsRFFSM2FERVpLVktSWnVZeTBKbU5DQkNoXy1mRw?oc=5</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Gigante chinesa CMOC gasta US$ 1 bilhão para abocanhar minas de ouro no Brasil, derruba concorrentes, turbina produção a 8 toneladas por ano e avança pesado no controle de metais preciosos na América do Sul - CPG Click Petróleo e Gás</t>
+          <t>Equinox vende minas de ouro no Brasil por US$ 1 bilhão para focar na América do Norte - Times Brasil | CNBC</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxNWGl1NS0wZzJVbG9BZ2ozUlFlOHNnejMwdXNFNFFnQm5majZCLWFkQ3ROc1JSX0hJaUdBbzhPUFJTalpCYTBKZkNjY25Sa0Y1OW9zcUkzY3ROZW4zYVRnMHJ0THlMYVJRUEt1ajBaMGwySm4xVkNlakw5ZW8yUER0MFBjcnhJazF2ZnNxVFVvamJGcHI1QWpscVAxS0x1M0I4OXYxUFhxaWpZX2RSVDZ4aXFBMXRScmV6cmNqbU5UMFlQRTJfMHBKS1RHWC03LW1IZkhvSFNQUWlpR0QxdzduRHFEZFlvNTJBTzJqUjZ0cmFLenZ1MWE2Yy1FX0NTS1VIcFVNU01QZEc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNR28ySFpHMzJDeW0xM3dXcXktU19yeVBESW1qVXF3dDA0dThMVkZ2WXFiT2J5ak5ZUjdzQW16Q0Z3dE5PZm9MVEkyb3F0MndOSDZTM2RhUFlBX2VTdVozR0ZaTHc2Y3d5M3JWdF9vNjJ6aGJXNko5RThyZjByeWtlSFRNdE1JZFdhVUUzVVBoUQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Equinox Gold vende minas no Brasil à chinesa CMOC por US$ 1 bilhão - Brasil 247</t>
+          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPU1ZKalFzaTc5NjZlSmE4UVY0dzNMMTZUWk9Cd0o5VDFxYVdVZDY1SEVUbVZKLXphOWcydlFQcXk2ZzZMUnhSVUNqSnNzY2s4bkdQcnNmU3FuT0ppTnZ1VmpfS3RZVlNRdzNlVWpMSDdJWENUby1ld2Y1X2lUeThtTFlRcEdNYXcyWi1qZWJUQkhmRHlXYUpMVElFeWlHMUladlA0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10588,17 +10588,17 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Mineração chinesa avança no Brasil com compra bilionária de ativos de ouro da Equinox Gold - Agência Brasil China</t>
+          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxPc2pwVXU4OGJVUHdzb2xLaHhoS21XQVVoN0kyeEF0Qm1LSzE2UnBCYzVUMXBRcGVYWTg2TkMyVXZiRW1zamNtdmF3WFFSMXFNYW1mcmJIUngtS2JIMTNWU3Q0ME9uV2k5aHlHT05DYUpqLWJvM0FIYlhhVm5mUFhtMHNzekNaYkZNLUFpaWVGb3lTdkViVDRWWGxJQWljSE1EM1BKUnpua3Vuc0NMTGtvdGVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
         </is>
       </c>
     </row>
@@ -10610,17 +10610,17 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Empresa chinesa compra minas de ouro no Brasil e amplia presença global - Revista Oeste</t>
+          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>14/12/2025 05:00</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQNzRxZEFqRTNNS3dablR5U2liLVhrbUZOVThwYUhwUGFrdWR1eWcwWHJGckxoWG5JNHY3V3hDZjhaRTRvX2wtaFRkdnJjdFUyZ1BlRjdCV2oxMTA1ZUxlYnlXOHY4ZjFxMGl2ODZDaUM2VWJhcWVjbE4wUWxPLVRxejFzaWduNnlGUFUzOGEzSE9CckhDUFBhTG5xNjJZSGR5OU1UUmtHblAtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
         </is>
       </c>
     </row>
@@ -10632,215 +10632,215 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro brasileiras da Equinox Gold por US$ 1 bilhão - InvestNews - InvestNews</t>
+          <t>CMOC Brasil é reconhecida nacionalmente com o Selo ODS Brasil 2025 - IBRAM - Mineração do Brasil</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>15/12/2025 05:00</t>
+          <t>12/12/2025 05:00</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPS0o5bC02RWVGMFNDRlFMV2huMEcyaGwwdTVPdjRUWEVwSk1RZGJGbWR5NG5aVnRGSzFzQTVJZUsxdHRvMVh1dU9zRTVvYVVmb0dzU2dkZUtuMzRFMXlmc2NEaEo3aFBQdy05RVpmNmd6dmpMQWctTERZNmVvYThyX3VaNTdGWTNZMlpKNk9HbXFXd3N3QzJFM2VfS3NvWklUQ21LbXBNR3NqdUtMcnhSdnhJR3lHVjdS0gG-AUFVX3lxTFBsRW5abk9ZQlFxd2dvV3ZhbFByOVFqNFBQWmROcEFfMGFHaWhrdkgxYmUzbGJPbmtFQXdTMzNINlJsNUNRTm1TZ3FyVXlURDRHT1hpakVxSXZqV3V3OEVEMUpwdFF1a2R3bXdKcEk4Zi1QUFJUcHQtcmQ5SUpOVkVYRVVtT1hMTDQyQmN3SDZfRDQ3c2ZEMGNHYWR3ajRWdDF3YlZNQjRGV2tpM3dORUNHeFNxcm1oOUFia1NQeUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMFRzbEdjWV9haVd4T0hEeGU3b3pvRkJTMjRCbFRnZkRjRzczZ2pWVm1ZcjdOSFBPN2dXR1BBOXF5Z1ZmRk9pUkJCNlZ0ZW1wZ3RDdVVsbGZxRkgwUHJON0c4NkNBUWhjbE91Q1pMLXBDTVJZVGlWWmdlaER6YldSa3FYRGc2LUtXTFdkVEpsZG55U0JHVHhmTGl4bzU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Chinesa CMOC fecha compra de minas de ouro no Brasil por US$ 1 bilhão - O GLOBO</t>
+          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>07/12/2025 19:00</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQWGs3cTNKQ1ZUQkw2M1FhQUtBRWVXRENXQlcxTlZZWVQxR3JwakE3VHhLSk85VHJZNW9FRlNZdTJxYWJod1JpZHNzQU5FZmQ4NTBlSHRzYWR2cGdmNUJBbjBfc2g4Z0xCeDhZS2lQUDNkZVM2YlNKUmRsaGRSUXlzaFhVc1VCUjdqdGJ4MVczTDdiXzBJdGY0MGxuRFNPanpMVkNmWllPd1Fubk9Fb3VVVUlQYmtHa05ZZGEzT3hMZFdhZU9YUVHSAdQBQVVfeXFMTnhIOF9JRDZ2d1VLU3lpT050cHpXdkNxTjIxUGJHNFlTbk9zLTRHeWZ2dWZLOVRXNVI4YVNPMVNOelZURVdSMTl5RVRfTU1GdTlZRkl0Y2hsQ1Bzd21yZzRPZ0RtMlZlNlhuRE1TbkdDczVIRTRpdWpfYzh1ZlloTVItWnJXVzN4TnBibDFweERzVDh0anhkajlTT0wyUkRxSWJUckhpSHlpTjY3ejNFRTlEcm4yWWZFM1FxQXRmQkJpVVN2T1JoZXl0WXVwRjlFM0d4QXM?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a6263720c134cf998936ed89d546006&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>OURO | Equinox Gold vende operações brasileiras para CMOC por US$ 1,015 bilhão - Brasil Mineral</t>
+          <t>FERTILIZANTES | Mosaic investe R$ 350 mil em projetos de inovação para melhoria operacional - Brasil Mineral</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>14/12/2025 05:00</t>
+          <t>02/12/2025 05:00</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPRVJxVWY5aVdLMG85emtjZ04xVG10c3JUSkdSVjdhQko5UUU4S2gtRXdzang5ckZmOHFoYUlqR2huemllR0lOMUQxYVFDWjAwbkIxSUx2ZjhFa1dQbTkyVGh0MlZlb3BWbWMwN2p3TEplUzM4UEpTQWxFckJsMVU0ckJmZXAwbEh6Vm9WbjRyNWhRZGdMRHJBT3ROZ1ZvcWFJYUVGMEVpekZQck9idWlmRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNenNPSXRyeVo2djFmWk9EQlFuWTdfZkdwb3EzUHdreWpqM3E1dk9meG9SYXZncnptdDBTV0xHUnpVSGVlXzZETUc1eEFWNWlEZnRTd0pkMEtaVm9GQkRtUXd6WEYwcmthZDZtQ2h3ckx3TGNLRFJVOFBPZXpHWXlESzdqbVdwTGg0X3JwWkRfOTlBVERmSTM2VkdMUkwwMDdTandqbTVlSFB3Z0MtZUVacmpoQmlhUHc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>CMOC Brasil é reconhecida nacionalmente com o Selo ODS Brasil 2025 - IBRAM - Mineração do Brasil</t>
+          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>12/12/2025 05:00</t>
+          <t>02/12/2025 05:00</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQMFRzbEdjWV9haVd4T0hEeGU3b3pvRkJTMjRCbFRnZkRjRzczZ2pWVm1ZcjdOSFBPN2dXR1BBOXF5Z1ZmRk9pUkJCNlZ0ZW1wZ3RDdVVsbGZxRkgwUHJON0c4NkNBUWhjbE91Q1pMLXBDTVJZVGlWWmdlaER6YldSa3FYRGc2LUtXTFdkVEpsZG55U0JHVHhmTGl4bzU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Maximize Soybean Yield by Applying Lime for Soil</t>
+          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>07/12/2025 19:00</t>
+          <t>01/12/2025 05:00</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e2471054300949a6a1e2db1d4be&amp;url=https%3a%2f%2fwww.agweb.com%2fnews%2fcrops%2flime-soybean-yield&amp;c=11130810557354802507&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>FERTILIZANTES | Mosaic investe R$ 350 mil em projetos de inovação para melhoria operacional - Brasil Mineral</t>
+          <t>ANM autoriza MBF Fertilizantes a extrair calcário no litoral do Piauí - Agência iNFRA</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>02/12/2025 05:00</t>
+          <t>27/11/2025 05:00</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNenNPSXRyeVo2djFmWk9EQlFuWTdfZkdwb3EzUHdreWpqM3E1dk9meG9SYXZncnptdDBTV0xHUnpVSGVlXzZETUc1eEFWNWlEZnRTd0pkMEtaVm9GQkRtUXd6WEYwcmthZDZtQ2h3ckx3TGNLRFJVOFBPZXpHWXlESzdqbVdwTGg0X3JwWkRfOTlBVERmSTM2VkdMUkwwMDdTandqbTVlSFB3Z0MtZUVacmpoQmlhUHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPLV9uSnA0c3dNdUtMaTNUbGU2YThONXZtdFk5cTVMZHFuSDlrYml2dHV4ZmZLcllzQnd6d0hpRzYzdVFVMEJWX2ttQ2EtME9ic0lPZnREcDJJRExzMEpicUluUEIzdzR5NHZYZHlCVU1meFdweFh2RjBRb3J1dkttenFNNHl0Y01hR1dEZUJTTDVUX1NfajMtN2VwN3B1d00?oc=5</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Viter, da Votorantim, dá novo passo em seu plano para o agro de MT - Globo Rural</t>
+          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>02/12/2025 05:00</t>
+          <t>26/11/2025 03:44</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQMDlja0FtOTBHX1ZRTUdWS3owOWVranBrZU53WGZIZVp6QnAzdWxpZC1qRGtSTEhRdldUbFNxd1QwX3F4cEhqZy1Kb21jcGRoT2YyaUY2alprTGFHOFlLRlc4WHo3cmtLWWhtUzhkYmFCaHE1dmpIMnlaVDAwa0IzZzk4QzFxQkJqdlpScnd4V1VZbl9RWmhmdWt1RV8xZkdWNlF5UG96R2lNTV9ocmVBN3VsSWUzNlBSdzhOYTBPc0fSAc8BQVVfeXFMTzF5NVFKcUZmWGZiY2FzdGl6U19DR082dHFlcHAzc3A5bktBT0ZpU2lnZVdjQ3VLcklVd3Qwc1A5WldEUmRNQ29zT1JySklwNWlNdG5tWTdJeXJSVFd3U2t1MHNmV1dITkdOamNtSkZ2bW5fZnFMNmFMWGwwU3BvLWNKX2dadVAyclNIQXVBX0VNakdmdzhlM1dwQmFMMnVtVURjbE9NVUYyMWdabnpUc0JHX3N4S19zb1labHF5Sm50UlpTV2RTSEtNdnJ2Q053?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Escalada global do enxofre pressiona mercado - Agrolink</t>
+          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>01/12/2025 05:00</t>
+          <t>24/11/2025 05:00</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObXVxLVFyVkN1SnNXVXZMa3hWU2VjVkNuZXRuWTZ4QTJ3bjl5ZTdEb1FFaXV1RC1aWjdBcVZWR09LNm9pWS1LdUdHbTZ2bThXc2l1WVV5eDYyQ081cXZEOW14UVh3T2RFTWFtTi1yUWstM0RMS2JiLTVLLWx2dFl5R2xFbEdUMnRxNVZVVm5sUGpCNU1WTnA3OQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>ANM autoriza MBF Fertilizantes a extrair calcário no litoral do Piauí - Agência iNFRA</t>
+          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>27/11/2025 05:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxPLV9uSnA0c3dNdUtMaTNUbGU2YThONXZtdFk5cTVMZHFuSDlrYml2dHV4ZmZLcllzQnd6d0hpRzYzdVFVMEJWX2ttQ2EtME9ic0lPZnREcDJJRExzMEpicUluUEIzdzR5NHZYZHlCVU1meFdweFh2RjBRb3J1dkttenFNNHl0Y01hR1dEZUJTTDVUX1NfajMtN2VwN3B1d00?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>Ical</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Lhoist e TotalEnergies inauguram central solar na Lusical em Alcanede - Mais Ribatejo</t>
+          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>26/11/2025 03:44</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQZ2hKV0x5cnRyTG9HYU5mS2ZKT0ZoZFV3bFczcDdvcHgyNkh2RGFFOEhLUm00V21uU1ExRG83MEtycU5vZ0Q1dzBpem5GRllxQzdodEIxam9FSFVOWEVIS3hjdXc2ejc3V3AzSkFTam1BMTJPQ25YU0ZPWjljM1RmcjVvYlhvTGZXRlVUdnFOYTh1MDVyNFFUNk9R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
         </is>
       </c>
     </row>
@@ -10852,39 +10852,39 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Fertilizante e corretivo de solo sustentável, AgroSilício entra na conta dos CBios da produção de cana - AgFeed</t>
+          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>24/11/2025 05:00</t>
+          <t>19/11/2025 05:00</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU3V5TmVZdTBGR2VEQVNkQmhZbXVuMC14VGN4NHdTWDBfYzZoT3RqU25YbGFMeEpocm9xZzVZQmE4T0p1dm13Wl8zYnZjcHhYdkJSOTlsOFNEMXluck41X09vdEQ4U0VmMEJibU1ObWJUalBLcGxUOWE1VHBkNjk3cXBfSUk0dE1YNFduUFUxQ2VfYUFyeFJUMGZYR01kNHg5N19sbjI5M0dJcXhVWTc1U3Jfd3ZfNGFvMGtkLVNZRmw4ZjZ5SFRzWXJyRmZhdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Ical</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Idoso morre e mulheres passam mal após suspeita de envenenamento em Alagoas - CNN Brasil</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café - Diário do Vale</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>18/11/2025 05:00</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxObS0yQjlSb05Xc01WWnJ0S0VoSUpyWWJzaWYtbkRFRlVPT05EX2x3NWtmZFU3TmhzMVM2ZzN5cW0tQnFuUDRjdTBrUEZ1dTJPT0huRHFqQmVoVUM3Z0V2dUJwSC14UVF6QTBkVlEwYmotdG5yWjJ1STBNeXBlclF4WjJ6TzRfYmVOblN5M0hSTjQyTkdQaXpuNEQwVVZIQXVkZFlSNDQzbGU2WjVzTFltSmFWQ0VtdkVWWVZNV2EzUHJuMzla?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNczJVdG5xdk5mQU0xak4xa3cyeExRaXN4czlqVGZOZ3NVWjlDWG15OTRzSHItcXprUE5mbmZaSWhSRERxWnI1MTA0YzE5UHlIeF9jQ2VYWDF6UFZEbHJfLUFVbU1vc2NuX3dwSDd5VExoQVVobW9GWmNEWVl0N21fZmpkTEg3UFZTNmdrY0VBM0R5WTdZWkU1dDFaTDNwZXQwNDlnR1c4WGxGaDNDRDZzWXlB?oc=5</t>
         </is>
       </c>
     </row>
@@ -10896,303 +10896,303 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>MAPA libera uso agrícola de agregado siderúrgico da CSN - Diário do Vale</t>
+          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>17/11/2025 13:00</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOMjFZNmJuVXBKRDlQMGhCQ1FMVzZnZHAtb1NhMEV0UWtua054NzVjc3hVa01uai15WUFCbnl1VXdheDZGam04QVRVU0ZMOGREdjhWMHRCM21PcjlrTmU2OUdJdlA5bHZidVlvSHRKM2s5Rm1JNVp4cnNwLVVGakRBVVhBX0xJYUFWbmFBZTVRdWRxVWxQb1I5Ng?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a62637111bb4415a383110696fcab4c&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>MAPA libera agregado siderúrgico da CSN para uso agrícola em todo o país - A Voz da Cidade</t>
+          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>19/11/2025 05:00</t>
+          <t>17/11/2025 05:00</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQdkNtbm82QkJhN0V3TjhhSUktbHlkU3NCTS1LdzVHWEtXVTF5UXdDWEZXanh3M0o3S2F3RXhwdmZWbE1EaUx4bENjU2cwTnFSdE5NUUZ4ZWlEVmV2SWtkOU8wQi1UUE00aWoxWC0zamtLbzU1TTUxZDdKTWdNenhaRjMyZTduNUpLR0tTRGZqOFFzYmRDYlZXdS11bGZSTnRyTUw0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café - Diário do Vale</t>
+          <t>Mosaic Entra no Mercado de Fertirrigação, um Setor de 4 Milhões de Toneladas até 2030 - Forbes Brasil</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>18/11/2025 05:00</t>
+          <t>17/11/2025 05:00</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNczJVdG5xdk5mQU0xak4xa3cyeExRaXN4czlqVGZOZ3NVWjlDWG15OTRzSHItcXprUE5mbmZaSWhSRERxWnI1MTA0YzE5UHlIeF9jQ2VYWDF6UFZEbHJfLUFVbU1vc2NuX3dwSDd5VExoQVVobW9GWmNEWVl0N21fZmpkTEg3UFZTNmdrY0VBM0R5WTdZWkU1dDFaTDNwZXQwNDlnR1c4WGxGaDNDRDZzWXlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ1Z6amZ6SDBLNHYtOGtuMnZ5VnRCQ2lrYjNIQS1WcmdMZE9wZG9TRk80R3ZjWGc1dzE2RTF1LV9EOEdWXzk2LXhMY20yZlFZY2tLREZabFhnTUZhb2x3eEstZVYtcnlyMUdjZFVjTUFHdlF6bW5iMkozY29hUFl0bG5aXzRVbVZrTjB1d3QxR1hMeXBxUVpaeDNGQ0swREQtVFVaT2ZndTRQd2xUT2FRWnA0UEY0TWYzQVBYNjh0QlpoTV84OEE?oc=5</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>CSN e prefeituras testarão resíduos como corretivo de solo no Vale do Café</t>
+          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>17/11/2025 13:00</t>
+          <t>11/11/2025 05:00</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e233b734cabaee823cb4f045c9e&amp;url=https%3a%2f%2fdiariodovale.com.br%2feconomia%2fcsn-e-prefeituras-testarao-residuos-como-corretivo-de-solo-no-vale-do-cafe%2f&amp;c=17301919194020704168&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna intensifica o fortalecimento da agricultura familiar com nova remessa de calcário para associações rurais - Prefeitura de Itabuna</t>
+          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura de Itararé</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>17/11/2025 05:00</t>
+          <t>10/11/2025 05:00</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQS3hSaWdZcnZzaWJaelBFbnN0aUExa2xWQUhUa2xFMFJPYWI1QXFBR3VTOFVqRm1BS1VjQkxmYmo4OVd4R0JXWno0dDBrYjYtWXhFVzI3LXhYeXh0Z0xsbUxvWmp6MG9xSGVaMktwUFpUbkZyMkpRcEY0anI5eUdaTUlhblJlMUpsbnl0dmx0OXJrZTk1MDVMNGJscDc5T2hINk9ZQUd6c0dXNVpSNGZMc2hGTU40X3VlaUdtMmJvaGlXM1oxdnpLSld2d1hMZGlHaUdOTFljOW1mdmJmVDlYWk9BUFFDaFYyR2hPSUNkRThWZl96SHdaNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYjRIbkk4bkExM1lhOUtmWVl5UXhXOU5rbkxhdnNEVUpZcGpoNE9xbGRRQy1JWVNrcWF0d3c1eEtJUDVENjJGVU15aEZjdnptLWM1VXlXdmVTUTJUX1NqVEJNU1IyTHRMYW4ybzdZMlBQUkFyNFRCVjFUZG0zM1VMVE9GRHFDZ3BnVzR0Y0tRLS13VHp4TVNRQ3NnMHVrcGhWU2ZVNHhLMXktaVJ5OWhxOGwwS1oydXhfYWZvcw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Mosaic</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Mosaic Entra no Mercado de Fertirrigação, um Setor de 4 Milhões de Toneladas até 2030 - Forbes Brasil</t>
+          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>17/11/2025 05:00</t>
+          <t>08/11/2025 05:00</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNZ1Z6amZ6SDBLNHYtOGtuMnZ5VnRCQ2lrYjNIQS1WcmdMZE9wZG9TRk80R3ZjWGc1dzE2RTF1LV9EOEdWXzk2LXhMY20yZlFZY2tLREZabFhnTUZhb2x3eEstZVYtcnlyMUdjZFVjTUFHdlF6bW5iMkozY29hUFl0bG5aXzRVbVZrTjB1d3QxR1hMeXBxUVpaeDNGQ0swREQtVFVaT2ZndTRQd2xUT2FRWnA0UEY0TWYzQVBYNjh0QlpoTV84OEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Alta do enxofre supera 130% em 2025 - Agrolink</t>
+          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>11/11/2025 05:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOalZhb0h6TTl5Nkx4dlY5d3NZc0tXS0c1anVfX3B5WXMxa1NTS1lXNmlwRmhvdlFiMDhtYmszbS13cl9UeUlOeW9xQVAzd05BM3ZudnRYZUt5LUkwSmdJbVVpaEg2NFZMdmJtVHQ1Z1pCenBjSmhFaV8yN3FWR1VIeHExS21UZzQyT21YcA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Prefeitura de Itararé (SP) investe em distribuição de calcário para fortalecer a produção rural - Prefeitura de Itararé</t>
+          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>10/11/2025 05:00</t>
+          <t>30/10/2025 04:00</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYjRIbkk4bkExM1lhOUtmWVl5UXhXOU5rbkxhdnNEVUpZcGpoNE9xbGRRQy1JWVNrcWF0d3c1eEtJUDVENjJGVU15aEZjdnptLWM1VXlXdmVTUTJUX1NqVEJNU1IyTHRMYW4ybzdZMlBQUkFyNFRCVjFUZG0zM1VMVE9GRHFDZ3BnVzR0Y0tRLS13VHp4TVNRQ3NnMHVrcGhWU2ZVNHhLMXktaVJ5OWhxOGwwS1oydXhfYWZvcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Autoridades acompanham recebimento de nova remessa de calcário para fortalecer agricultura familiar - Prefeitura de Itabuna</t>
+          <t>Alta explosiva: preço do enxofre dispara 115% e ameaça elevar custos da agricultura - CompreRural</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>08/11/2025 05:00</t>
+          <t>29/10/2025 04:00</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNdlJVcUg5WXdKaDVrNmtoTWtpNlhxWi1oMFEwTjduTHU2d2E0cHVkaEV3M05Cd0pocDVDY2Z4aEZNWEhMY2I0WjhZNGxYQTNQaVUxaDFZaWpCckdSdkM5T0xjdWxnaVpabGY3OEV0c0xxN1R5anROVmFUS0ZaYW1meHp5cXNocTBCUl9aUDU5Vi1qTDR0dGotYVlkZG5FcXNOdTZIMnQxRzQ4TkJvY0RuVVRfOW9qbUIzaFZ3U0I5cVdTSFdxOVBpeDlIWWphd2hVQjdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOaVRLcmRCTmtsX0FhdlRBTDJXVXpacVE1a1pOdi1yTlBPSlg1TndpelpzMjBIeTFseEd5MjU2ZWdCRVNNVUZleWtDRjVaUnZxRVUzZkN2bjhaZENsSU1ZSktHNlMzaDF0YTNOY0VmdnYyUllnWFVJVWJSaUVFVmQ0VnRZUFRDQ2thRVFLaEhpcXNlWWp4ZGF2WWJNbTI3d0xpQjFUdE5KTEw5a09XN2Rv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Empresa mineira cria primeiro e-commerce para o setor de mineração - Diário do Comércio</t>
+          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>27/10/2025 04:00</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxOYjhzVnJadjNlOHRJMXVuLVlrd25FQWUzWGduc1FPRXFsbE91a2NoOHFCdWg2cjg5eDlCaUZOWTZqOXY4VnpwdTFrb05ReXBlTzlXUE9qSzB6M2FpNTZER3FMLTFZcUJabzQ0VnY2QXRzSHlfMXdRei14MEdJTFpvTXU1NUhpdm9aT3BlS3BqV3Y4U2pnQnQwVQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Trabalhadores da mineração podem parar: Metabase contesta proposta da CMOC em Catalão - Badiinho</t>
+          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>30/10/2025 04:00</t>
+          <t>22/10/2025 10:56</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxNOTg0UGo4RnZPRGE0RUY3TTcyamY2cEZROVhGT3dTNjZpdjRKX0poYXhWR01YOURsT1FoU0lQRU5WNW0zdGtndG5sUUM5YlhqOFNmTER6eF9OLWtOT0ZrMmdLR0ZzeHpVRGE0T0FfMjdPeVJydk5yNEEwem9xMlVNbjRwUWltd9IBiwFBVV95cUxNN2lrTE5FN3BabGE3UzhMOG1qRWRsUWFsVE5CUXZCeWQ0VkVpa0pONUVqdzJBNTdTdW1tY1VreHI1TnM1bDE5UDZIbWtKWjlHemdHOVR6UU13VFJvS0xtXzVHdEplaHgxQ0txcnNncW1TMTM0ZzVDakpPQ3FTMEVhM3ZJWFhrZXR1UWFn?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a6263720c134cf998936ed89d546006&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Sibelco</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Alta explosiva: preço do enxofre dispara 115% e ameaça elevar custos da agricultura - CompreRural</t>
+          <t>Sibelco prioriza ambiente e sustentabilidade - O Mirante</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>29/10/2025 04:00</t>
+          <t>14/10/2025 04:00</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOaVRLcmRCTmtsX0FhdlRBTDJXVXpacVE1a1pOdi1yTlBPSlg1TndpelpzMjBIeTFseEd5MjU2ZWdCRVNNVUZleWtDRjVaUnZxRVUzZkN2bjhaZENsSU1ZSktHNlMzaDF0YTNOY0VmdnYyUllnWFVJVWJSaUVFVmQ0VnRZUFRDQ2thRVFLaEhpcXNlWWp4ZGF2WWJNbTI3d0xpQjFUdE5KTEw5a09XN2Rv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPcTZuY1FkWnluSllYNDRFMDcyeUtDeHlFeGNSQ0FaV20tcnNreHpHT1NVRUR0ZUd0a0hUOEw0M0EtS3lnd3lTalJrbWI0Q2ZpeUZIWlc0N1VwQ3NrMHhnR1NQV2FEdkp5RVBraXdSMzdoUEpTcEwwVmljdVBRcTF2RzY5azRkQTVhTnZKRDNrQlY5cjlocDlhSWNQQkY?oc=5</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Enxofre dispara 115% em 2025 e preocupa setor de fertilizantes - Revista Cultivar</t>
+          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>27/10/2025 04:00</t>
+          <t>14/10/2025 04:00</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQSFlkU21VODVuMXFLakZsaktmNlRORjVPd0pET2F1bE5FWEJaNWkxUEhNcDVNUVRXaEJlODI3ZG05RTBLZ21rWTE4dk9zOW82NVBFZjltNzlWNTZEb2IteDRNa2dCZkpDNlQxeUJPWW42UjR5SkJDckhXbnFRRHYxTUk2SGlfQl8xY3BJUW1qREM3WFMtSzN3THRqMl9KYThhX2lv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>Enxofre</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Agricultural lime spills on Mattis; drivers encouraged to wash it off ASAP</t>
+          <t>De 100 mil a 1,2 milhão: UGC faz sabonete de enxofre da Granado multiplicar as vendas - Mundo do Marketing</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>22/10/2025 10:56</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e2471054300949a6a1e2db1d4be&amp;url=https%3a%2f%2fwww.yahoo.com%2fnews%2farticles%2fagricultural-lime-spills-mattis-drivers-205639042.html&amp;c=8051146937692834356&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTWprTW9RT3lxQkVOTjZ3QzVvX2R0RHhCZUxFeE1BNGtMY3VKc1Z4NWViSEYyLXdFQnRkWlYwTEZSOHg4UHpQLTJ3RDEySk9Ld2xkaGp4WnVLQWUtcFdrVzcyQ01pUGxfS2lwbzNERGp3WVdYYmdTd2h6SUxVdEhnUHdDRG5Hb2lRZjlBNUQ5QU1MYnlDV3kyRHpFR3lRcXNMa2xDMTR6Y2ZSaE1JczI2RkpENGU1VE0?oc=5</t>
         </is>
       </c>
     </row>
@@ -11204,149 +11204,149 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Corredor hidroviário opera em Roraima com potencial para movimentar soja, calcário e fertilizantes - GlobalFert</t>
+          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>14/10/2025 04:00</t>
+          <t>13/10/2025 04:00</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxPWS13UUhhekp2enROZ3Z3SEpNWFd1REZvME9tS0EwT1Z0Y2ZxSHZOTE1oRWNKQ3lGZUV4TW5Gd2ZtT0lpZ1o2YWZXbWh3cjZNSlpaMHZfaF9vZUREMTJObk56TUlSRERYWk5Vd1BWZTJtOXBEMzJlVDZqRnc5M0xMTndCOU56SDZrOFF1dDJUeEFmRzlBdG1fc0pXVEJWTmJaODliQjJnWkdHVGVWak9hY3BtWllxa3lCTFl5SXZNYTRfakNBU1RneXhjR2RxWkxVU0RHZm9oLWp1RXdLZkl3WnVjdExGcjZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Sibelco</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Sibelco prioriza ambiente e sustentabilidade - O Mirante</t>
+          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>14/10/2025 04:00</t>
+          <t>10/10/2025 04:00</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPcTZuY1FkWnluSllYNDRFMDcyeUtDeHlFeGNSQ0FaV20tcnNreHpHT1NVRUR0ZUd0a0hUOEw0M0EtS3lnd3lTalJrbWI0Q2ZpeUZIWlc0N1VwQ3NrMHhnR1NQV2FEdkp5RVBraXdSMzdoUEpTcEwwVmljdVBRcTF2RzY5azRkQTVhTnZKRDNrQlY5cjlocDlhSWNQQkY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Prefeitura de Itabuna recebe 25 toneladas de calcário para fortalecer a produção rural - Prefeitura de Itabuna</t>
+          <t>Calcário: o insumo que transformou o Cerrado em uma das maiores potências agrícolas do país</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>09/10/2025 23:34</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPM0Ztc21zYlQ0UThHanYxVnMtV3F4VElqcUtOLWt5S1FhYy1IUU9FdURWenZ0RkIzNGVFMVhRRGdHc25IZDFSNDU1NFc4N0c3NmtQMDVHVjcyREpWWWtFNlY5U0k2OE9waFRZWFkxTEIxYkoyd3lkd2ZyRTBRcVg1cEs3WEtTSHgzRkQ5N01ocTVNWjhhQmxBcUpXbEFJRTBiZHIxSzczZGRwNm5NWldZTmdIY0hsUTA4RE1qOXNMdkZLdw?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a62636f6cd94bc8bdca994297ea964e&amp;url=https%3a%2f%2fopopular.com.br%2finfomercial%2fcalcario-o-insumo-que-transformou-o-cerrado-em-uma-das-maiores-potencias-agricolas-do-pais-1.3322503&amp;c=8695352406975221608&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Enxofre</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>De 100 mil a 1,2 milhão: UGC faz sabonete de enxofre da Granado multiplicar as vendas - Mundo do Marketing</t>
+          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>13/10/2025 04:00</t>
+          <t>09/10/2025 04:00</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQTWprTW9RT3lxQkVOTjZ3QzVvX2R0RHhCZUxFeE1BNGtMY3VKc1Z4NWViSEYyLXdFQnRkWlYwTEZSOHg4UHpQLTJ3RDEySk9Ld2xkaGp4WnVLQWUtcFdrVzcyQ01pUGxfS2lwbzNERGp3WVdYYmdTd2h6SUxVdEhnUHdDRG5Hb2lRZjlBNUQ5QU1MYnlDV3kyRHpFR3lRcXNMa2xDMTR6Y2ZSaE1JczI2RkpENGU1VE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Notícias - Caçapava do Sul - Enacal 2025: O Futuro do Calcário e da Produtividade Agrícola Nacional em debate - PORTAL FARRAPO</t>
+          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>10/10/2025 04:00</t>
+          <t>02/10/2025 04:00</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxPX0g1MjlaM01tc2JuWk5KX2dHeG41elVsX3laa0FBemVkVC01eGJzZlhaY0xndEFXNHcxVjNNdmR5YmZiRGotcERXWXVHaFBnWmZYdFk0cmhqNXV3TnMzV0had0NKbE5DTlJ4cDh5dWdSTFZhM1kyU2M3SVVJdXRoeDdsTGxHZTF1RHI5RnFiVmNuMXhpcm42T2xkTUgyVG5IbW5RTGRxRHdUb3RGemtkemhlOTZoaWplTnhoTU12ZGZ5aExmZ0EyVTMwOHJMN25veGgxbFYzaEtjU0FfOU9Wam5B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>Lhoist</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Calcário: o insumo que transformou o Cerrado em uma das maiores potências agrícolas do país</t>
+          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>09/10/2025 23:34</t>
+          <t>01/10/2025 04:00</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e21ecd84de49accbae724bcd093&amp;url=https%3a%2f%2fopopular.com.br%2finfomercial%2fcalcario-o-insumo-que-transformou-o-cerrado-em-uma-das-maiores-potencias-agricolas-do-pais-1.3322503&amp;c=8695352406975221608&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Carmeuse Brasil inaugura nova planta em Taquaritinga e fortalece presença no setor - JornalCana</t>
+          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>09/10/2025 04:00</t>
+          <t>21/09/2025 04:00</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOOTlxVkNXc2dQdlFScWo4WTJRb2wwd0tGVDUzcGVKakwycEJTWWlGRGo2S1JfNEJUZkF5TjB0LVRqNFc3a3lweTZvZ1dkVkxvanQxU0FOdEtjSC1NRVMzUTN6TFBVMmloa1JRdXdMc1ZmSU83YXNHeXNMQUhQUDd5RFAyWDltYlJKa1ZBSHhnVUNpSDBlZFpRamRaN2RXU0tITjBQa0hORk1zU0RNTl9pQ21pRDA0YVEwbWI0V3k1ZlRFYUZWZWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
         </is>
       </c>
     </row>
@@ -11358,83 +11358,83 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Aplicar calcário na cobertura da pastagem funciona mesmo? - Portal DBO</t>
+          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>02/10/2025 04:00</t>
+          <t>20/09/2025 04:00</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxOOUUtMGV2R2N5MEo2X3BWR3J2REloQS1Vb0oxVUNWazU1c2FUWHBTWnJoS2E5ODZoaW5JT1lNSlFDT0NIQkVqSFI0RTNQai1vQWhlR0JFcWdXTGJFSkNVa2RjOXBRaEVwYjBzNmc4R0R6YlNEbURKbGt2SEZRU0V6ZktaWEhzTWpla1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Lhoist</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Lhoist abre inscrições para nova edição do Programa Jovem Aprendiz com 40 vagas para mulheres - Portal Arcos</t>
+          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>01/10/2025 04:00</t>
+          <t>15/09/2025 04:00</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxNSGxOMXVsOFpvTE9mS0Y5ZW1JdFcwRWRvdHE4NmNBZzFBWWdLSmxzOE4wY0RGdXNTMk8wNDJ5RHRXSVhobXhYaVJaMU9LU0tFZ29KRXZPYWhEenc1ckRKVlUtamphUnoyVnlIZTF4VVBJTkFvVkNDcGFYWmhUUnR1RWhlYy1rN3BBcXZNdTMzU2pfRzhReFR5d3VoWV9CZHh6aUtPTjdnaTRjMmQxZ3ZWWER0bC12UHRfRnR4bk5rRl8wNjc5UDBaLTNZb3RTX19ZMTdPbg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Congo vai retomar a exportação de cobalto, depois de ter forçado uma alta de 60% - InvestNews - InvestNews</t>
+          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>21/09/2025 04:00</t>
+          <t>07/09/2025 14:00</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNckRwbnFjSEdfS3dIN0t4S21CdkE1U1lZUWpLVE9Ubjh4MTltOFRtbS1hTi03YXVqczV3QWVnOEptUzRoXzYwb1drZy1RMzlEa2tOY19mN1JsUG8wWFlWeGpCbS1iMnFFUFByR095ZUpEbWVqOXcyTTVJV050R0g4QXlxQ0hzdXNoMUNLdHNwM3FHVjFORUxiakREZ2R6cXgzajdScGMzcTdVZUQtRDVQcnpaX2zSAboBQVVfeXFMT3NhcHA1NWlldE1CSTZCYlFFMXdYaExRSjU0UEhfRlRZWDFUam1OQzZLbXdxcnlqUnZBSW92bFN6WnczVlNwZ1VQRDNlMWIzaGFIWjF3V2FCZFVUY0ljTWRQWE5BTVFNY0EzUjlWd0xQa0RWdmZBSE9OdUhVd2F3a3JHaWNvei02NV83R3hfNkUyQU84UnpiMlRhU3laWDB5TXViclZ5SzJTcjd1bllCcFhXc0hGb3dMdVZB?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a62637111bb4415a383110696fcab4c&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>calcario agricola</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Aplicação conjunta de calcário e fosfato natural gera 12 sacas de soja a mais por hectare - Canal Rural</t>
+          <t>Líder em fornecimento de calcário agrícola, FIDA projeta crescimento do setor na Expointer - Jornal O Sul</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>20/09/2025 04:00</t>
+          <t>06/09/2025 04:00</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPWmZCdkpqRF9uYUhERS1tS050aHNvaGpjNE1XUWJ4QTZmZ1dtQk1JcElPNEZLaXA1NENVX3hDQ0YwQWZTMVgyY3FsTi12cVBUSG5CaTR2aldlSXRRNWJGeklvNTh0YlZsSmV6SUY5amN5aUJGbFZBZWVuTmhjN1Fsa1VuZVVfSk9IWGtjbFRTUG1GQURHTHV3VDkzRHlKMEowaFdmMjlCc2JyQkZzeno3WktXd212WUhHenBCRy1uUVZQV3VPbHUwUXF6bGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRG9EYmVPQVF4emNrdE05dG1YU2dmc29CRnNicHdrWWdfQURremhXQnY1V0FTMW1FX3RfWjVIRlV6cFF4U2FCV3BfR2RJZkc0aGVsTXlBRkZqMnFyY2NNQTZFOGxxZDBFeEx2NUlIa0xYYURuMzM4OWdLWngtZnJYajNncGlpbmdSRGJrZTlibEpyMXh2Nlc2NW1SYjQ3Vnk2TXJ0Z2lBaU90dmRkbTRvcTIyYmjSAboBQVVfeXFMTXUwUXpMVFlNSlFLSkhpUTdBMWdGN2IwUUtyZ05YbTY0R1hvNS1ybkJsdnN2RTJwa0cxQzFCYVVBTU8ySkVLYzRSYWpuS3kyMTV0dnA4b2ZoazFmWUpYWjJWdkFrWFl0QkVKMGpDQlZLM09PM01xZVJGMDgtY0NGN01GdUo2ZEFSM0MweXczVnhielRfbnFLRFN2Zlo3WDc5bE5rTkFlNTk2TVB1QXdhdzgyTTBETk4wNWF3?oc=5</t>
         </is>
       </c>
     </row>
@@ -11446,17 +11446,17 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Áurea investe em novo distribuidor de calcário para o setor agrícola - Jornal Bom Dia</t>
+          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>15/09/2025 04:00</t>
+          <t>05/09/2025 04:00</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQRGR6N2hWX3A2ZGR4RmJWbWNqdnBqUGktU25QbDhLZUlvSmVIVERqRVpTazJKRlFSdzBfQ2s3UzJJZFN6dHd5TllCZXR6SGYxV3llYUFwdlFlSDZEWi1jb1V0bXVfVDVQZTNjWVRXcnZ3WDVPVUlaZ2xhZXNFcmNBUXlPdGFZdVFrVkM4RTZkNjEzTXMzT3RodVJSS3ZvMkxlXy1pbDl2OU1vVlY5dU9NVHp3LVU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
         </is>
       </c>
     </row>
@@ -11468,17 +11468,17 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>CSN apresenta projeto de aproveitamento de resíduos ao secretário de Agricultura</t>
+          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>07/09/2025 14:00</t>
+          <t>02/09/2025 14:00</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e233b734cabaee823cb4f045c9e&amp;url=https%3a%2f%2fdiariodovale.com.br%2fdestaque%2fcsn-apresenta-projeto-de-aproveitamento-de-residuos-ao-secretario-de-agricultura%2f&amp;c=15059526041694740664&amp;mkt=pt-br</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a62637111bb4415a383110696fcab4c&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
@@ -11490,389 +11490,367 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Líder em fornecimento de calcário agrícola, FIDA projeta crescimento do setor na Expointer - Jornal O Sul</t>
+          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>06/09/2025 04:00</t>
+          <t>02/09/2025 04:00</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNRG9EYmVPQVF4emNrdE05dG1YU2dmc29CRnNicHdrWWdfQURremhXQnY1V0FTMW1FX3RfWjVIRlV6cFF4U2FCV3BfR2RJZkc0aGVsTXlBRkZqMnFyY2NNQTZFOGxxZDBFeEx2NUlIa0xYYURuMzM4OWdLWngtZnJYajNncGlpbmdSRGJrZTlibEpyMXh2Nlc2NW1SYjQ3Vnk2TXJ0Z2lBaU90dmRkbTRvcTIyYmjSAboBQVVfeXFMTXUwUXpMVFlNSlFLSkhpUTdBMWdGN2IwUUtyZ05YbTY0R1hvNS1ybkJsdnN2RTJwa0cxQzFCYVVBTU8ySkVLYzRSYWpuS3kyMTV0dnA4b2ZoazFmWUpYWjJWdkFrWFl0QkVKMGpDQlZLM09PM01xZVJGMDgtY0NGN01GdUo2ZEFSM0MweXczVnhielRfbnFLRFN2Zlo3WDc5bE5rTkFlNTk2TVB1QXdhdzgyTTBETk4wNWF3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Pesquisa da UFMT aponta ganhos na soja com calcário e gesso - Revista Cultivar</t>
+          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>05/09/2025 04:00</t>
+          <t>01/09/2025 04:00</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTlZiNHZqcS1SX0dWTEZ0OEh6UnNzb2EzNEl6bjVNODBrZHFoODcybHlyRjlOd1JJalliX3F1UDczcGdoU2F0bnFDck9tbDJpYjREX2pQVExqdVJxSzNDTHIwVm5DckEwOElfdmYtbmhBYkd5TVJjbWtxenhtWWJITXhETVVYUER2dVFVNXpwalVXV2hLLUhvbzNGdXlvOXJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Mais de 5 mil toneladas de calcário foram entregues pelo governo de RO a produtores em 2025</t>
+          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>02/09/2025 14:00</t>
+          <t>01/09/2025 04:00</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e233b734cabaee823cb4f045c9e&amp;url=https%3a%2f%2fwww.tudorondonia.com%2fnoticias%2fmais-de-5-mil-toneladas-de-calcario-foram-entregues-pelo-governo-de-ro-a-produtores-em-2025%2c146623.shtml&amp;c=898900062870723656&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>calcario agricola</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Novo método propõe cálculo mais preciso da calagem para aumentar produtividade agrícola - UFLA - Universidade Federal de Lavras</t>
+          <t>Com minas e novo centro de pesquisa, Catalão busca se tornar a capital brasileira das terras raras - Jornal Opção</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>02/09/2025 04:00</t>
+          <t>26/08/2025 04:00</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNUTRJN01vT2x1dVliRnVleUlieDVXbkc5eWYtZVZBSXc2OEt5VmttWWhyX1liTzQ1SGx4YWN3alZMNWdMNmVYVjJoM2ZYNzN5OXZyUGZOQXVZSUxLYjNLcXktdVVMY0hqNWdNMVU1NXR5cVBRM0NpMFMtdzNDajJTTUNRbTYtOVVXRTdocWgtV3ptN2ZDbXZMeS1YbjFSVjBTY2RtT1N5VkxOX1VhVEYyOGcxWWF2UVh2RGlzY2ZPUEpyWVJQZ0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNYWVzamxVeFVmaGt0TnlfU3o0YjVDUVc5ZlJROS1KajRLWldJdEdMQWFoLXQ1OFhwU2VhMGtNMlRwQUx4VGVFdVA0RUNHTnREaEl3MW5maG15S2RxelhRWEg0N0YxcTNfaFdDc1BGYnF1dUdmOE55MzItSnAtcUZqZVZpM3o0VXVKanhfRldFWFM2TDFxWldtUDYxa0FCV01rcXJYMFU1UXU5emo0RUl5MjZEbjF3MXZPVHdCeUhuTzJuN1ZwdW5lNG9BUlZNRGdmbFptcnMzaGY4WnZleGk4S0VTRVY3QTZU?oc=5</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>RESULTADOS | CMOC Brasil produz 3% a mais de nióbio no primeiro semestre - Brasil Mineral</t>
+          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>22/08/2025 04:00</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQWXVjQkdsWUV3ZktWcld5RzIyZFlBSFhybW9wNEV4NGV4OGdnaDBha0NrZzI0X3VzN2N4d0M0bGNUdkRtYmR6bFE2Q0JDbkJyN25iVzFDemJDbTlOSDJ4NENpTjNZWWpTbFkzTzF0SXhIQUhCdkw2Y1J4aW9nVEFhdVRBR25aTVJldElQQ2pabFZZNWVyMWNoSndGd1hTUzBXS3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>CMOC Brasil tem resultados do 1º semestre impulsionados por produção recorde de nióbio - Valor Econômico</t>
+          <t>Governo de RO entrega mais de 950 toneladas de calcário para fortalecer produção agropecuária no estado - ro.gov.br</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>01/09/2025 04:00</t>
+          <t>19/08/2025 04:00</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPM1RuT2czaU14c3FTekU3cVNObDZDX19TRmRQWjZUT2FhVm56b2ZLWmZ5dG9iZlBoZ2ZXenNXckw1ZmE1S0pCS1FpcWlRYkp3M3dpUWV0Q1g4U013SjAtS3psTTlpWUtzdW1JTTNlbjhDMk5wZVp6MkRubXlNV21kWlViVEVNNjNMeklHS3ExMEQ3VGV1dEY1QVJvMjNoT0x0MVNKcEJxLXZHdHU2Uk5Ia0lPdF85QUFiVzA5WDBRU3c4cXk4WjZPS0dMLWQ1cExKZFNpYk9lZXZjcmFC0gHrAUFVX3lxTE1uellrN1Z6RWNvZE1oQjlIUHNzd3hITG8zdHBvWDd1RWp4Ymp2NnFic2pET1dhMUxQeU1YdXlOQ0U0cmtDWjZGVGM0Q0VWSk9iMUZLNEpHSjhQX3FOZGlibnhiUmtqZDY4YUdMVzNlTEY3X2VQb1lZbmtKUXFGTm4tS1FOWHM2R2NmMVI1TXJIVmV0aUJpVU9aZHMwQjBqRlJqaW9FcjA4YmtEakNUZFZpYTFnblNHVWl2Zm5tRnZsTVBrV0dVTVJYc0hiLXo5aGNJdEJqVFFTOExDTVBHWHVGMUZZUGNkbjRuRGM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTUEzVERudnBEWUlEZXBYZmZPdEJhR3RFZHRrdlpBTVZBdDlxdExmRDRRTWJNNXQtNjFfQWRxUmoxQlBadUdsWG1SRUJZTG9BbkR2clhSOTg0SG9YY1BtaF85dHBrS0ZybFRLYUdnZUhyYlNfM3ZJR29aMlRiS0wwbm53bzlpTWV4S3V2NnMtZjJScjRKcXR5RGtsVTVMcjkwLVFTdl9TeHJ5U0x3b1R2WHZzQlNoTHY4MFpxeGdQN2tDT2t3cGtjR3J1MA?oc=5</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>agricultural lime</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Com minas e novo centro de pesquisa, Catalão busca se tornar a capital brasileira das terras raras - Jornal Opção</t>
+          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>26/08/2025 04:00</t>
+          <t>18/08/2025 14:00</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6AFBVV95cUxNYWVzamxVeFVmaGt0TnlfU3o0YjVDUVc5ZlJROS1KajRLWldJdEdMQWFoLXQ1OFhwU2VhMGtNMlRwQUx4VGVFdVA0RUNHTnREaEl3MW5maG15S2RxelhRWEg0N0YxcTNfaFdDc1BGYnF1dUdmOE55MzItSnAtcUZqZVZpM3o0VXVKanhfRldFWFM2TDFxWldtUDYxa0FCV01rcXJYMFU1UXU5emo0RUl5MjZEbjF3MXZPVHdCeUhuTzJuN1ZwdW5lNG9BUlZNRGdmbFptcnMzaGY4WnZleGk4S0VTRVY3QTZU?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a6263720c134cf998936ed89d546006&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Mosaic</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Mais de 1.600 toneladas de calcário são entregues a agricultores familiares para preparo de solo - Prefeitura Municipal de Boa Vista</t>
+          <t>Empresa da família Batista estreia na produção de fertilizantes com aquisição de mina de potássio</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>22/08/2025 04:00</t>
+          <t>15/08/2025 04:31</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQLXdRbkZkNHpnb1NhakYtOWNSTkFBa2VTdFNJTUhPUXZZeXhrekp3dlg4UEZuUWZDWk5SZm44LUQtWDdUNkVkZUdRSWRkcXZ1QUhCUzVqRzM3YTU3TkFGYlJrcE93YXQ5LS15X29oWkE2OV82ZmVKQ2JaWXhJcjZycDl5ZURxMGhDVERtcEttT0NVb1M4V2hOdEpCd2JpZWdlWWV0STZXdk9HZUtrTm04WmNSb2JJalVsbTk5Wk43OTAyTF9ESXNobjQ0VU5XS2xMQ0dHaQ?oc=5</t>
+          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a626377261a4eedb2d81e9c56dd2079&amp;url=https%3a%2f%2fwww.estadao.com.br%2feconomia%2ffamilia-batista-producao-fertilizantes-aquisicao-potassio-mosaic%2f&amp;c=677292496599485556&amp;mkt=pt-br</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>Carmeuse</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Governo de RO entrega mais de 950 toneladas de calcário para fortalecer produção agropecuária no estado - ro.gov.br</t>
+          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>19/08/2025 04:00</t>
+          <t>15/08/2025 04:00</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPTUEzVERudnBEWUlEZXBYZmZPdEJhR3RFZHRrdlpBTVZBdDlxdExmRDRRTWJNNXQtNjFfQWRxUmoxQlBadUdsWG1SRUJZTG9BbkR2clhSOTg0SG9YY1BtaF85dHBrS0ZybFRLYUdnZUhyYlNfM3ZJR29aMlRiS0wwbm53bzlpTWV4S3V2NnMtZjJScjRKcXR5RGtsVTVMcjkwLVFTdl9TeHJ5U0x3b1R2WHZzQlNoTHY4MFpxeGdQN2tDT2t3cGtjR3J1MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>agricultural lime</t>
+          <t>calcario</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Spreading Ag Lime for Food Plots | Improving Deer Habitat on Our Southern Illinois Farm</t>
+          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>18/08/2025 14:00</t>
+          <t>13/08/2025 04:00</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>http://www.bing.com/news/apiclick.aspx?ref=FexRss&amp;aid=&amp;tid=6a624e2471054300949a6a1e2db1d4be&amp;url=https%3a%2f%2fwww.msn.com%2fen-us%2ffoodanddrink%2ffoodnews%2fspreading-ag-lime-for-food-plots-improving-deer-habitat-on-our-southern-illinois-farm%2fvi-AA1KMIuT&amp;c=14837966501036489110&amp;mkt=pt-br</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Carmeuse</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Multinacional Carmeuse Brasil anuncia investimento em Araçatuba - O LIBERAL REGIONAL</t>
+          <t>Cooperja realiza 4° Campo de Inverno, edição itinerante em Içara - Portal C1</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>15/08/2025 04:00</t>
+          <t>11/08/2025 04:00</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNUC16YUloeERuMjNLeHMtOVBReUltWEN5dGhOMFctRmd0T25uYzdUbVM4SnFZcVA4X0owRzMtQUg5eUN1WXpRdk5abjZrYkVNcXcyYzNYQ2hsZGdFWFo4SU9JTTNOcnJqVVhMc0ttTDd2T2d3X21WZzlNUUhFck1MSzVUdFVRZENCZ21LN2h4NURZR0NjRTBKaFRhUjRoemFOY2ZJ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOSGlYelBIZk55b0xpZ1FReHdSTk1JWG9KSUt2cWpZNVVLMTFFNWw5NmE3eFdNYlpFV3prRXk2YnNlVXhDM0N5OUE3UTFjRUJNdzM0UVZRX3RiZU1rT0lNTUQ5c20zTmdFaGs0aWFUaTBJNmNfTUhWd0VaeFMyODFyVmNHaXVUSEN5YmhnVmdTQjQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>calcario</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Calcário líquido: é por isso que ele não funciona na correção do solo - Canal Rural</t>
+          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>13/08/2025 04:00</t>
+          <t>11/08/2025 04:00</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSHlxZDdybW5fY0FOMmRRMEN0bURlZDAxSjQ1LWJrOExhWUxTa1RqT2l6Z2FqVWZZWFlLOG9LekduQTA3Vmp0QW5VME1oNEktdmZ4cDdsbU9YX0pJMUNwbVdzaDdkbzB5Mi1DalF0Z0JoN1ZoVE1ENVB2UjJpdHp3LWFVZGZsV2pETlZRTlhQNkxlR2o1RkstSUhiQ1FqX3ZXSDROcFpWdFh4Yzd2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Limestone Capital Investe na Nokken para Abastecer a Expansão de Hospitalidade Modular - PR Newswire</t>
+          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>11/08/2025 04:00</t>
+          <t>06/08/2025 04:00</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxPWU80YXJ5NDJUWmw1VjJscFpVbDRWVlJsM09lZ3Vjdkg4czlKekxPUWJUWXpaQjg4WDZONGk1MjdxV29mRm1aTHZWRG5FeUFsWHpPTk50VFVhak9QU1dYak9tM3Buc21nRGxmLTljbzNSd1I2ZVlZa2luY3BrRGIwb1lTcml2RU1NMUlrdmt6WVExREs4S1psdHdXM3czY2pUcjBzeU92UDhpZ0lELTFZQjZaaHN6WVY1WjRDWmdJZklfV2dpbWk0ZDBjUk8xcDlnQjU0X05nU01idTJCZmNmUmNZUXpaRWZveHBv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>CMOC</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Trabalhadores da Manserv entram em greve e exigem jornada 4×4 e melhores condições de trabalho - Badiinho</t>
+          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>06/08/2025 04:00</t>
+          <t>02/08/2025 04:00</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9fN3VVZmJNM2pGMzB3V19FM1N4d3hpWnVaMUZvZUtXWXZhUFFCSXMxNXlyTUt6dnQyalF6bFNZN0ZPcW5QVWp1dDV2d1FoX19nRzg4VXJjaG93OUJYSndmTEdCUDBacHFyUVRBNTFaRmhiYzBhcVQtV9IBfkFVX3lxTFBuc1ZCZ1hCOFRSdVBxVktkYldTdUE0QUkzQzEybEZzVXplV1A2MlRscGxudmhPOW9xNTlic25DVURrMWhIaW9QS3ZfNl92OWJzS1FkeXhQMXpaWGVidUhjeWtmamR6MmNsZkV6ZTVneVdsYkQ4RnA4OEpSTFNfUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>limestone</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>O futuro circular do agro: como cientistas e empresas estão transformando resíduos em fertilizantes - AgFeed</t>
+          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>02/08/2025 04:00</t>
+          <t>01/08/2025 21:12</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOdXhBZ1hpcXVfVG11ME5ZRUZZOG1DNUM3Rk55dmNoNGNLbVVqcjZZanVVRkZJV24wc1c3VktmWUFpR2steTRQdkJzbzdLU29WQU5kb2lmalhLSlFQdmFCbU9helVFTzZWZThyWExESVhOX3VRTE1GTGZFMmtEOWo2SkY5RDV6TzZwNXN6RFY1LVM3SjRzeTBkT3ZPWURzNFp3YWtKX05NWnM0dWNEQUV0amNqbW52RzJqaUxVMFIzT3EzR0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>limestone</t>
+          <t>corretivo de solo</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>WILSON HUSUM, Limestone Carrier - Detalhes e posição atual - IMO 9017379 - VesselFinder</t>
+          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>01/08/2025 21:12</t>
+          <t>31/07/2025 04:00</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9VeVpNZDZDc09nd0F4WWJFTGR0VGlYMmtiYV9OVjloQ254cllIaERRX3psSzVTaUJhNjdVcXJpZHFmQmVyUVhKc2tOSXZOYzhFaFF2OGNKMEVHNmxFU3FUeGh6VmszZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>corretivo de solo</t>
+          <t>CMOC</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Emater-MG encerra segunda etapa da entrega de agrosilício a agricultores de Minas Gerais - emater.mg.gov.br</t>
+          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>31/07/2025 04:00</t>
+          <t>29/07/2025 04:00</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxONmF2eGdidE1Nai1hZ2E4bU84U3FqMWYzTlF0dEJQdVNxOHJuNmNlSDhWdG16cjJGcFRvd3luU2dQWjlNQ2NWb3M4R3JlNHRpUFg3TjlDM2E1eElCRzFNZ01vMUVEdl90THNLMU5MeHNONkd0ajl4TWI4Tm9nejlOWm5MUk82bUxWaHotWlkyWGl6MWUtWkkyT0NkalBkaEp5ajBreEc1b3dIcC1EaFZfQkotWnA2b2RtcktJbUUtWVlCZ2tobFZIb3N0dkdzaDViRXRkX0NHNG05ZjZJTTV6MENqQXAwMHF6QS1WcXFjWmVTbEstZVp0VDdNRW5ESk1UN05HZnkxLS1ZVXZRelVQOWFsU2xxSDhxNXpV?oc=5</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>CMOC</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>CMOC é destaque nacional por melhorias na planta de nióbio em Ouvidor (GO) - Portal Serra Dourada News</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>29/07/2025 04:00</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxOZWZ1SmNscXJLQTgtcGo3S2JvMGM0UXhTRnAyVW9mYzFNYmNzMHRtTG5rNjJWWWg3c1pFeUVHczBRNEw2NVU1R3dlLW5hbTFYUXc0a0diRFBFWFBUVzFpLUkyNXpselV2TVBIcnZvNUhkNjEzN3ZzTjNvX0pvdVQzM3RJZkFmdkMtaFp3aHZRZ1gxN3kwdmZCNDJ6NFBjb2pyZHNIc2pwS0F6bUhtOEpoOVJNUQ?oc=5</t>
         </is>
